--- a/research/traditional_assets/database/data/spain/spain_apparel.xlsx
+++ b/research/traditional_assets/database/data/spain/spain_apparel.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="bme_adz" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -351,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,34 +590,34 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0443</v>
+        <v>0.008150000000000001</v>
       </c>
       <c r="G2">
-        <v>-0.1093015332197615</v>
+        <v>-0.0282132396016403</v>
       </c>
       <c r="H2">
-        <v>-0.1131516183986371</v>
+        <v>-0.02835383714118336</v>
       </c>
       <c r="I2">
-        <v>-0.1142759795570698</v>
+        <v>-0.007510251903925015</v>
       </c>
       <c r="J2">
-        <v>-0.1142759795570698</v>
+        <v>-0.007510251903925015</v>
       </c>
       <c r="K2">
-        <v>-62.7</v>
+        <v>-5.890000000000001</v>
       </c>
       <c r="L2">
-        <v>-0.2136286201022147</v>
+        <v>-0.03450497949619215</v>
       </c>
       <c r="M2">
-        <v>0.354</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.001842982090795502</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>-0.005645933014354066</v>
+        <v>-0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -627,79 +629,76 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>0.354</v>
-      </c>
-      <c r="T2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>27.82</v>
+        <v>13.1</v>
       </c>
       <c r="V2">
-        <v>0.144835485214494</v>
+        <v>0.06693919264179868</v>
       </c>
       <c r="W2">
-        <v>-0.4752186588921283</v>
+        <v>0.03259160066100633</v>
       </c>
       <c r="X2">
-        <v>0.1150272659581076</v>
+        <v>0.1550823297482159</v>
       </c>
       <c r="Y2">
-        <v>-0.5902459248502359</v>
+        <v>-0.1224907290872096</v>
       </c>
       <c r="Z2">
-        <v>0.975180250523308</v>
+        <v>2.159392789373814</v>
       </c>
       <c r="AA2">
-        <v>-0.3234782608695653</v>
+        <v>-0.03653172759744695</v>
       </c>
       <c r="AB2">
-        <v>0.06550730156948141</v>
+        <v>0.1091007857070927</v>
       </c>
       <c r="AC2">
-        <v>-0.3889849622387354</v>
+        <v>-0.1456325133045396</v>
       </c>
       <c r="AD2">
-        <v>286.2</v>
+        <v>110.8</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>286.2</v>
+        <v>110.8</v>
       </c>
       <c r="AG2">
-        <v>258.38</v>
+        <v>97.7</v>
       </c>
       <c r="AH2">
-        <v>0.5983942460483399</v>
+        <v>0.3615008156606851</v>
       </c>
       <c r="AI2">
-        <v>0.9774590163934426</v>
+        <v>1.079922027290448</v>
       </c>
       <c r="AJ2">
-        <v>0.573591439861475</v>
+        <v>0.3329925017041582</v>
       </c>
       <c r="AK2">
-        <v>0.9750924598082873</v>
+        <v>1.091620111731844</v>
       </c>
       <c r="AL2">
-        <v>12.32</v>
+        <v>4.56</v>
       </c>
       <c r="AM2">
-        <v>11.902</v>
+        <v>4.322000000000001</v>
       </c>
       <c r="AN2">
-        <v>-13.3675852405418</v>
+        <v>31.65714285714285</v>
       </c>
       <c r="AO2">
-        <v>-2.722402597402597</v>
+        <v>-0.281140350877193</v>
       </c>
       <c r="AP2">
-        <v>-12.06819243344232</v>
+        <v>27.91428571428571</v>
       </c>
       <c r="AQ2">
-        <v>-2.818013779196773</v>
+        <v>-0.2966219342896806</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +709,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Liwe Española, S.A. (BDM:LIW)</t>
+          <t>Adolfo Domínguez, S.A. (BME:ADZ)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,25 +718,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0443</v>
+        <v>-0.0206</v>
       </c>
       <c r="G3">
-        <v>-0.04121969140337987</v>
+        <v>-0.08480154888673766</v>
       </c>
       <c r="H3">
-        <v>-0.04121969140337987</v>
+        <v>-0.08480154888673766</v>
       </c>
       <c r="I3">
-        <v>-0.01058045554739162</v>
+        <v>0.006176185866408519</v>
       </c>
       <c r="J3">
-        <v>-0.01058045554739162</v>
+        <v>0.006176185866408519</v>
       </c>
       <c r="K3">
-        <v>-16.3</v>
+        <v>-1.24</v>
       </c>
       <c r="L3">
-        <v>-0.1197648787656135</v>
+        <v>-0.01200387221684414</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -761,73 +760,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>7.76</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="V3">
-        <v>0.8940092165898618</v>
+        <v>0.2168765743073048</v>
       </c>
       <c r="W3">
-        <v>-0.4752186588921283</v>
+        <v>-0.07701863354037267</v>
       </c>
       <c r="X3">
-        <v>0.801593128926344</v>
+        <v>0.1753085997381087</v>
       </c>
       <c r="Y3">
-        <v>-1.276811787818472</v>
+        <v>-0.2523272332784814</v>
       </c>
       <c r="Z3">
-        <v>0.6572339192582577</v>
+        <v>1.834813499111901</v>
       </c>
       <c r="AA3">
-        <v>-0.006953834266949972</v>
+        <v>0.01133214920071048</v>
       </c>
       <c r="AB3">
-        <v>0.07097338567718592</v>
+        <v>0.1082610149307064</v>
       </c>
       <c r="AC3">
-        <v>-0.07792721994413589</v>
+        <v>-0.09692886572999589</v>
       </c>
       <c r="AD3">
-        <v>169</v>
+        <v>45.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>169</v>
+        <v>45.8</v>
       </c>
       <c r="AG3">
-        <v>161.24</v>
+        <v>37.19</v>
       </c>
       <c r="AH3">
-        <v>0.9511481314723097</v>
+        <v>0.535672514619883</v>
       </c>
       <c r="AI3">
-        <v>0.8792924037460979</v>
+        <v>0.765886287625418</v>
       </c>
       <c r="AJ3">
-        <v>0.9489171374764594</v>
+        <v>0.4836779815320588</v>
       </c>
       <c r="AK3">
-        <v>0.8742138364779874</v>
+        <v>0.7265090838054308</v>
       </c>
       <c r="AL3">
-        <v>7.6</v>
+        <v>1.35</v>
       </c>
       <c r="AM3">
-        <v>7.598999999999999</v>
+        <v>1.143</v>
       </c>
       <c r="AN3">
-        <v>28.69269949066214</v>
+        <v>22.23300970873786</v>
       </c>
       <c r="AO3">
-        <v>-0.1894736842105263</v>
+        <v>0.4725925925925926</v>
       </c>
       <c r="AP3">
-        <v>27.37521222410866</v>
+        <v>18.05339805825243</v>
       </c>
       <c r="AQ3">
-        <v>-0.189498618239242</v>
+        <v>0.558180227471566</v>
       </c>
     </row>
     <row r="4">
@@ -838,7 +837,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Adolfo Domínguez, S.A. (BME:ADZ)</t>
+          <t>Nueva Expresión Textil, S.A. (BME:NXT)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -847,34 +846,34 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.05599999999999999</v>
+        <v>0.0369</v>
       </c>
       <c r="G4">
-        <v>-0.1768488745980707</v>
+        <v>0.05851632047477744</v>
       </c>
       <c r="H4">
-        <v>-0.1768488745980707</v>
+        <v>0.05816023738872403</v>
       </c>
       <c r="I4">
-        <v>-0.1993569131832798</v>
+        <v>-0.02848664688427299</v>
       </c>
       <c r="J4">
-        <v>-0.1993569131832798</v>
+        <v>-0.02848664688427299</v>
       </c>
       <c r="K4">
-        <v>-23.2</v>
+        <v>-4.65</v>
       </c>
       <c r="L4">
-        <v>-0.2486602357984995</v>
+        <v>-0.06899109792284866</v>
       </c>
       <c r="M4">
-        <v>0.354</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.008916876574307304</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>-0.01525862068965517</v>
+        <v>0</v>
       </c>
       <c r="P4">
         <v>-0</v>
@@ -886,207 +885,8777 @@
         <v>0</v>
       </c>
       <c r="S4">
-        <v>0.354</v>
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>4.49</v>
+      </c>
+      <c r="V4">
+        <v>0.02878205128205128</v>
+      </c>
+      <c r="W4">
+        <v>0.1422018348623853</v>
+      </c>
+      <c r="X4">
+        <v>0.1348560597583231</v>
+      </c>
+      <c r="Y4">
+        <v>0.007345775104062202</v>
+      </c>
+      <c r="Z4">
+        <v>2.962637362637362</v>
+      </c>
+      <c r="AA4">
+        <v>-0.08439560439560438</v>
+      </c>
+      <c r="AB4">
+        <v>0.109940556483479</v>
+      </c>
+      <c r="AC4">
+        <v>-0.1943361608790834</v>
+      </c>
+      <c r="AD4">
+        <v>65</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>65</v>
+      </c>
+      <c r="AG4">
+        <v>60.51</v>
+      </c>
+      <c r="AH4">
+        <v>0.2941176470588235</v>
+      </c>
+      <c r="AI4">
+        <v>1.518691588785047</v>
+      </c>
+      <c r="AJ4">
+        <v>0.2794790078980185</v>
+      </c>
+      <c r="AK4">
+        <v>1.579483163664839</v>
+      </c>
+      <c r="AL4">
+        <v>3.21</v>
+      </c>
+      <c r="AM4">
+        <v>3.179</v>
+      </c>
+      <c r="AN4">
+        <v>45.13888888888889</v>
+      </c>
+      <c r="AO4">
+        <v>-0.5981308411214953</v>
+      </c>
+      <c r="AP4">
+        <v>42.02083333333334</v>
+      </c>
+      <c r="AQ4">
+        <v>-0.603963510537905</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Adolfo Domínguez, S.A. (BME:ADZ)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BME:ADZ</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Apparel</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.535672514619883</v>
+      </c>
+      <c r="F2">
+        <v>0.01</v>
+      </c>
+      <c r="G2">
+        <v>39.7</v>
+      </c>
+      <c r="H2">
+        <v>59.0206277218666</v>
+      </c>
+      <c r="I2">
+        <v>76.89</v>
+      </c>
+      <c r="J2">
+        <v>51.2656277218666</v>
+      </c>
+      <c r="K2">
+        <v>45.8</v>
+      </c>
+      <c r="L2">
+        <v>0.855</v>
+      </c>
+      <c r="M2">
+        <v>0.108261014930706</v>
+      </c>
+      <c r="N2">
+        <v>0.142980084695304</v>
+      </c>
+      <c r="O2">
+        <v>0.0501433486238532</v>
+      </c>
+      <c r="P2">
+        <v>2.45809824561404</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.175308599738109</v>
+      </c>
+      <c r="T2">
+        <v>0.119595052766832</v>
+      </c>
+      <c r="U2">
+        <v>1.57392881238592</v>
+      </c>
+      <c r="V2">
+        <v>0.931557877613025</v>
+      </c>
+      <c r="W2">
+        <v>-37.1741749684093</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>39.7</v>
+      </c>
+      <c r="AB2">
+        <v>0.08673111430699013</v>
+      </c>
+      <c r="AC2">
+        <v>0.06685779816513762</v>
+      </c>
+      <c r="AD2">
+        <v>0.25</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>2.06</v>
+      </c>
+      <c r="AH2">
+        <v>9.65</v>
+      </c>
+      <c r="AI2">
+        <v>3.7</v>
+      </c>
+      <c r="AJ2">
+        <v>45.8</v>
+      </c>
+      <c r="AK2">
+        <v>45.8</v>
+      </c>
+      <c r="AL2">
+        <v>1.35</v>
+      </c>
+      <c r="AM2">
+        <v>45.8</v>
+      </c>
+      <c r="AN2">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>-45.8</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H2">
+        <v>39.7</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>2.06</v>
+      </c>
+      <c r="K2">
+        <v>9.65</v>
+      </c>
+      <c r="L2">
+        <v>-7.59</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>-7.59</v>
+      </c>
+      <c r="O2">
+        <v>-1.8975</v>
+      </c>
+      <c r="P2">
+        <v>-5.6925</v>
+      </c>
+      <c r="Q2">
+        <v>3.9575</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>-Inf</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1429800846953044</v>
+      </c>
+      <c r="C3">
+        <v>59.02062772186663</v>
+      </c>
+      <c r="D3">
+        <v>51.26562772186663</v>
+      </c>
+      <c r="E3">
+        <v>-44.945</v>
+      </c>
+      <c r="F3">
+        <v>0.855</v>
+      </c>
+      <c r="G3">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H3">
+        <v>39.7</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>2.06</v>
+      </c>
+      <c r="K3">
+        <v>9.65</v>
+      </c>
+      <c r="L3">
+        <v>-7.59</v>
+      </c>
+      <c r="M3">
+        <v>0.204174</v>
+      </c>
+      <c r="N3">
+        <v>-7.794174</v>
+      </c>
+      <c r="O3">
+        <v>-1.9485435</v>
+      </c>
+      <c r="P3">
+        <v>-5.8456305</v>
+      </c>
+      <c r="Q3">
+        <v>3.8043695</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1195950527668324</v>
+      </c>
+      <c r="T3">
+        <v>0.9315578776130251</v>
+      </c>
+      <c r="U3">
+        <v>0.2388</v>
+      </c>
+      <c r="V3">
+        <v>-9.293543742102324</v>
+      </c>
+      <c r="W3">
+        <v>2.458098245614035</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>-37.1741749684093</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1449800846953044</v>
+      </c>
+      <c r="C4">
+        <v>57.1999922570056</v>
+      </c>
+      <c r="D4">
+        <v>50.2999922570056</v>
+      </c>
+      <c r="E4">
+        <v>-44.09</v>
+      </c>
+      <c r="F4">
+        <v>1.71</v>
+      </c>
+      <c r="G4">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H4">
+        <v>39.7</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>2.06</v>
+      </c>
+      <c r="K4">
+        <v>9.65</v>
+      </c>
+      <c r="L4">
+        <v>-7.59</v>
+      </c>
+      <c r="M4">
+        <v>0.408348</v>
+      </c>
+      <c r="N4">
+        <v>-7.998348</v>
+      </c>
+      <c r="O4">
+        <v>-1.999587</v>
+      </c>
+      <c r="P4">
+        <v>-5.998761</v>
+      </c>
+      <c r="Q4">
+        <v>3.651239</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1204194920807797</v>
       </c>
       <c r="T4">
+        <v>0.9410635702417294</v>
+      </c>
+      <c r="U4">
+        <v>0.2388</v>
+      </c>
+      <c r="V4">
+        <v>-4.646771871051162</v>
+      </c>
+      <c r="W4">
+        <v>1.348449122807018</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>-18.58708748420465</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1469800846953044</v>
+      </c>
+      <c r="C5">
+        <v>55.41506153271973</v>
+      </c>
+      <c r="D5">
+        <v>49.37006153271973</v>
+      </c>
+      <c r="E5">
+        <v>-43.235</v>
+      </c>
+      <c r="F5">
+        <v>2.565</v>
+      </c>
+      <c r="G5">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H5">
+        <v>39.7</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>2.06</v>
+      </c>
+      <c r="K5">
+        <v>9.65</v>
+      </c>
+      <c r="L5">
+        <v>-7.59</v>
+      </c>
+      <c r="M5">
+        <v>0.612522</v>
+      </c>
+      <c r="N5">
+        <v>-8.202522</v>
+      </c>
+      <c r="O5">
+        <v>-2.0506305</v>
+      </c>
+      <c r="P5">
+        <v>-6.1518915</v>
+      </c>
+      <c r="Q5">
+        <v>3.498108500000001</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1212609301434681</v>
+      </c>
+      <c r="T5">
+        <v>0.9507652565328814</v>
+      </c>
+      <c r="U5">
+        <v>0.2388</v>
+      </c>
+      <c r="V5">
+        <v>-3.097847914034108</v>
+      </c>
+      <c r="W5">
+        <v>0.9785660818713452</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>-12.39139165613643</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1489800846953044</v>
+      </c>
+      <c r="C6">
+        <v>53.66389120086259</v>
+      </c>
+      <c r="D6">
+        <v>48.4738912008626</v>
+      </c>
+      <c r="E6">
+        <v>-42.38</v>
+      </c>
+      <c r="F6">
+        <v>3.42</v>
+      </c>
+      <c r="G6">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H6">
+        <v>39.7</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>2.06</v>
+      </c>
+      <c r="K6">
+        <v>9.65</v>
+      </c>
+      <c r="L6">
+        <v>-7.59</v>
+      </c>
+      <c r="M6">
+        <v>0.816696</v>
+      </c>
+      <c r="N6">
+        <v>-8.406696</v>
+      </c>
+      <c r="O6">
+        <v>-2.101674</v>
+      </c>
+      <c r="P6">
+        <v>-6.305022</v>
+      </c>
+      <c r="Q6">
+        <v>3.344978</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1221198981657959</v>
+      </c>
+      <c r="T6">
+        <v>0.960669061288432</v>
+      </c>
+      <c r="U6">
+        <v>0.2388</v>
+      </c>
+      <c r="V6">
+        <v>-2.323385935525581</v>
+      </c>
+      <c r="W6">
+        <v>0.7936245614035088</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>-9.293543742102324</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1509800846953044</v>
+      </c>
+      <c r="C7">
+        <v>51.94467557234843</v>
+      </c>
+      <c r="D7">
+        <v>47.60967557234843</v>
+      </c>
+      <c r="E7">
+        <v>-41.525</v>
+      </c>
+      <c r="F7">
+        <v>4.275</v>
+      </c>
+      <c r="G7">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H7">
+        <v>39.7</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>2.06</v>
+      </c>
+      <c r="K7">
+        <v>9.65</v>
+      </c>
+      <c r="L7">
+        <v>-7.59</v>
+      </c>
+      <c r="M7">
+        <v>1.02087</v>
+      </c>
+      <c r="N7">
+        <v>-8.61087</v>
+      </c>
+      <c r="O7">
+        <v>-2.1527175</v>
+      </c>
+      <c r="P7">
+        <v>-6.458152500000001</v>
+      </c>
+      <c r="Q7">
+        <v>3.1918475</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1229969497254359</v>
+      </c>
+      <c r="T7">
+        <v>0.9707813671967314</v>
+      </c>
+      <c r="U7">
+        <v>0.2388</v>
+      </c>
+      <c r="V7">
+        <v>-1.858708748420465</v>
+      </c>
+      <c r="W7">
+        <v>0.6826596491228069</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>-7.434834993681859</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1529800846953044</v>
+      </c>
+      <c r="C8">
+        <v>50.25573547326026</v>
+      </c>
+      <c r="D8">
+        <v>46.77573547326026</v>
+      </c>
+      <c r="E8">
+        <v>-40.66999999999999</v>
+      </c>
+      <c r="F8">
+        <v>5.13</v>
+      </c>
+      <c r="G8">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H8">
+        <v>39.7</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>2.06</v>
+      </c>
+      <c r="K8">
+        <v>9.65</v>
+      </c>
+      <c r="L8">
+        <v>-7.59</v>
+      </c>
+      <c r="M8">
+        <v>1.225044</v>
+      </c>
+      <c r="N8">
+        <v>-8.815044</v>
+      </c>
+      <c r="O8">
+        <v>-2.203761</v>
+      </c>
+      <c r="P8">
+        <v>-6.611283</v>
+      </c>
+      <c r="Q8">
+        <v>3.038717</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1238926619565575</v>
+      </c>
+      <c r="T8">
+        <v>0.981108828549888</v>
+      </c>
+      <c r="U8">
+        <v>0.2388</v>
+      </c>
+      <c r="V8">
+        <v>-1.548923957017054</v>
+      </c>
+      <c r="W8">
+        <v>0.6086830409356726</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>-6.195695828068216</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1549800846953044</v>
+      </c>
+      <c r="C9">
+        <v>48.59550735527542</v>
+      </c>
+      <c r="D9">
+        <v>45.97050735527542</v>
+      </c>
+      <c r="E9">
+        <v>-39.815</v>
+      </c>
+      <c r="F9">
+        <v>5.985</v>
+      </c>
+      <c r="G9">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H9">
+        <v>39.7</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>2.06</v>
+      </c>
+      <c r="K9">
+        <v>9.65</v>
+      </c>
+      <c r="L9">
+        <v>-7.59</v>
+      </c>
+      <c r="M9">
+        <v>1.429218</v>
+      </c>
+      <c r="N9">
+        <v>-9.019218</v>
+      </c>
+      <c r="O9">
+        <v>-2.2548045</v>
+      </c>
+      <c r="P9">
+        <v>-6.7644135</v>
+      </c>
+      <c r="Q9">
+        <v>2.8855865</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1248076368163055</v>
+      </c>
+      <c r="T9">
+        <v>0.9916583858461234</v>
+      </c>
+      <c r="U9">
+        <v>0.2388</v>
+      </c>
+      <c r="V9">
+        <v>-1.327649106014618</v>
+      </c>
+      <c r="W9">
+        <v>0.5558426065162907</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>-5.310596424058471</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1569800846953044</v>
+      </c>
+      <c r="C10">
+        <v>46.96253351181781</v>
+      </c>
+      <c r="D10">
+        <v>45.19253351181781</v>
+      </c>
+      <c r="E10">
+        <v>-38.95999999999999</v>
+      </c>
+      <c r="F10">
+        <v>6.84</v>
+      </c>
+      <c r="G10">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H10">
+        <v>39.7</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>2.06</v>
+      </c>
+      <c r="K10">
+        <v>9.65</v>
+      </c>
+      <c r="L10">
+        <v>-7.59</v>
+      </c>
+      <c r="M10">
+        <v>1.633392</v>
+      </c>
+      <c r="N10">
+        <v>-9.223392</v>
+      </c>
+      <c r="O10">
+        <v>-2.305848</v>
+      </c>
+      <c r="P10">
+        <v>-6.917544</v>
+      </c>
+      <c r="Q10">
+        <v>2.732456</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.125742502433874</v>
+      </c>
+      <c r="T10">
+        <v>1.002437281344451</v>
+      </c>
+      <c r="U10">
+        <v>0.2388</v>
+      </c>
+      <c r="V10">
+        <v>-1.161692967762791</v>
+      </c>
+      <c r="W10">
+        <v>0.5162122807017544</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>-4.646771871051163</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1589800846953044</v>
+      </c>
+      <c r="C11">
+        <v>45.35545327112908</v>
+      </c>
+      <c r="D11">
+        <v>44.44045327112908</v>
+      </c>
+      <c r="E11">
+        <v>-38.105</v>
+      </c>
+      <c r="F11">
+        <v>7.694999999999999</v>
+      </c>
+      <c r="G11">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H11">
+        <v>39.7</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>2.06</v>
+      </c>
+      <c r="K11">
+        <v>9.65</v>
+      </c>
+      <c r="L11">
+        <v>-7.59</v>
+      </c>
+      <c r="M11">
+        <v>1.837566</v>
+      </c>
+      <c r="N11">
+        <v>-9.427566000000001</v>
+      </c>
+      <c r="O11">
+        <v>-2.3568915</v>
+      </c>
+      <c r="P11">
+        <v>-7.070674500000001</v>
+      </c>
+      <c r="Q11">
+        <v>2.579325499999999</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.126697914548532</v>
+      </c>
+      <c r="T11">
+        <v>1.013453075644939</v>
+      </c>
+      <c r="U11">
+        <v>0.2388</v>
+      </c>
+      <c r="V11">
+        <v>-1.032615971344703</v>
+      </c>
+      <c r="W11">
+        <v>0.485388693957115</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>-4.130463885378811</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1609800846953044</v>
+      </c>
+      <c r="C12">
+        <v>43.77299505431812</v>
+      </c>
+      <c r="D12">
+        <v>43.71299505431812</v>
+      </c>
+      <c r="E12">
+        <v>-37.25</v>
+      </c>
+      <c r="F12">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="G12">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H12">
+        <v>39.7</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>2.06</v>
+      </c>
+      <c r="K12">
+        <v>9.65</v>
+      </c>
+      <c r="L12">
+        <v>-7.59</v>
+      </c>
+      <c r="M12">
+        <v>2.04174</v>
+      </c>
+      <c r="N12">
+        <v>-9.631740000000001</v>
+      </c>
+      <c r="O12">
+        <v>-2.407935</v>
+      </c>
+      <c r="P12">
+        <v>-7.223805</v>
+      </c>
+      <c r="Q12">
+        <v>2.426195</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1276745580435156</v>
+      </c>
+      <c r="T12">
+        <v>1.024713665374327</v>
+      </c>
+      <c r="U12">
+        <v>0.2388</v>
+      </c>
+      <c r="V12">
+        <v>-0.9293543742102323</v>
+      </c>
+      <c r="W12">
+        <v>0.4607298245614034</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>-3.717417496840929</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1629800846953044</v>
+      </c>
+      <c r="C13">
+        <v>42.21396920087191</v>
+      </c>
+      <c r="D13">
+        <v>43.00896920087191</v>
+      </c>
+      <c r="E13">
+        <v>-36.395</v>
+      </c>
+      <c r="F13">
+        <v>9.404999999999999</v>
+      </c>
+      <c r="G13">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H13">
+        <v>39.7</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>2.06</v>
+      </c>
+      <c r="K13">
+        <v>9.65</v>
+      </c>
+      <c r="L13">
+        <v>-7.59</v>
+      </c>
+      <c r="M13">
+        <v>2.245914</v>
+      </c>
+      <c r="N13">
+        <v>-9.835913999999999</v>
+      </c>
+      <c r="O13">
+        <v>-2.4589785</v>
+      </c>
+      <c r="P13">
+        <v>-7.376935499999999</v>
+      </c>
+      <c r="Q13">
+        <v>2.273064500000001</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1286731485833304</v>
+      </c>
+      <c r="T13">
+        <v>1.036227302063927</v>
+      </c>
+      <c r="U13">
+        <v>0.2388</v>
+      </c>
+      <c r="V13">
+        <v>-0.8448676129183932</v>
+      </c>
+      <c r="W13">
+        <v>0.4405543859649123</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>-3.379470451673572</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1649800846953044</v>
+      </c>
+      <c r="C14">
+        <v>40.67726147647581</v>
+      </c>
+      <c r="D14">
+        <v>42.3272614764758</v>
+      </c>
+      <c r="E14">
+        <v>-35.54</v>
+      </c>
+      <c r="F14">
+        <v>10.26</v>
+      </c>
+      <c r="G14">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H14">
+        <v>39.7</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>2.06</v>
+      </c>
+      <c r="K14">
+        <v>9.65</v>
+      </c>
+      <c r="L14">
+        <v>-7.59</v>
+      </c>
+      <c r="M14">
+        <v>2.450088</v>
+      </c>
+      <c r="N14">
+        <v>-10.040088</v>
+      </c>
+      <c r="O14">
+        <v>-2.510022</v>
+      </c>
+      <c r="P14">
+        <v>-7.530066000000001</v>
+      </c>
+      <c r="Q14">
+        <v>2.119934</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1296944343626864</v>
+      </c>
+      <c r="T14">
+        <v>1.048002612314653</v>
+      </c>
+      <c r="U14">
+        <v>0.2388</v>
+      </c>
+      <c r="V14">
+        <v>-0.774461978508527</v>
+      </c>
+      <c r="W14">
+        <v>0.4237415204678363</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>-3.097847914034109</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1669800846953044</v>
+      </c>
+      <c r="C15">
+        <v>39.16182718862068</v>
+      </c>
+      <c r="D15">
+        <v>41.66682718862069</v>
+      </c>
+      <c r="E15">
+        <v>-34.685</v>
+      </c>
+      <c r="F15">
+        <v>11.115</v>
+      </c>
+      <c r="G15">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H15">
+        <v>39.7</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>2.06</v>
+      </c>
+      <c r="K15">
+        <v>9.65</v>
+      </c>
+      <c r="L15">
+        <v>-7.59</v>
+      </c>
+      <c r="M15">
+        <v>2.654262</v>
+      </c>
+      <c r="N15">
+        <v>-10.244262</v>
+      </c>
+      <c r="O15">
+        <v>-2.5610655</v>
+      </c>
+      <c r="P15">
+        <v>-7.683196499999999</v>
+      </c>
+      <c r="Q15">
+        <v>1.966803500000001</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1307391979760507</v>
+      </c>
+      <c r="T15">
+        <v>1.060048619352753</v>
+      </c>
+      <c r="U15">
+        <v>0.2388</v>
+      </c>
+      <c r="V15">
+        <v>-0.7148879801617172</v>
+      </c>
+      <c r="W15">
+        <v>0.4095152496626181</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>-2.859551920646869</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1689800846953044</v>
+      </c>
+      <c r="C16">
+        <v>37.66668584463331</v>
+      </c>
+      <c r="D16">
+        <v>41.02668584463331</v>
+      </c>
+      <c r="E16">
+        <v>-33.83</v>
+      </c>
+      <c r="F16">
+        <v>11.97</v>
+      </c>
+      <c r="G16">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H16">
+        <v>39.7</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>2.06</v>
+      </c>
+      <c r="K16">
+        <v>9.65</v>
+      </c>
+      <c r="L16">
+        <v>-7.59</v>
+      </c>
+      <c r="M16">
+        <v>2.858436</v>
+      </c>
+      <c r="N16">
+        <v>-10.448436</v>
+      </c>
+      <c r="O16">
+        <v>-2.612109</v>
+      </c>
+      <c r="P16">
+        <v>-7.836327000000001</v>
+      </c>
+      <c r="Q16">
+        <v>1.813673</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1318082584176326</v>
+      </c>
+      <c r="T16">
+        <v>1.072374766089413</v>
+      </c>
+      <c r="U16">
+        <v>0.2388</v>
+      </c>
+      <c r="V16">
+        <v>-0.6638245530073088</v>
+      </c>
+      <c r="W16">
+        <v>0.3973213032581454</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>-2.655298212029236</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1709800846953044</v>
+      </c>
+      <c r="C17">
+        <v>36.1909162946787</v>
+      </c>
+      <c r="D17">
+        <v>40.4059162946787</v>
+      </c>
+      <c r="E17">
+        <v>-32.97499999999999</v>
+      </c>
+      <c r="F17">
+        <v>12.825</v>
+      </c>
+      <c r="G17">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H17">
+        <v>39.7</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>2.06</v>
+      </c>
+      <c r="K17">
+        <v>9.65</v>
+      </c>
+      <c r="L17">
+        <v>-7.59</v>
+      </c>
+      <c r="M17">
+        <v>3.06261</v>
+      </c>
+      <c r="N17">
+        <v>-10.65261</v>
+      </c>
+      <c r="O17">
+        <v>-2.6631525</v>
+      </c>
+      <c r="P17">
+        <v>-7.989457499999999</v>
+      </c>
+      <c r="Q17">
+        <v>1.660542500000001</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1329024732225459</v>
+      </c>
+      <c r="T17">
+        <v>1.084990939808111</v>
+      </c>
+      <c r="U17">
+        <v>0.2388</v>
+      </c>
+      <c r="V17">
+        <v>-0.6195695828068216</v>
+      </c>
+      <c r="W17">
+        <v>0.3867532163742691</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>-2.478278331227286</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1729800846953044</v>
+      </c>
+      <c r="C18">
+        <v>34.73365230913371</v>
+      </c>
+      <c r="D18">
+        <v>39.80365230913371</v>
+      </c>
+      <c r="E18">
+        <v>-32.12</v>
+      </c>
+      <c r="F18">
+        <v>13.68</v>
+      </c>
+      <c r="G18">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H18">
+        <v>39.7</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>2.06</v>
+      </c>
+      <c r="K18">
+        <v>9.65</v>
+      </c>
+      <c r="L18">
+        <v>-7.59</v>
+      </c>
+      <c r="M18">
+        <v>3.266784</v>
+      </c>
+      <c r="N18">
+        <v>-10.856784</v>
+      </c>
+      <c r="O18">
+        <v>-2.714196</v>
+      </c>
+      <c r="P18">
+        <v>-8.142588</v>
+      </c>
+      <c r="Q18">
+        <v>1.507412</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1340227407609096</v>
+      </c>
+      <c r="T18">
+        <v>1.097907498615351</v>
+      </c>
+      <c r="U18">
+        <v>0.2388</v>
+      </c>
+      <c r="V18">
+        <v>-0.5808464838813953</v>
+      </c>
+      <c r="W18">
+        <v>0.3775061403508772</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>-2.323385935525581</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1749800846953044</v>
+      </c>
+      <c r="C19">
+        <v>33.29407854567642</v>
+      </c>
+      <c r="D19">
+        <v>39.21907854567642</v>
+      </c>
+      <c r="E19">
+        <v>-31.26499999999999</v>
+      </c>
+      <c r="F19">
+        <v>14.535</v>
+      </c>
+      <c r="G19">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H19">
+        <v>39.7</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>2.06</v>
+      </c>
+      <c r="K19">
+        <v>9.65</v>
+      </c>
+      <c r="L19">
+        <v>-7.59</v>
+      </c>
+      <c r="M19">
+        <v>3.470958</v>
+      </c>
+      <c r="N19">
+        <v>-11.060958</v>
+      </c>
+      <c r="O19">
+        <v>-2.7652395</v>
+      </c>
+      <c r="P19">
+        <v>-8.2957185</v>
+      </c>
+      <c r="Q19">
+        <v>1.354281500000001</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.135170002697788</v>
+      </c>
+      <c r="T19">
+        <v>1.111135299803488</v>
+      </c>
+      <c r="U19">
+        <v>0.2388</v>
+      </c>
+      <c r="V19">
+        <v>-0.5466790436530778</v>
+      </c>
+      <c r="W19">
+        <v>0.369346955624355</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>-2.186716174612311</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1769800846953044</v>
+      </c>
+      <c r="C20">
+        <v>31.87142686660621</v>
+      </c>
+      <c r="D20">
+        <v>38.65142686660622</v>
+      </c>
+      <c r="E20">
+        <v>-30.41</v>
+      </c>
+      <c r="F20">
+        <v>15.39</v>
+      </c>
+      <c r="G20">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H20">
+        <v>39.7</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>2.06</v>
+      </c>
+      <c r="K20">
+        <v>9.65</v>
+      </c>
+      <c r="L20">
+        <v>-7.59</v>
+      </c>
+      <c r="M20">
+        <v>3.675132</v>
+      </c>
+      <c r="N20">
+        <v>-11.265132</v>
+      </c>
+      <c r="O20">
+        <v>-2.816283</v>
+      </c>
+      <c r="P20">
+        <v>-8.448848999999999</v>
+      </c>
+      <c r="Q20">
+        <v>1.201151000000001</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1363452466331269</v>
+      </c>
+      <c r="T20">
+        <v>1.124685730288896</v>
+      </c>
+      <c r="U20">
+        <v>0.2388</v>
+      </c>
+      <c r="V20">
+        <v>-0.5163079856723514</v>
+      </c>
+      <c r="W20">
+        <v>0.3620943469785575</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>-2.065231942689405</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1789800846953045</v>
+      </c>
+      <c r="C21">
+        <v>30.46497297141676</v>
+      </c>
+      <c r="D21">
+        <v>38.09997297141676</v>
+      </c>
+      <c r="E21">
+        <v>-29.555</v>
+      </c>
+      <c r="F21">
+        <v>16.245</v>
+      </c>
+      <c r="G21">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H21">
+        <v>39.7</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>2.06</v>
+      </c>
+      <c r="K21">
+        <v>9.65</v>
+      </c>
+      <c r="L21">
+        <v>-7.59</v>
+      </c>
+      <c r="M21">
+        <v>3.879306000000001</v>
+      </c>
+      <c r="N21">
+        <v>-11.469306</v>
+      </c>
+      <c r="O21">
+        <v>-2.8673265</v>
+      </c>
+      <c r="P21">
+        <v>-8.601979499999999</v>
+      </c>
+      <c r="Q21">
+        <v>1.048020500000002</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1375495089372396</v>
+      </c>
+      <c r="T21">
+        <v>1.138570739304808</v>
+      </c>
+      <c r="U21">
+        <v>0.2388</v>
+      </c>
+      <c r="V21">
+        <v>-0.4891338811632802</v>
+      </c>
+      <c r="W21">
+        <v>0.3556051708217913</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>-1.95653552465312</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1809800846953044</v>
+      </c>
+      <c r="C22">
+        <v>29.0740333135798</v>
+      </c>
+      <c r="D22">
+        <v>37.56403331357981</v>
+      </c>
+      <c r="E22">
+        <v>-28.7</v>
+      </c>
+      <c r="F22">
+        <v>17.1</v>
+      </c>
+      <c r="G22">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H22">
+        <v>39.7</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>2.06</v>
+      </c>
+      <c r="K22">
+        <v>9.65</v>
+      </c>
+      <c r="L22">
+        <v>-7.59</v>
+      </c>
+      <c r="M22">
+        <v>4.083480000000001</v>
+      </c>
+      <c r="N22">
+        <v>-11.67348</v>
+      </c>
+      <c r="O22">
+        <v>-2.91837</v>
+      </c>
+      <c r="P22">
+        <v>-8.755110000000002</v>
+      </c>
+      <c r="Q22">
+        <v>0.8948899999999984</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1387838777989551</v>
+      </c>
+      <c r="T22">
+        <v>1.152802873546118</v>
+      </c>
+      <c r="U22">
+        <v>0.2388</v>
+      </c>
+      <c r="V22">
+        <v>-0.4646771871051161</v>
+      </c>
+      <c r="W22">
+        <v>0.3497649122807017</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>-1.858708748420465</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1829800846953044</v>
+      </c>
+      <c r="C23">
+        <v>27.69796227394261</v>
+      </c>
+      <c r="D23">
+        <v>37.04296227394261</v>
+      </c>
+      <c r="E23">
+        <v>-27.845</v>
+      </c>
+      <c r="F23">
+        <v>17.955</v>
+      </c>
+      <c r="G23">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H23">
+        <v>39.7</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>2.06</v>
+      </c>
+      <c r="K23">
+        <v>9.65</v>
+      </c>
+      <c r="L23">
+        <v>-7.59</v>
+      </c>
+      <c r="M23">
+        <v>4.287654</v>
+      </c>
+      <c r="N23">
+        <v>-11.877654</v>
+      </c>
+      <c r="O23">
+        <v>-2.9694135</v>
+      </c>
+      <c r="P23">
+        <v>-8.9082405</v>
+      </c>
+      <c r="Q23">
+        <v>0.7417595000000006</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.140049496505271</v>
+      </c>
+      <c r="T23">
+        <v>1.167395314983411</v>
+      </c>
+      <c r="U23">
+        <v>0.2388</v>
+      </c>
+      <c r="V23">
+        <v>-0.4425497020048726</v>
+      </c>
+      <c r="W23">
+        <v>0.3444808688387636</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>-1.770198808019491</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1849800846953044</v>
+      </c>
+      <c r="C24">
+        <v>26.33614956616296</v>
+      </c>
+      <c r="D24">
+        <v>36.53614956616296</v>
+      </c>
+      <c r="E24">
+        <v>-26.99</v>
+      </c>
+      <c r="F24">
+        <v>18.81</v>
+      </c>
+      <c r="G24">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H24">
+        <v>39.7</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>2.06</v>
+      </c>
+      <c r="K24">
+        <v>9.65</v>
+      </c>
+      <c r="L24">
+        <v>-7.59</v>
+      </c>
+      <c r="M24">
+        <v>4.491828</v>
+      </c>
+      <c r="N24">
+        <v>-12.081828</v>
+      </c>
+      <c r="O24">
+        <v>-3.020457</v>
+      </c>
+      <c r="P24">
+        <v>-9.061370999999999</v>
+      </c>
+      <c r="Q24">
+        <v>0.588629000000001</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1413475669732873</v>
+      </c>
+      <c r="T24">
+        <v>1.182361921585762</v>
+      </c>
+      <c r="U24">
+        <v>0.2388</v>
+      </c>
+      <c r="V24">
+        <v>-0.4224338064591966</v>
+      </c>
+      <c r="W24">
+        <v>0.3396771929824562</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>-1.689735225836786</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1869800846953044</v>
+      </c>
+      <c r="C25">
+        <v>24.98801785225835</v>
+      </c>
+      <c r="D25">
+        <v>36.04301785225835</v>
+      </c>
+      <c r="E25">
+        <v>-26.135</v>
+      </c>
+      <c r="F25">
+        <v>19.665</v>
+      </c>
+      <c r="G25">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H25">
+        <v>39.7</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>2.06</v>
+      </c>
+      <c r="K25">
+        <v>9.65</v>
+      </c>
+      <c r="L25">
+        <v>-7.59</v>
+      </c>
+      <c r="M25">
+        <v>4.696002</v>
+      </c>
+      <c r="N25">
+        <v>-12.286002</v>
+      </c>
+      <c r="O25">
+        <v>-3.0715005</v>
+      </c>
+      <c r="P25">
+        <v>-9.214501500000001</v>
+      </c>
+      <c r="Q25">
+        <v>0.4354984999999996</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1426793535573559</v>
+      </c>
+      <c r="T25">
+        <v>1.197717271216746</v>
+      </c>
+      <c r="U25">
+        <v>0.2388</v>
+      </c>
+      <c r="V25">
+        <v>-0.4040671192218402</v>
+      </c>
+      <c r="W25">
+        <v>0.3352912280701754</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>-1.616268476887361</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1889800846953044</v>
+      </c>
+      <c r="C26">
+        <v>23.65302054868265</v>
+      </c>
+      <c r="D26">
+        <v>35.56302054868265</v>
+      </c>
+      <c r="E26">
+        <v>-25.28</v>
+      </c>
+      <c r="F26">
+        <v>20.52</v>
+      </c>
+      <c r="G26">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H26">
+        <v>39.7</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>2.06</v>
+      </c>
+      <c r="K26">
+        <v>9.65</v>
+      </c>
+      <c r="L26">
+        <v>-7.59</v>
+      </c>
+      <c r="M26">
+        <v>4.900176</v>
+      </c>
+      <c r="N26">
+        <v>-12.490176</v>
+      </c>
+      <c r="O26">
+        <v>-3.122544</v>
+      </c>
+      <c r="P26">
+        <v>-9.367632</v>
+      </c>
+      <c r="Q26">
+        <v>0.282368</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1440461871567948</v>
+      </c>
+      <c r="T26">
+        <v>1.213476708995914</v>
+      </c>
+      <c r="U26">
+        <v>0.2388</v>
+      </c>
+      <c r="V26">
+        <v>-0.3872309892542635</v>
+      </c>
+      <c r="W26">
+        <v>0.3312707602339182</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>-1.548923957017054</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1909800846953044</v>
+      </c>
+      <c r="C27">
+        <v>22.33063980540225</v>
+      </c>
+      <c r="D27">
+        <v>35.09563980540225</v>
+      </c>
+      <c r="E27">
+        <v>-24.425</v>
+      </c>
+      <c r="F27">
+        <v>21.375</v>
+      </c>
+      <c r="G27">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H27">
+        <v>39.7</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>2.06</v>
+      </c>
+      <c r="K27">
+        <v>9.65</v>
+      </c>
+      <c r="L27">
+        <v>-7.59</v>
+      </c>
+      <c r="M27">
+        <v>5.10435</v>
+      </c>
+      <c r="N27">
+        <v>-12.69435</v>
+      </c>
+      <c r="O27">
+        <v>-3.1735875</v>
+      </c>
+      <c r="P27">
+        <v>-9.5207625</v>
+      </c>
+      <c r="Q27">
+        <v>0.1292375000000003</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1454494696522188</v>
+      </c>
+      <c r="T27">
+        <v>1.229656398449193</v>
+      </c>
+      <c r="U27">
+        <v>0.2388</v>
+      </c>
+      <c r="V27">
+        <v>-0.371741749684093</v>
+      </c>
+      <c r="W27">
+        <v>0.3275719298245614</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>-1.486966998736372</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1929800846953044</v>
+      </c>
+      <c r="C28">
+        <v>21.02038464226287</v>
+      </c>
+      <c r="D28">
+        <v>34.64038464226287</v>
+      </c>
+      <c r="E28">
+        <v>-23.57</v>
+      </c>
+      <c r="F28">
+        <v>22.23</v>
+      </c>
+      <c r="G28">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H28">
+        <v>39.7</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>2.06</v>
+      </c>
+      <c r="K28">
+        <v>9.65</v>
+      </c>
+      <c r="L28">
+        <v>-7.59</v>
+      </c>
+      <c r="M28">
+        <v>5.308524</v>
+      </c>
+      <c r="N28">
+        <v>-12.898524</v>
+      </c>
+      <c r="O28">
+        <v>-3.224631</v>
+      </c>
+      <c r="P28">
+        <v>-9.673893</v>
+      </c>
+      <c r="Q28">
+        <v>-0.02389299999999928</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1468906787015731</v>
+      </c>
+      <c r="T28">
+        <v>1.246273376806615</v>
+      </c>
+      <c r="U28">
+        <v>0.2388</v>
+      </c>
+      <c r="V28">
+        <v>-0.3574439900808586</v>
+      </c>
+      <c r="W28">
+        <v>0.3241576248313091</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>-1.429775960323434</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1949800846953044</v>
+      </c>
+      <c r="C29">
+        <v>19.72178922854744</v>
+      </c>
+      <c r="D29">
+        <v>34.19678922854744</v>
+      </c>
+      <c r="E29">
+        <v>-22.715</v>
+      </c>
+      <c r="F29">
+        <v>23.085</v>
+      </c>
+      <c r="G29">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H29">
+        <v>39.7</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>2.06</v>
+      </c>
+      <c r="K29">
+        <v>9.65</v>
+      </c>
+      <c r="L29">
+        <v>-7.59</v>
+      </c>
+      <c r="M29">
+        <v>5.512698</v>
+      </c>
+      <c r="N29">
+        <v>-13.102698</v>
+      </c>
+      <c r="O29">
+        <v>-3.2756745</v>
+      </c>
+      <c r="P29">
+        <v>-9.827023499999999</v>
+      </c>
+      <c r="Q29">
+        <v>-0.1770234999999989</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1483713729303617</v>
+      </c>
+      <c r="T29">
+        <v>1.263345614845061</v>
+      </c>
+      <c r="U29">
+        <v>0.2388</v>
+      </c>
+      <c r="V29">
+        <v>-0.3442053237815675</v>
+      </c>
+      <c r="W29">
+        <v>0.3209962313190383</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>-1.37682129512627</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1969800846953045</v>
+      </c>
+      <c r="C30">
+        <v>18.4344112930517</v>
+      </c>
+      <c r="D30">
+        <v>33.7644112930517</v>
+      </c>
+      <c r="E30">
+        <v>-21.86</v>
+      </c>
+      <c r="F30">
+        <v>23.94</v>
+      </c>
+      <c r="G30">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H30">
+        <v>39.7</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>2.06</v>
+      </c>
+      <c r="K30">
+        <v>9.65</v>
+      </c>
+      <c r="L30">
+        <v>-7.59</v>
+      </c>
+      <c r="M30">
+        <v>5.716872</v>
+      </c>
+      <c r="N30">
+        <v>-13.306872</v>
+      </c>
+      <c r="O30">
+        <v>-3.326718</v>
+      </c>
+      <c r="P30">
+        <v>-9.980154000000001</v>
+      </c>
+      <c r="Q30">
+        <v>-0.3301540000000003</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1498931975543946</v>
+      </c>
+      <c r="T30">
+        <v>1.280892081717909</v>
+      </c>
+      <c r="U30">
+        <v>0.2388</v>
+      </c>
+      <c r="V30">
+        <v>-0.3319122765036544</v>
+      </c>
+      <c r="W30">
+        <v>0.3180606516290727</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>-1.327649106014618</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1989800846953044</v>
+      </c>
+      <c r="C31">
+        <v>17.1578306532702</v>
+      </c>
+      <c r="D31">
+        <v>33.3428306532702</v>
+      </c>
+      <c r="E31">
+        <v>-21.005</v>
+      </c>
+      <c r="F31">
+        <v>24.795</v>
+      </c>
+      <c r="G31">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H31">
+        <v>39.7</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>2.06</v>
+      </c>
+      <c r="K31">
+        <v>9.65</v>
+      </c>
+      <c r="L31">
+        <v>-7.59</v>
+      </c>
+      <c r="M31">
+        <v>5.921046</v>
+      </c>
+      <c r="N31">
+        <v>-13.511046</v>
+      </c>
+      <c r="O31">
+        <v>-3.3777615</v>
+      </c>
+      <c r="P31">
+        <v>-10.1332845</v>
+      </c>
+      <c r="Q31">
+        <v>-0.4832844999999999</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1514578904776959</v>
+      </c>
+      <c r="T31">
+        <v>1.298932815263232</v>
+      </c>
+      <c r="U31">
+        <v>0.2388</v>
+      </c>
+      <c r="V31">
+        <v>-0.3204670255897353</v>
+      </c>
+      <c r="W31">
+        <v>0.3153275257108288</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>-1.281868102358942</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.2009800846953044</v>
+      </c>
+      <c r="C32">
+        <v>15.89164785341023</v>
+      </c>
+      <c r="D32">
+        <v>32.93164785341023</v>
+      </c>
+      <c r="E32">
+        <v>-20.15</v>
+      </c>
+      <c r="F32">
+        <v>25.65</v>
+      </c>
+      <c r="G32">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H32">
+        <v>39.7</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>2.06</v>
+      </c>
+      <c r="K32">
+        <v>9.65</v>
+      </c>
+      <c r="L32">
+        <v>-7.59</v>
+      </c>
+      <c r="M32">
+        <v>6.12522</v>
+      </c>
+      <c r="N32">
+        <v>-13.71522</v>
+      </c>
+      <c r="O32">
+        <v>-3.428805</v>
+      </c>
+      <c r="P32">
+        <v>-10.286415</v>
+      </c>
+      <c r="Q32">
+        <v>-0.6364149999999977</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1530672889130915</v>
+      </c>
+      <c r="T32">
+        <v>1.317488998338421</v>
+      </c>
+      <c r="U32">
+        <v>0.2388</v>
+      </c>
+      <c r="V32">
+        <v>-0.3097847914034108</v>
+      </c>
+      <c r="W32">
+        <v>0.3127766081871345</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>-1.239139165613643</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.2029800846953044</v>
+      </c>
+      <c r="C33">
+        <v>14.63548290195432</v>
+      </c>
+      <c r="D33">
+        <v>32.53048290195431</v>
+      </c>
+      <c r="E33">
+        <v>-19.295</v>
+      </c>
+      <c r="F33">
+        <v>26.505</v>
+      </c>
+      <c r="G33">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H33">
+        <v>39.7</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>2.06</v>
+      </c>
+      <c r="K33">
+        <v>9.65</v>
+      </c>
+      <c r="L33">
+        <v>-7.59</v>
+      </c>
+      <c r="M33">
+        <v>6.329394</v>
+      </c>
+      <c r="N33">
+        <v>-13.919394</v>
+      </c>
+      <c r="O33">
+        <v>-3.4798485</v>
+      </c>
+      <c r="P33">
+        <v>-10.4395455</v>
+      </c>
+      <c r="Q33">
+        <v>-0.7895455000000009</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1547233365784987</v>
+      </c>
+      <c r="T33">
+        <v>1.336583041792601</v>
+      </c>
+      <c r="U33">
+        <v>0.2388</v>
+      </c>
+      <c r="V33">
+        <v>-0.299791733616204</v>
+      </c>
+      <c r="W33">
+        <v>0.3103902659875495</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>-1.199166934464816</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.2049800846953044</v>
+      </c>
+      <c r="C34">
+        <v>13.38897410038403</v>
+      </c>
+      <c r="D34">
+        <v>32.13897410038403</v>
+      </c>
+      <c r="E34">
+        <v>-18.44</v>
+      </c>
+      <c r="F34">
+        <v>27.36</v>
+      </c>
+      <c r="G34">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H34">
+        <v>39.7</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>2.06</v>
+      </c>
+      <c r="K34">
+        <v>9.65</v>
+      </c>
+      <c r="L34">
+        <v>-7.59</v>
+      </c>
+      <c r="M34">
+        <v>6.533568</v>
+      </c>
+      <c r="N34">
+        <v>-14.123568</v>
+      </c>
+      <c r="O34">
+        <v>-3.530892</v>
+      </c>
+      <c r="P34">
+        <v>-10.592676</v>
+      </c>
+      <c r="Q34">
+        <v>-0.9426759999999987</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1564280915281824</v>
+      </c>
+      <c r="T34">
+        <v>1.356238674760139</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>-0.2904232419406976</v>
+      </c>
+      <c r="W34">
+        <v>0.3081530701754386</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>-1.16169296776279</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.2069800846953044</v>
+      </c>
+      <c r="C35">
+        <v>12.15177695547699</v>
+      </c>
+      <c r="D35">
+        <v>31.75677695547699</v>
+      </c>
+      <c r="E35">
+        <v>-17.585</v>
+      </c>
+      <c r="F35">
+        <v>28.215</v>
+      </c>
+      <c r="G35">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H35">
+        <v>39.7</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>2.06</v>
+      </c>
+      <c r="K35">
+        <v>9.65</v>
+      </c>
+      <c r="L35">
+        <v>-7.59</v>
+      </c>
+      <c r="M35">
+        <v>6.737742</v>
+      </c>
+      <c r="N35">
+        <v>-14.327742</v>
+      </c>
+      <c r="O35">
+        <v>-3.5819355</v>
+      </c>
+      <c r="P35">
+        <v>-10.7458065</v>
+      </c>
+      <c r="Q35">
+        <v>-1.0958065</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1581837346853195</v>
+      </c>
+      <c r="T35">
+        <v>1.376481043040142</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>-0.2816225376394644</v>
+      </c>
+      <c r="W35">
+        <v>0.3060514619883041</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>-1.126490150557858</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.2089800846953044</v>
+      </c>
+      <c r="C36">
+        <v>10.92356316830164</v>
+      </c>
+      <c r="D36">
+        <v>31.38356316830165</v>
+      </c>
+      <c r="E36">
+        <v>-16.72999999999999</v>
+      </c>
+      <c r="F36">
+        <v>29.07</v>
+      </c>
+      <c r="G36">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H36">
+        <v>39.7</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>2.06</v>
+      </c>
+      <c r="K36">
+        <v>9.65</v>
+      </c>
+      <c r="L36">
+        <v>-7.59</v>
+      </c>
+      <c r="M36">
+        <v>6.941916000000001</v>
+      </c>
+      <c r="N36">
+        <v>-14.531916</v>
+      </c>
+      <c r="O36">
+        <v>-3.632979</v>
+      </c>
+      <c r="P36">
+        <v>-10.898937</v>
+      </c>
+      <c r="Q36">
+        <v>-1.248937</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1599925791502486</v>
+      </c>
+      <c r="T36">
+        <v>1.397336816419538</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>-0.2733395218265389</v>
+      </c>
+      <c r="W36">
+        <v>0.3040734778121775</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>-1.093358087306155</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.2109800846953044</v>
+      </c>
+      <c r="C37">
+        <v>9.704019693673452</v>
+      </c>
+      <c r="D37">
+        <v>31.01901969367346</v>
+      </c>
+      <c r="E37">
+        <v>-15.87499999999999</v>
+      </c>
+      <c r="F37">
+        <v>29.925</v>
+      </c>
+      <c r="G37">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H37">
+        <v>39.7</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>2.06</v>
+      </c>
+      <c r="K37">
+        <v>9.65</v>
+      </c>
+      <c r="L37">
+        <v>-7.59</v>
+      </c>
+      <c r="M37">
+        <v>7.146090000000001</v>
+      </c>
+      <c r="N37">
+        <v>-14.73609</v>
+      </c>
+      <c r="O37">
+        <v>-3.6840225</v>
+      </c>
+      <c r="P37">
+        <v>-11.0520675</v>
+      </c>
+      <c r="Q37">
+        <v>-1.402067499999999</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1618570803679447</v>
+      </c>
+      <c r="T37">
+        <v>1.418834305902915</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>-0.2655298212029235</v>
+      </c>
+      <c r="W37">
+        <v>0.3022085213032581</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>-1.062119284811694</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.2129800846953044</v>
+      </c>
+      <c r="C38">
+        <v>8.492847864409111</v>
+      </c>
+      <c r="D38">
+        <v>30.66284786440911</v>
+      </c>
+      <c r="E38">
+        <v>-15.02</v>
+      </c>
+      <c r="F38">
+        <v>30.78</v>
+      </c>
+      <c r="G38">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H38">
+        <v>39.7</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>2.06</v>
+      </c>
+      <c r="K38">
+        <v>9.65</v>
+      </c>
+      <c r="L38">
+        <v>-7.59</v>
+      </c>
+      <c r="M38">
+        <v>7.350264</v>
+      </c>
+      <c r="N38">
+        <v>-14.940264</v>
+      </c>
+      <c r="O38">
+        <v>-3.735066</v>
+      </c>
+      <c r="P38">
+        <v>-11.205198</v>
+      </c>
+      <c r="Q38">
+        <v>-1.555197999999999</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1637798472486938</v>
+      </c>
+      <c r="T38">
+        <v>1.441003591932648</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>-0.2581539928361757</v>
+      </c>
+      <c r="W38">
+        <v>0.3004471734892787</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>-1.032615971344703</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.2149800846953044</v>
+      </c>
+      <c r="C39">
+        <v>7.289762575229695</v>
+      </c>
+      <c r="D39">
+        <v>30.31476257522969</v>
+      </c>
+      <c r="E39">
+        <v>-14.165</v>
+      </c>
+      <c r="F39">
+        <v>31.635</v>
+      </c>
+      <c r="G39">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H39">
+        <v>39.7</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>2.06</v>
+      </c>
+      <c r="K39">
+        <v>9.65</v>
+      </c>
+      <c r="L39">
+        <v>-7.59</v>
+      </c>
+      <c r="M39">
+        <v>7.554438</v>
+      </c>
+      <c r="N39">
+        <v>-15.144438</v>
+      </c>
+      <c r="O39">
+        <v>-3.7861095</v>
+      </c>
+      <c r="P39">
+        <v>-11.3583285</v>
+      </c>
+      <c r="Q39">
+        <v>-1.7083285</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1657636543478795</v>
+      </c>
+      <c r="T39">
+        <v>1.463876664820468</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>-0.2511768578946574</v>
+      </c>
+      <c r="W39">
+        <v>0.2987810336652442</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>-1.00470743157863</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.2169800846953044</v>
+      </c>
+      <c r="C40">
+        <v>6.094491521626047</v>
+      </c>
+      <c r="D40">
+        <v>29.97449152162605</v>
+      </c>
+      <c r="E40">
+        <v>-13.31</v>
+      </c>
+      <c r="F40">
+        <v>32.49</v>
+      </c>
+      <c r="G40">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H40">
+        <v>39.7</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>2.06</v>
+      </c>
+      <c r="K40">
+        <v>9.65</v>
+      </c>
+      <c r="L40">
+        <v>-7.59</v>
+      </c>
+      <c r="M40">
+        <v>7.758612000000001</v>
+      </c>
+      <c r="N40">
+        <v>-15.348612</v>
+      </c>
+      <c r="O40">
+        <v>-3.837153</v>
+      </c>
+      <c r="P40">
+        <v>-11.511459</v>
+      </c>
+      <c r="Q40">
+        <v>-1.861459</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1678114552244582</v>
+      </c>
+      <c r="T40">
+        <v>1.487487578769185</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>-0.2445669405816401</v>
+      </c>
+      <c r="W40">
+        <v>0.2972025854108956</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>-0.9782677623265603</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.2189800846953044</v>
+      </c>
+      <c r="C41">
+        <v>4.906774489415568</v>
+      </c>
+      <c r="D41">
+        <v>29.64177448941557</v>
+      </c>
+      <c r="E41">
+        <v>-12.455</v>
+      </c>
+      <c r="F41">
+        <v>33.345</v>
+      </c>
+      <c r="G41">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H41">
+        <v>39.7</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>2.06</v>
+      </c>
+      <c r="K41">
+        <v>9.65</v>
+      </c>
+      <c r="L41">
+        <v>-7.59</v>
+      </c>
+      <c r="M41">
+        <v>7.962786</v>
+      </c>
+      <c r="N41">
+        <v>-15.552786</v>
+      </c>
+      <c r="O41">
+        <v>-3.8881965</v>
+      </c>
+      <c r="P41">
+        <v>-11.6645895</v>
+      </c>
+      <c r="Q41">
+        <v>-2.014589500000001</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1699263971133837</v>
+      </c>
+      <c r="T41">
+        <v>1.51187262104409</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>-0.2382959933872391</v>
+      </c>
+      <c r="W41">
+        <v>0.2957050832208727</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>-0.9531839735489565</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.2209800846953044</v>
+      </c>
+      <c r="C42">
+        <v>3.726362691095332</v>
+      </c>
+      <c r="D42">
+        <v>29.31636269109534</v>
+      </c>
+      <c r="E42">
+        <v>-11.59999999999999</v>
+      </c>
+      <c r="F42">
+        <v>34.2</v>
+      </c>
+      <c r="G42">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H42">
+        <v>39.7</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>2.06</v>
+      </c>
+      <c r="K42">
+        <v>9.65</v>
+      </c>
+      <c r="L42">
+        <v>-7.59</v>
+      </c>
+      <c r="M42">
+        <v>8.166960000000001</v>
+      </c>
+      <c r="N42">
+        <v>-15.75696</v>
+      </c>
+      <c r="O42">
+        <v>-3.93924</v>
+      </c>
+      <c r="P42">
+        <v>-11.81772</v>
+      </c>
+      <c r="Q42">
+        <v>-2.167720000000001</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1721118370652734</v>
+      </c>
+      <c r="T42">
+        <v>1.537070498061491</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>-0.2323385935525581</v>
+      </c>
+      <c r="W42">
+        <v>0.2942824561403509</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>-0.9293543742102324</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.2229800846953044</v>
+      </c>
+      <c r="C43">
+        <v>2.553018145434017</v>
+      </c>
+      <c r="D43">
+        <v>28.99801814543402</v>
+      </c>
+      <c r="E43">
+        <v>-10.745</v>
+      </c>
+      <c r="F43">
+        <v>35.055</v>
+      </c>
+      <c r="G43">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H43">
+        <v>39.7</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>2.06</v>
+      </c>
+      <c r="K43">
+        <v>9.65</v>
+      </c>
+      <c r="L43">
+        <v>-7.59</v>
+      </c>
+      <c r="M43">
+        <v>8.371134</v>
+      </c>
+      <c r="N43">
+        <v>-15.961134</v>
+      </c>
+      <c r="O43">
+        <v>-3.9902835</v>
+      </c>
+      <c r="P43">
+        <v>-11.9708505</v>
+      </c>
+      <c r="Q43">
+        <v>-2.320850499999999</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1743713597273967</v>
+      </c>
+      <c r="T43">
+        <v>1.563122540401517</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>-0.2266717985878616</v>
+      </c>
+      <c r="W43">
+        <v>0.2929292255027814</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>-0.9066871943514463</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.2249800846953044</v>
+      </c>
+      <c r="C44">
+        <v>1.38651309705152</v>
+      </c>
+      <c r="D44">
+        <v>28.68651309705152</v>
+      </c>
+      <c r="E44">
+        <v>-9.890000000000001</v>
+      </c>
+      <c r="F44">
+        <v>35.91</v>
+      </c>
+      <c r="G44">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H44">
+        <v>39.7</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>2.06</v>
+      </c>
+      <c r="K44">
+        <v>9.65</v>
+      </c>
+      <c r="L44">
+        <v>-7.59</v>
+      </c>
+      <c r="M44">
+        <v>8.575308</v>
+      </c>
+      <c r="N44">
+        <v>-16.165308</v>
+      </c>
+      <c r="O44">
+        <v>-4.041327</v>
+      </c>
+      <c r="P44">
+        <v>-12.123981</v>
+      </c>
+      <c r="Q44">
+        <v>-2.473981</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.176708796964076</v>
+      </c>
+      <c r="T44">
+        <v>1.590072929029129</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>-0.2212748510024363</v>
+      </c>
+      <c r="W44">
+        <v>0.2916404344193818</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>-0.8850994040097453</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.2269800846953044</v>
+      </c>
+      <c r="C45">
+        <v>0.2266294730112861</v>
+      </c>
+      <c r="D45">
+        <v>28.38162947301129</v>
+      </c>
+      <c r="E45">
+        <v>-9.034999999999997</v>
+      </c>
+      <c r="F45">
+        <v>36.765</v>
+      </c>
+      <c r="G45">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H45">
+        <v>39.7</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>2.06</v>
+      </c>
+      <c r="K45">
+        <v>9.65</v>
+      </c>
+      <c r="L45">
+        <v>-7.59</v>
+      </c>
+      <c r="M45">
+        <v>8.779482</v>
+      </c>
+      <c r="N45">
+        <v>-16.369482</v>
+      </c>
+      <c r="O45">
+        <v>-4.092370499999999</v>
+      </c>
+      <c r="P45">
+        <v>-12.2771115</v>
+      </c>
+      <c r="Q45">
+        <v>-2.627111499999998</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1791282495423931</v>
+      </c>
+      <c r="T45">
+        <v>1.617968945327885</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>-0.2161289242349378</v>
+      </c>
+      <c r="W45">
+        <v>0.2904115871073031</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>-0.8645156969397509</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.2289800846953044</v>
+      </c>
+      <c r="C46">
+        <v>-0.9268416262994776</v>
+      </c>
+      <c r="D46">
+        <v>28.08315837370052</v>
+      </c>
+      <c r="E46">
+        <v>-8.18</v>
+      </c>
+      <c r="F46">
+        <v>37.62</v>
+      </c>
+      <c r="G46">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H46">
+        <v>39.7</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>2.06</v>
+      </c>
+      <c r="K46">
+        <v>9.65</v>
+      </c>
+      <c r="L46">
+        <v>-7.59</v>
+      </c>
+      <c r="M46">
+        <v>8.983656</v>
+      </c>
+      <c r="N46">
+        <v>-16.573656</v>
+      </c>
+      <c r="O46">
+        <v>-4.143414</v>
+      </c>
+      <c r="P46">
+        <v>-12.430242</v>
+      </c>
+      <c r="Q46">
+        <v>-2.780241999999999</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1816341111413644</v>
+      </c>
+      <c r="T46">
+        <v>1.646861247923026</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>-0.2112169032295983</v>
+      </c>
+      <c r="W46">
+        <v>0.2892385964912281</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>-0.8448676129183932</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.2309800846953044</v>
+      </c>
+      <c r="C47">
+        <v>-2.074100404499376</v>
+      </c>
+      <c r="D47">
+        <v>27.79089959550063</v>
+      </c>
+      <c r="E47">
+        <v>-7.324999999999996</v>
+      </c>
+      <c r="F47">
+        <v>38.475</v>
+      </c>
+      <c r="G47">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H47">
+        <v>39.7</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>2.06</v>
+      </c>
+      <c r="K47">
+        <v>9.65</v>
+      </c>
+      <c r="L47">
+        <v>-7.59</v>
+      </c>
+      <c r="M47">
+        <v>9.18783</v>
+      </c>
+      <c r="N47">
+        <v>-16.77783</v>
+      </c>
+      <c r="O47">
+        <v>-4.1944575</v>
+      </c>
+      <c r="P47">
+        <v>-12.5833725</v>
+      </c>
+      <c r="Q47">
+        <v>-2.933372500000001</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1842310949802983</v>
+      </c>
+      <c r="T47">
+        <v>1.676804179703445</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>-0.2065231942689405</v>
+      </c>
+      <c r="W47">
+        <v>0.288117738791423</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>-0.8260927770757625</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.2329800846953045</v>
+      </c>
+      <c r="C48">
+        <v>-3.215338817044184</v>
+      </c>
+      <c r="D48">
+        <v>27.50466118295581</v>
+      </c>
+      <c r="E48">
+        <v>-6.469999999999999</v>
+      </c>
+      <c r="F48">
+        <v>39.33</v>
+      </c>
+      <c r="G48">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H48">
+        <v>39.7</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>2.06</v>
+      </c>
+      <c r="K48">
+        <v>9.65</v>
+      </c>
+      <c r="L48">
+        <v>-7.59</v>
+      </c>
+      <c r="M48">
+        <v>9.392004</v>
+      </c>
+      <c r="N48">
+        <v>-16.982004</v>
+      </c>
+      <c r="O48">
+        <v>-4.245501</v>
+      </c>
+      <c r="P48">
+        <v>-12.736503</v>
+      </c>
+      <c r="Q48">
+        <v>-3.086502999999999</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1869242634058594</v>
+      </c>
+      <c r="T48">
+        <v>1.707856108957213</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>-0.2020335596109201</v>
+      </c>
+      <c r="W48">
+        <v>0.2870456140350878</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>-0.8081342384436803</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.2349800846953045</v>
+      </c>
+      <c r="C49">
+        <v>-4.350740991665276</v>
+      </c>
+      <c r="D49">
+        <v>27.22425900833473</v>
+      </c>
+      <c r="E49">
+        <v>-5.614999999999995</v>
+      </c>
+      <c r="F49">
+        <v>40.185</v>
+      </c>
+      <c r="G49">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H49">
+        <v>39.7</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>2.06</v>
+      </c>
+      <c r="K49">
+        <v>9.65</v>
+      </c>
+      <c r="L49">
+        <v>-7.59</v>
+      </c>
+      <c r="M49">
+        <v>9.596178000000002</v>
+      </c>
+      <c r="N49">
+        <v>-17.186178</v>
+      </c>
+      <c r="O49">
+        <v>-4.2965445</v>
+      </c>
+      <c r="P49">
+        <v>-12.8896335</v>
+      </c>
+      <c r="Q49">
+        <v>-3.239633500000002</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1897190608286115</v>
+      </c>
+      <c r="T49">
+        <v>1.740079809126217</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>-0.1977349732362196</v>
+      </c>
+      <c r="W49">
+        <v>0.2860191116088093</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>-0.7909398929448785</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.2369800846953044</v>
+      </c>
+      <c r="C50">
+        <v>-5.48048362334989</v>
+      </c>
+      <c r="D50">
+        <v>26.94951637665011</v>
+      </c>
+      <c r="E50">
+        <v>-4.759999999999998</v>
+      </c>
+      <c r="F50">
+        <v>41.04</v>
+      </c>
+      <c r="G50">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H50">
+        <v>39.7</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>2.06</v>
+      </c>
+      <c r="K50">
+        <v>9.65</v>
+      </c>
+      <c r="L50">
+        <v>-7.59</v>
+      </c>
+      <c r="M50">
+        <v>9.800352</v>
+      </c>
+      <c r="N50">
+        <v>-17.390352</v>
+      </c>
+      <c r="O50">
+        <v>-4.347588</v>
+      </c>
+      <c r="P50">
+        <v>-13.042764</v>
+      </c>
+      <c r="Q50">
+        <v>-3.392764</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1926213504599309</v>
+      </c>
+      <c r="T50">
+        <v>1.773542882378644</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>-0.1936154946271318</v>
+      </c>
+      <c r="W50">
+        <v>0.2850353801169591</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>-0.7744619785085269</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.2389800846953044</v>
+      </c>
+      <c r="C51">
+        <v>-6.604736345644113</v>
+      </c>
+      <c r="D51">
+        <v>26.68026365435588</v>
+      </c>
+      <c r="E51">
+        <v>-3.905000000000001</v>
+      </c>
+      <c r="F51">
+        <v>41.895</v>
+      </c>
+      <c r="G51">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H51">
+        <v>39.7</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>2.06</v>
+      </c>
+      <c r="K51">
+        <v>9.65</v>
+      </c>
+      <c r="L51">
+        <v>-7.59</v>
+      </c>
+      <c r="M51">
+        <v>10.004526</v>
+      </c>
+      <c r="N51">
+        <v>-17.594526</v>
+      </c>
+      <c r="O51">
+        <v>-4.3986315</v>
+      </c>
+      <c r="P51">
+        <v>-13.1958945</v>
+      </c>
+      <c r="Q51">
+        <v>-3.545894500000001</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1956374553709099</v>
+      </c>
+      <c r="T51">
+        <v>1.808318233013519</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>-0.1896641580020882</v>
+      </c>
+      <c r="W51">
+        <v>0.2840918009308987</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>-0.7586566320083532</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.2409800846953044</v>
+      </c>
+      <c r="C52">
+        <v>-7.723662079917744</v>
+      </c>
+      <c r="D52">
+        <v>26.41633792008225</v>
+      </c>
+      <c r="E52">
+        <v>-3.049999999999997</v>
+      </c>
+      <c r="F52">
+        <v>42.75</v>
+      </c>
+      <c r="G52">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H52">
+        <v>39.7</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>2.06</v>
+      </c>
+      <c r="K52">
+        <v>9.65</v>
+      </c>
+      <c r="L52">
+        <v>-7.59</v>
+      </c>
+      <c r="M52">
+        <v>10.2087</v>
+      </c>
+      <c r="N52">
+        <v>-17.7987</v>
+      </c>
+      <c r="O52">
+        <v>-4.449675</v>
+      </c>
+      <c r="P52">
+        <v>-13.349025</v>
+      </c>
+      <c r="Q52">
+        <v>-3.699025000000001</v>
+      </c>
+      <c r="R52">
         <v>1</v>
       </c>
-      <c r="U4">
-        <v>11.8</v>
-      </c>
-      <c r="V4">
-        <v>0.2972292191435768</v>
-      </c>
-      <c r="W4">
-        <v>-0.596401028277635</v>
-      </c>
-      <c r="X4">
-        <v>0.1150272659581076</v>
-      </c>
-      <c r="Y4">
-        <v>-0.7114282942357426</v>
-      </c>
-      <c r="Z4">
-        <v>1.622608695652174</v>
-      </c>
-      <c r="AA4">
-        <v>-0.3234782608695653</v>
-      </c>
-      <c r="AB4">
-        <v>0.06550670136917006</v>
-      </c>
-      <c r="AC4">
-        <v>-0.3889849622387354</v>
-      </c>
-      <c r="AD4">
-        <v>52</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>52</v>
-      </c>
-      <c r="AG4">
-        <v>40.2</v>
-      </c>
-      <c r="AH4">
-        <v>0.5670665212649946</v>
-      </c>
-      <c r="AI4">
-        <v>0.7635829662261381</v>
-      </c>
-      <c r="AJ4">
-        <v>0.5031289111389237</v>
-      </c>
-      <c r="AK4">
-        <v>0.714031971580817</v>
-      </c>
-      <c r="AL4">
-        <v>1.43</v>
-      </c>
-      <c r="AM4">
-        <v>1.229</v>
-      </c>
-      <c r="AN4">
-        <v>-2.841530054644809</v>
-      </c>
-      <c r="AO4">
-        <v>-13.00699300699301</v>
-      </c>
-      <c r="AP4">
-        <v>-2.19672131147541</v>
-      </c>
-      <c r="AQ4">
-        <v>-15.13425549227014</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Nueva Expresión Textil, S.A. (BME:NXT)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Apparel</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>0.0636</v>
-      </c>
-      <c r="G5">
-        <v>-0.1555382215288612</v>
-      </c>
-      <c r="H5">
-        <v>-0.1731669266770671</v>
-      </c>
-      <c r="I5">
-        <v>-0.2106084243369735</v>
-      </c>
-      <c r="J5">
-        <v>-0.2106084243369735</v>
-      </c>
-      <c r="K5">
-        <v>-23.2</v>
-      </c>
-      <c r="L5">
-        <v>-0.3619344773790952</v>
-      </c>
-      <c r="M5">
-        <v>-0</v>
-      </c>
-      <c r="N5">
-        <v>-0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
-        <v>-0</v>
-      </c>
-      <c r="Q5">
-        <v>-0</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>8.26</v>
-      </c>
-      <c r="V5">
-        <v>0.05748086290883786</v>
-      </c>
-      <c r="W5">
-        <v>2.555066079295154</v>
-      </c>
-      <c r="X5">
-        <v>0.08266150170915877</v>
-      </c>
-      <c r="Y5">
-        <v>2.472404577585995</v>
-      </c>
-      <c r="Z5">
-        <v>1.76147293212421</v>
-      </c>
-      <c r="AA5">
-        <v>-0.3709810387469085</v>
-      </c>
-      <c r="AB5">
-        <v>0.06550730156948141</v>
-      </c>
-      <c r="AC5">
-        <v>-0.4364883403163899</v>
-      </c>
-      <c r="AD5">
-        <v>65.2</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>65.2</v>
-      </c>
-      <c r="AG5">
-        <v>56.94</v>
-      </c>
-      <c r="AH5">
-        <v>0.312111057922451</v>
-      </c>
-      <c r="AI5">
-        <v>2.006153846153846</v>
-      </c>
-      <c r="AJ5">
-        <v>0.2837918660287082</v>
-      </c>
-      <c r="AK5">
-        <v>2.349009900990099</v>
-      </c>
-      <c r="AL5">
-        <v>3.29</v>
-      </c>
-      <c r="AM5">
-        <v>3.074</v>
-      </c>
-      <c r="AN5">
-        <v>-7.244444444444444</v>
-      </c>
-      <c r="AO5">
-        <v>-4.103343465045593</v>
-      </c>
-      <c r="AP5">
-        <v>-6.326666666666667</v>
-      </c>
-      <c r="AQ5">
-        <v>-4.39167208848406</v>
+      <c r="S52">
+        <v>0.1987742044783281</v>
+      </c>
+      <c r="T52">
+        <v>1.844484597673789</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>-0.1858708748420465</v>
+      </c>
+      <c r="W52">
+        <v>0.2831859649122807</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>-0.743483499368186</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.2429800846953044</v>
+      </c>
+      <c r="C53">
+        <v>-8.837417364102322</v>
+      </c>
+      <c r="D53">
+        <v>26.15758263589768</v>
+      </c>
+      <c r="E53">
+        <v>-2.194999999999993</v>
+      </c>
+      <c r="F53">
+        <v>43.605</v>
+      </c>
+      <c r="G53">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H53">
+        <v>39.7</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>2.06</v>
+      </c>
+      <c r="K53">
+        <v>9.65</v>
+      </c>
+      <c r="L53">
+        <v>-7.59</v>
+      </c>
+      <c r="M53">
+        <v>10.412874</v>
+      </c>
+      <c r="N53">
+        <v>-18.002874</v>
+      </c>
+      <c r="O53">
+        <v>-4.500718500000001</v>
+      </c>
+      <c r="P53">
+        <v>-13.5021555</v>
+      </c>
+      <c r="Q53">
+        <v>-3.8521555</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.2020389841615593</v>
+      </c>
+      <c r="T53">
+        <v>1.882127140483459</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>-0.1822263478843593</v>
+      </c>
+      <c r="W53">
+        <v>0.282315651874785</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>-0.7289053915374371</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.2449800846953044</v>
+      </c>
+      <c r="C54">
+        <v>-9.946152662296171</v>
+      </c>
+      <c r="D54">
+        <v>25.90384733770383</v>
+      </c>
+      <c r="E54">
+        <v>-1.339999999999996</v>
+      </c>
+      <c r="F54">
+        <v>44.46</v>
+      </c>
+      <c r="G54">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H54">
+        <v>39.7</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>2.06</v>
+      </c>
+      <c r="K54">
+        <v>9.65</v>
+      </c>
+      <c r="L54">
+        <v>-7.59</v>
+      </c>
+      <c r="M54">
+        <v>10.617048</v>
+      </c>
+      <c r="N54">
+        <v>-18.207048</v>
+      </c>
+      <c r="O54">
+        <v>-4.551762</v>
+      </c>
+      <c r="P54">
+        <v>-13.655286</v>
+      </c>
+      <c r="Q54">
+        <v>-4.005286</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.2054397963315918</v>
+      </c>
+      <c r="T54">
+        <v>1.921338122576864</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>-0.1787219950404293</v>
+      </c>
+      <c r="W54">
+        <v>0.2814788124156545</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>-0.7148879801617172</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2469800846953044</v>
+      </c>
+      <c r="C55">
+        <v>-11.05001265652297</v>
+      </c>
+      <c r="D55">
+        <v>25.65498734347703</v>
+      </c>
+      <c r="E55">
+        <v>-0.4849999999999923</v>
+      </c>
+      <c r="F55">
+        <v>45.315</v>
+      </c>
+      <c r="G55">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H55">
+        <v>39.7</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>2.06</v>
+      </c>
+      <c r="K55">
+        <v>9.65</v>
+      </c>
+      <c r="L55">
+        <v>-7.59</v>
+      </c>
+      <c r="M55">
+        <v>10.821222</v>
+      </c>
+      <c r="N55">
+        <v>-18.411222</v>
+      </c>
+      <c r="O55">
+        <v>-4.602805500000001</v>
+      </c>
+      <c r="P55">
+        <v>-13.8084165</v>
+      </c>
+      <c r="Q55">
+        <v>-4.158416500000001</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.2089853239131151</v>
+      </c>
+      <c r="T55">
+        <v>1.962217657099776</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>-0.1753498819264589</v>
+      </c>
+      <c r="W55">
+        <v>0.2806735518040384</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>-0.7013995277058356</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2489800846953044</v>
+      </c>
+      <c r="C56">
+        <v>-12.14913652183274</v>
+      </c>
+      <c r="D56">
+        <v>25.41086347816726</v>
+      </c>
+      <c r="E56">
+        <v>0.3700000000000045</v>
+      </c>
+      <c r="F56">
+        <v>46.17</v>
+      </c>
+      <c r="G56">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H56">
+        <v>39.7</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>2.06</v>
+      </c>
+      <c r="K56">
+        <v>9.65</v>
+      </c>
+      <c r="L56">
+        <v>-7.59</v>
+      </c>
+      <c r="M56">
+        <v>11.025396</v>
+      </c>
+      <c r="N56">
+        <v>-18.615396</v>
+      </c>
+      <c r="O56">
+        <v>-4.653849</v>
+      </c>
+      <c r="P56">
+        <v>-13.961547</v>
+      </c>
+      <c r="Q56">
+        <v>-4.311546999999999</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.212685004867748</v>
+      </c>
+      <c r="T56">
+        <v>2.004874562688902</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>-0.1721026618907838</v>
+      </c>
+      <c r="W56">
+        <v>0.2798981156595192</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>-0.6884106475631351</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2509800846953045</v>
+      </c>
+      <c r="C57">
+        <v>-13.24365818584432</v>
+      </c>
+      <c r="D57">
+        <v>25.17134181415569</v>
+      </c>
+      <c r="E57">
+        <v>1.225000000000009</v>
+      </c>
+      <c r="F57">
+        <v>47.02500000000001</v>
+      </c>
+      <c r="G57">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H57">
+        <v>39.7</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>2.06</v>
+      </c>
+      <c r="K57">
+        <v>9.65</v>
+      </c>
+      <c r="L57">
+        <v>-7.59</v>
+      </c>
+      <c r="M57">
+        <v>11.22957</v>
+      </c>
+      <c r="N57">
+        <v>-18.81957</v>
+      </c>
+      <c r="O57">
+        <v>-4.704892500000001</v>
+      </c>
+      <c r="P57">
+        <v>-14.1146775</v>
+      </c>
+      <c r="Q57">
+        <v>-4.464677500000002</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.2165491160870313</v>
+      </c>
+      <c r="T57">
+        <v>2.049427330748655</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>-0.1689735225836786</v>
+      </c>
+      <c r="W57">
+        <v>0.2791508771929825</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>-0.6758940903347144</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2529800846953044</v>
+      </c>
+      <c r="C58">
+        <v>-14.33370657374616</v>
+      </c>
+      <c r="D58">
+        <v>24.93629342625385</v>
+      </c>
+      <c r="E58">
+        <v>2.080000000000005</v>
+      </c>
+      <c r="F58">
+        <v>47.88</v>
+      </c>
+      <c r="G58">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H58">
+        <v>39.7</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>2.06</v>
+      </c>
+      <c r="K58">
+        <v>9.65</v>
+      </c>
+      <c r="L58">
+        <v>-7.59</v>
+      </c>
+      <c r="M58">
+        <v>11.433744</v>
+      </c>
+      <c r="N58">
+        <v>-19.023744</v>
+      </c>
+      <c r="O58">
+        <v>-4.755936</v>
+      </c>
+      <c r="P58">
+        <v>-14.267808</v>
+      </c>
+      <c r="Q58">
+        <v>-4.617808</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.2205888687253729</v>
+      </c>
+      <c r="T58">
+        <v>2.096005224629307</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>-0.1659561382518272</v>
+      </c>
+      <c r="W58">
+        <v>0.2784303258145364</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>-0.6638245530073088</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2549800846953045</v>
+      </c>
+      <c r="C59">
+        <v>-15.41940583969751</v>
+      </c>
+      <c r="D59">
+        <v>24.70559416030249</v>
+      </c>
+      <c r="E59">
+        <v>2.935000000000009</v>
+      </c>
+      <c r="F59">
+        <v>48.73500000000001</v>
+      </c>
+      <c r="G59">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H59">
+        <v>39.7</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>2.06</v>
+      </c>
+      <c r="K59">
+        <v>9.65</v>
+      </c>
+      <c r="L59">
+        <v>-7.59</v>
+      </c>
+      <c r="M59">
+        <v>11.637918</v>
+      </c>
+      <c r="N59">
+        <v>-19.227918</v>
+      </c>
+      <c r="O59">
+        <v>-4.806979500000001</v>
+      </c>
+      <c r="P59">
+        <v>-14.4209385</v>
+      </c>
+      <c r="Q59">
+        <v>-4.770938500000002</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.2248165168352653</v>
+      </c>
+      <c r="T59">
+        <v>2.144749532178825</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>-0.1630446270544267</v>
+      </c>
+      <c r="W59">
+        <v>0.2777350569405971</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>-0.6521785082177067</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2569800846953044</v>
+      </c>
+      <c r="C60">
+        <v>-16.50087558550225</v>
+      </c>
+      <c r="D60">
+        <v>24.47912441449775</v>
+      </c>
+      <c r="E60">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="F60">
+        <v>49.59</v>
+      </c>
+      <c r="G60">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H60">
+        <v>39.7</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>2.06</v>
+      </c>
+      <c r="K60">
+        <v>9.65</v>
+      </c>
+      <c r="L60">
+        <v>-7.59</v>
+      </c>
+      <c r="M60">
+        <v>11.842092</v>
+      </c>
+      <c r="N60">
+        <v>-19.432092</v>
+      </c>
+      <c r="O60">
+        <v>-4.858022999999999</v>
+      </c>
+      <c r="P60">
+        <v>-14.574069</v>
+      </c>
+      <c r="Q60">
+        <v>-4.924068999999998</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.2292454815218192</v>
+      </c>
+      <c r="T60">
+        <v>2.195814997230702</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>-0.1602335127948677</v>
+      </c>
+      <c r="W60">
+        <v>0.2770637628554145</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>-0.6409340511794706</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2589800846953044</v>
+      </c>
+      <c r="C61">
+        <v>-17.57823106736496</v>
+      </c>
+      <c r="D61">
+        <v>24.25676893263504</v>
+      </c>
+      <c r="E61">
+        <v>4.645000000000003</v>
+      </c>
+      <c r="F61">
+        <v>50.445</v>
+      </c>
+      <c r="G61">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H61">
+        <v>39.7</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>2.06</v>
+      </c>
+      <c r="K61">
+        <v>9.65</v>
+      </c>
+      <c r="L61">
+        <v>-7.59</v>
+      </c>
+      <c r="M61">
+        <v>12.046266</v>
+      </c>
+      <c r="N61">
+        <v>-19.636266</v>
+      </c>
+      <c r="O61">
+        <v>-4.9090665</v>
+      </c>
+      <c r="P61">
+        <v>-14.7271995</v>
+      </c>
+      <c r="Q61">
+        <v>-5.077199499999999</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.2338904932662538</v>
+      </c>
+      <c r="T61">
+        <v>2.249371460577792</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>-0.1575176905441072</v>
+      </c>
+      <c r="W61">
+        <v>0.2764152245019328</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>-0.6300707621764285</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2609800846953044</v>
+      </c>
+      <c r="C62">
+        <v>-18.65158339147988</v>
+      </c>
+      <c r="D62">
+        <v>24.03841660852012</v>
+      </c>
+      <c r="E62">
+        <v>5.5</v>
+      </c>
+      <c r="F62">
+        <v>51.3</v>
+      </c>
+      <c r="G62">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H62">
+        <v>39.7</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>2.06</v>
+      </c>
+      <c r="K62">
+        <v>9.65</v>
+      </c>
+      <c r="L62">
+        <v>-7.59</v>
+      </c>
+      <c r="M62">
+        <v>12.25044</v>
+      </c>
+      <c r="N62">
+        <v>-19.84044</v>
+      </c>
+      <c r="O62">
+        <v>-4.96011</v>
+      </c>
+      <c r="P62">
+        <v>-14.88033</v>
+      </c>
+      <c r="Q62">
+        <v>-5.23033</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2387677555979101</v>
+      </c>
+      <c r="T62">
+        <v>2.305605747092236</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>-0.1548923957017054</v>
+      </c>
+      <c r="W62">
+        <v>0.2757883040935672</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>-0.6195695828068217</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2629800846953044</v>
+      </c>
+      <c r="C63">
+        <v>-19.7210396991505</v>
+      </c>
+      <c r="D63">
+        <v>23.82396030084951</v>
+      </c>
+      <c r="E63">
+        <v>6.355000000000004</v>
+      </c>
+      <c r="F63">
+        <v>52.155</v>
+      </c>
+      <c r="G63">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H63">
+        <v>39.7</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>2.06</v>
+      </c>
+      <c r="K63">
+        <v>9.65</v>
+      </c>
+      <c r="L63">
+        <v>-7.59</v>
+      </c>
+      <c r="M63">
+        <v>12.454614</v>
+      </c>
+      <c r="N63">
+        <v>-20.044614</v>
+      </c>
+      <c r="O63">
+        <v>-5.011153500000001</v>
+      </c>
+      <c r="P63">
+        <v>-15.0334605</v>
+      </c>
+      <c r="Q63">
+        <v>-5.383460500000002</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2438951339465745</v>
+      </c>
+      <c r="T63">
+        <v>2.364723843171525</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>-0.1523531761000381</v>
+      </c>
+      <c r="W63">
+        <v>0.2751819384526891</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>-0.6094127044001525</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2649800846953044</v>
+      </c>
+      <c r="C64">
+        <v>-20.78670334208744</v>
+      </c>
+      <c r="D64">
+        <v>23.61329665791256</v>
+      </c>
+      <c r="E64">
+        <v>7.210000000000001</v>
+      </c>
+      <c r="F64">
+        <v>53.01</v>
+      </c>
+      <c r="G64">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H64">
+        <v>39.7</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>2.06</v>
+      </c>
+      <c r="K64">
+        <v>9.65</v>
+      </c>
+      <c r="L64">
+        <v>-7.59</v>
+      </c>
+      <c r="M64">
+        <v>12.658788</v>
+      </c>
+      <c r="N64">
+        <v>-20.248788</v>
+      </c>
+      <c r="O64">
+        <v>-5.062196999999999</v>
+      </c>
+      <c r="P64">
+        <v>-15.186591</v>
+      </c>
+      <c r="Q64">
+        <v>-5.536590999999998</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2492923743135897</v>
+      </c>
+      <c r="T64">
+        <v>2.426953417991828</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>-0.149895866808102</v>
+      </c>
+      <c r="W64">
+        <v>0.2745951329937748</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>-0.5995834672324079</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2669800846953044</v>
+      </c>
+      <c r="C65">
+        <v>-21.84867404848755</v>
+      </c>
+      <c r="D65">
+        <v>23.40632595151245</v>
+      </c>
+      <c r="E65">
+        <v>8.065000000000005</v>
+      </c>
+      <c r="F65">
+        <v>53.865</v>
+      </c>
+      <c r="G65">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H65">
+        <v>39.7</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>2.06</v>
+      </c>
+      <c r="K65">
+        <v>9.65</v>
+      </c>
+      <c r="L65">
+        <v>-7.59</v>
+      </c>
+      <c r="M65">
+        <v>12.862962</v>
+      </c>
+      <c r="N65">
+        <v>-20.452962</v>
+      </c>
+      <c r="O65">
+        <v>-5.1132405</v>
+      </c>
+      <c r="P65">
+        <v>-15.3397215</v>
+      </c>
+      <c r="Q65">
+        <v>-5.689721499999999</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2549813574031461</v>
+      </c>
+      <c r="T65">
+        <v>2.492546753613229</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>-0.1475165673349575</v>
+      </c>
+      <c r="W65">
+        <v>0.2740269562795878</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>-0.59006626933983</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2689800846953044</v>
+      </c>
+      <c r="C66">
+        <v>-22.9070480804547</v>
+      </c>
+      <c r="D66">
+        <v>23.2029519195453</v>
+      </c>
+      <c r="E66">
+        <v>8.920000000000002</v>
+      </c>
+      <c r="F66">
+        <v>54.72</v>
+      </c>
+      <c r="G66">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H66">
+        <v>39.7</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>2.06</v>
+      </c>
+      <c r="K66">
+        <v>9.65</v>
+      </c>
+      <c r="L66">
+        <v>-7.59</v>
+      </c>
+      <c r="M66">
+        <v>13.067136</v>
+      </c>
+      <c r="N66">
+        <v>-20.657136</v>
+      </c>
+      <c r="O66">
+        <v>-5.164284</v>
+      </c>
+      <c r="P66">
+        <v>-15.492852</v>
+      </c>
+      <c r="Q66">
+        <v>-5.842852000000001</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2609863951087891</v>
+      </c>
+      <c r="T66">
+        <v>2.561784163435819</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>-0.1452116209703488</v>
+      </c>
+      <c r="W66">
+        <v>0.2734765350877194</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>-0.5808464838813954</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2709800846953044</v>
+      </c>
+      <c r="C67">
+        <v>-23.96191838328447</v>
+      </c>
+      <c r="D67">
+        <v>23.00308161671553</v>
+      </c>
+      <c r="E67">
+        <v>9.775000000000006</v>
+      </c>
+      <c r="F67">
+        <v>55.575</v>
+      </c>
+      <c r="G67">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H67">
+        <v>39.7</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>2.06</v>
+      </c>
+      <c r="K67">
+        <v>9.65</v>
+      </c>
+      <c r="L67">
+        <v>-7.59</v>
+      </c>
+      <c r="M67">
+        <v>13.27131</v>
+      </c>
+      <c r="N67">
+        <v>-20.86131</v>
+      </c>
+      <c r="O67">
+        <v>-5.215327500000001</v>
+      </c>
+      <c r="P67">
+        <v>-15.6459825</v>
+      </c>
+      <c r="Q67">
+        <v>-5.995982500000002</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2673345778261831</v>
+      </c>
+      <c r="T67">
+        <v>2.634977996676843</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>-0.1429775960323434</v>
+      </c>
+      <c r="W67">
+        <v>0.2729430499325236</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>-0.5719103841293738</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2729800846953044</v>
+      </c>
+      <c r="C68">
+        <v>-25.01337472709906</v>
+      </c>
+      <c r="D68">
+        <v>22.80662527290094</v>
+      </c>
+      <c r="E68">
+        <v>10.63</v>
+      </c>
+      <c r="F68">
+        <v>56.43</v>
+      </c>
+      <c r="G68">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H68">
+        <v>39.7</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>2.06</v>
+      </c>
+      <c r="K68">
+        <v>9.65</v>
+      </c>
+      <c r="L68">
+        <v>-7.59</v>
+      </c>
+      <c r="M68">
+        <v>13.475484</v>
+      </c>
+      <c r="N68">
+        <v>-21.065484</v>
+      </c>
+      <c r="O68">
+        <v>-5.266370999999999</v>
+      </c>
+      <c r="P68">
+        <v>-15.799113</v>
+      </c>
+      <c r="Q68">
+        <v>-6.149112999999998</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2740561830563649</v>
+      </c>
+      <c r="T68">
+        <v>2.712477349520279</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>-0.1408112688197322</v>
+      </c>
+      <c r="W68">
+        <v>0.2724257309941521</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>-0.5632450752789286</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2749800846953044</v>
+      </c>
+      <c r="C69">
+        <v>-26.06150384128602</v>
+      </c>
+      <c r="D69">
+        <v>22.61349615871399</v>
+      </c>
+      <c r="E69">
+        <v>11.48500000000001</v>
+      </c>
+      <c r="F69">
+        <v>57.285</v>
+      </c>
+      <c r="G69">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H69">
+        <v>39.7</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>2.06</v>
+      </c>
+      <c r="K69">
+        <v>9.65</v>
+      </c>
+      <c r="L69">
+        <v>-7.59</v>
+      </c>
+      <c r="M69">
+        <v>13.679658</v>
+      </c>
+      <c r="N69">
+        <v>-21.269658</v>
+      </c>
+      <c r="O69">
+        <v>-5.3174145</v>
+      </c>
+      <c r="P69">
+        <v>-15.9522435</v>
+      </c>
+      <c r="Q69">
+        <v>-6.302243499999999</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2811851583004972</v>
+      </c>
+      <c r="T69">
+        <v>2.794673632839076</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>-0.1387096080910795</v>
+      </c>
+      <c r="W69">
+        <v>0.2719238544121498</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>-0.5548384323643176</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2769800846953044</v>
+      </c>
+      <c r="C70">
+        <v>-27.10638954216351</v>
+      </c>
+      <c r="D70">
+        <v>22.4236104578365</v>
+      </c>
+      <c r="E70">
+        <v>12.34000000000001</v>
+      </c>
+      <c r="F70">
+        <v>58.14000000000001</v>
+      </c>
+      <c r="G70">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H70">
+        <v>39.7</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>2.06</v>
+      </c>
+      <c r="K70">
+        <v>9.65</v>
+      </c>
+      <c r="L70">
+        <v>-7.59</v>
+      </c>
+      <c r="M70">
+        <v>13.883832</v>
+      </c>
+      <c r="N70">
+        <v>-21.473832</v>
+      </c>
+      <c r="O70">
+        <v>-5.368458</v>
+      </c>
+      <c r="P70">
+        <v>-16.105374</v>
+      </c>
+      <c r="Q70">
+        <v>-6.455374000000001</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2887596944973878</v>
+      </c>
+      <c r="T70">
+        <v>2.882007183865297</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>-0.1366697609132695</v>
+      </c>
+      <c r="W70">
+        <v>0.2714367389060888</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>-0.5466790436530777</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2789800846953044</v>
+      </c>
+      <c r="C71">
+        <v>-28.14811285426727</v>
+      </c>
+      <c r="D71">
+        <v>22.23688714573273</v>
+      </c>
+      <c r="E71">
+        <v>13.19500000000001</v>
+      </c>
+      <c r="F71">
+        <v>58.995</v>
+      </c>
+      <c r="G71">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H71">
+        <v>39.7</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>2.06</v>
+      </c>
+      <c r="K71">
+        <v>9.65</v>
+      </c>
+      <c r="L71">
+        <v>-7.59</v>
+      </c>
+      <c r="M71">
+        <v>14.088006</v>
+      </c>
+      <c r="N71">
+        <v>-21.678006</v>
+      </c>
+      <c r="O71">
+        <v>-5.419501500000001</v>
+      </c>
+      <c r="P71">
+        <v>-16.2585045</v>
+      </c>
+      <c r="Q71">
+        <v>-6.6085045</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2968229104489163</v>
+      </c>
+      <c r="T71">
+        <v>2.97497515753837</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>-0.1346890397406134</v>
+      </c>
+      <c r="W71">
+        <v>0.2709637426900585</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>-0.5387561589624537</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2809800846953044</v>
+      </c>
+      <c r="C72">
+        <v>-29.18675212562777</v>
+      </c>
+      <c r="D72">
+        <v>22.05324787437224</v>
+      </c>
+      <c r="E72">
+        <v>14.05000000000001</v>
+      </c>
+      <c r="F72">
+        <v>59.85000000000001</v>
+      </c>
+      <c r="G72">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H72">
+        <v>39.7</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>2.06</v>
+      </c>
+      <c r="K72">
+        <v>9.65</v>
+      </c>
+      <c r="L72">
+        <v>-7.59</v>
+      </c>
+      <c r="M72">
+        <v>14.29218</v>
+      </c>
+      <c r="N72">
+        <v>-21.88218</v>
+      </c>
+      <c r="O72">
+        <v>-5.470545</v>
+      </c>
+      <c r="P72">
+        <v>-16.411635</v>
+      </c>
+      <c r="Q72">
+        <v>-6.761635</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.3054236741305469</v>
+      </c>
+      <c r="T72">
+        <v>3.074140996122983</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>-0.1327649106014618</v>
+      </c>
+      <c r="W72">
+        <v>0.2705042606516291</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>-0.5310596424058471</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2829800846953044</v>
+      </c>
+      <c r="C73">
+        <v>-30.22238313738198</v>
+      </c>
+      <c r="D73">
+        <v>21.87261686261802</v>
+      </c>
+      <c r="E73">
+        <v>14.905</v>
+      </c>
+      <c r="F73">
+        <v>60.705</v>
+      </c>
+      <c r="G73">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H73">
+        <v>39.7</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>2.06</v>
+      </c>
+      <c r="K73">
+        <v>9.65</v>
+      </c>
+      <c r="L73">
+        <v>-7.59</v>
+      </c>
+      <c r="M73">
+        <v>14.496354</v>
+      </c>
+      <c r="N73">
+        <v>-22.086354</v>
+      </c>
+      <c r="O73">
+        <v>-5.5215885</v>
+      </c>
+      <c r="P73">
+        <v>-16.5647655</v>
+      </c>
+      <c r="Q73">
+        <v>-6.9147655</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.314617593928152</v>
+      </c>
+      <c r="T73">
+        <v>3.180145858058258</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>-0.1308949822831313</v>
+      </c>
+      <c r="W73">
+        <v>0.2700577217692118</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>-0.5235799291325254</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2849800846953044</v>
+      </c>
+      <c r="C74">
+        <v>-31.25507920804252</v>
+      </c>
+      <c r="D74">
+        <v>21.69492079195748</v>
+      </c>
+      <c r="E74">
+        <v>15.76</v>
+      </c>
+      <c r="F74">
+        <v>61.56</v>
+      </c>
+      <c r="G74">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H74">
+        <v>39.7</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>2.06</v>
+      </c>
+      <c r="K74">
+        <v>9.65</v>
+      </c>
+      <c r="L74">
+        <v>-7.59</v>
+      </c>
+      <c r="M74">
+        <v>14.700528</v>
+      </c>
+      <c r="N74">
+        <v>-22.290528</v>
+      </c>
+      <c r="O74">
+        <v>-5.572632</v>
+      </c>
+      <c r="P74">
+        <v>-16.717896</v>
+      </c>
+      <c r="Q74">
+        <v>-7.067896000000003</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.3244682222827288</v>
+      </c>
+      <c r="T74">
+        <v>3.293722495846052</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>-0.1290769964180878</v>
+      </c>
+      <c r="W74">
+        <v>0.2696235867446394</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>-0.5163079856723514</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2869800846953044</v>
+      </c>
+      <c r="C75">
+        <v>-32.28491129272484</v>
+      </c>
+      <c r="D75">
+        <v>21.52008870727515</v>
+      </c>
+      <c r="E75">
+        <v>16.615</v>
+      </c>
+      <c r="F75">
+        <v>62.415</v>
+      </c>
+      <c r="G75">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H75">
+        <v>39.7</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>2.06</v>
+      </c>
+      <c r="K75">
+        <v>9.65</v>
+      </c>
+      <c r="L75">
+        <v>-7.59</v>
+      </c>
+      <c r="M75">
+        <v>14.904702</v>
+      </c>
+      <c r="N75">
+        <v>-22.494702</v>
+      </c>
+      <c r="O75">
+        <v>-5.6236755</v>
+      </c>
+      <c r="P75">
+        <v>-16.8710265</v>
+      </c>
+      <c r="Q75">
+        <v>-7.221026499999999</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.3350485268117188</v>
+      </c>
+      <c r="T75">
+        <v>3.415712217914425</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>-0.1273088183849634</v>
+      </c>
+      <c r="W75">
+        <v>0.2692013458303292</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>-0.5092352735398533</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2889800846953045</v>
+      </c>
+      <c r="C76">
+        <v>-33.3119480776151</v>
+      </c>
+      <c r="D76">
+        <v>21.3480519223849</v>
+      </c>
+      <c r="E76">
+        <v>17.47</v>
+      </c>
+      <c r="F76">
+        <v>63.27</v>
+      </c>
+      <c r="G76">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H76">
+        <v>39.7</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>2.06</v>
+      </c>
+      <c r="K76">
+        <v>9.65</v>
+      </c>
+      <c r="L76">
+        <v>-7.59</v>
+      </c>
+      <c r="M76">
+        <v>15.108876</v>
+      </c>
+      <c r="N76">
+        <v>-22.698876</v>
+      </c>
+      <c r="O76">
+        <v>-5.674719</v>
+      </c>
+      <c r="P76">
+        <v>-17.024157</v>
+      </c>
+      <c r="Q76">
+        <v>-7.374156999999999</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.3464427009198618</v>
+      </c>
+      <c r="T76">
+        <v>3.547085764757288</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>-0.1255884289473287</v>
+      </c>
+      <c r="W76">
+        <v>0.2687905168326221</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>-0.5023537157893148</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2909800846953044</v>
+      </c>
+      <c r="C77">
+        <v>-34.33625606994271</v>
+      </c>
+      <c r="D77">
+        <v>21.17874393005729</v>
+      </c>
+      <c r="E77">
+        <v>18.325</v>
+      </c>
+      <c r="F77">
+        <v>64.125</v>
+      </c>
+      <c r="G77">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H77">
+        <v>39.7</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>2.06</v>
+      </c>
+      <c r="K77">
+        <v>9.65</v>
+      </c>
+      <c r="L77">
+        <v>-7.59</v>
+      </c>
+      <c r="M77">
+        <v>15.31305</v>
+      </c>
+      <c r="N77">
+        <v>-22.90305</v>
+      </c>
+      <c r="O77">
+        <v>-5.7257625</v>
+      </c>
+      <c r="P77">
+        <v>-17.1772875</v>
+      </c>
+      <c r="Q77">
+        <v>-7.527287499999998</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.3587484089566562</v>
+      </c>
+      <c r="T77">
+        <v>3.688969195347579</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>-0.1239139165613643</v>
+      </c>
+      <c r="W77">
+        <v>0.2683906432748538</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>-0.4956556662454572</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2929800846953044</v>
+      </c>
+      <c r="C78">
+        <v>-35.35789968370533</v>
+      </c>
+      <c r="D78">
+        <v>21.01210031629467</v>
+      </c>
+      <c r="E78">
+        <v>19.18000000000001</v>
+      </c>
+      <c r="F78">
+        <v>64.98</v>
+      </c>
+      <c r="G78">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H78">
+        <v>39.7</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>2.06</v>
+      </c>
+      <c r="K78">
+        <v>9.65</v>
+      </c>
+      <c r="L78">
+        <v>-7.59</v>
+      </c>
+      <c r="M78">
+        <v>15.517224</v>
+      </c>
+      <c r="N78">
+        <v>-23.107224</v>
+      </c>
+      <c r="O78">
+        <v>-5.776806000000001</v>
+      </c>
+      <c r="P78">
+        <v>-17.330418</v>
+      </c>
+      <c r="Q78">
+        <v>-7.680418000000001</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.3720795926631836</v>
+      </c>
+      <c r="T78">
+        <v>3.842676245153728</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>-0.12228347029082</v>
+      </c>
+      <c r="W78">
+        <v>0.2680012927054478</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>-0.4891338811632802</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2949800846953044</v>
+      </c>
+      <c r="C79">
+        <v>-36.3769413213782</v>
+      </c>
+      <c r="D79">
+        <v>20.84805867862181</v>
+      </c>
+      <c r="E79">
+        <v>20.03500000000001</v>
+      </c>
+      <c r="F79">
+        <v>65.83500000000001</v>
+      </c>
+      <c r="G79">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H79">
+        <v>39.7</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>2.06</v>
+      </c>
+      <c r="K79">
+        <v>9.65</v>
+      </c>
+      <c r="L79">
+        <v>-7.59</v>
+      </c>
+      <c r="M79">
+        <v>15.721398</v>
+      </c>
+      <c r="N79">
+        <v>-23.311398</v>
+      </c>
+      <c r="O79">
+        <v>-5.827849500000001</v>
+      </c>
+      <c r="P79">
+        <v>-17.4835485</v>
+      </c>
+      <c r="Q79">
+        <v>-7.833548500000004</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.3865700097354959</v>
+      </c>
+      <c r="T79">
+        <v>4.009749125377803</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>-0.1206953732740561</v>
+      </c>
+      <c r="W79">
+        <v>0.2676220551378446</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>-0.4827814930962246</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2969800846953045</v>
+      </c>
+      <c r="C80">
+        <v>-37.39344145182571</v>
+      </c>
+      <c r="D80">
+        <v>20.68655854817429</v>
+      </c>
+      <c r="E80">
+        <v>20.89</v>
+      </c>
+      <c r="F80">
+        <v>66.69</v>
+      </c>
+      <c r="G80">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H80">
+        <v>39.7</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>2.06</v>
+      </c>
+      <c r="K80">
+        <v>9.65</v>
+      </c>
+      <c r="L80">
+        <v>-7.59</v>
+      </c>
+      <c r="M80">
+        <v>15.925572</v>
+      </c>
+      <c r="N80">
+        <v>-23.515572</v>
+      </c>
+      <c r="O80">
+        <v>-5.878893</v>
+      </c>
+      <c r="P80">
+        <v>-17.636679</v>
+      </c>
+      <c r="Q80">
+        <v>-7.986679000000001</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.4023777374507458</v>
+      </c>
+      <c r="T80">
+        <v>4.192010449258613</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>-0.1191479966936195</v>
+      </c>
+      <c r="W80">
+        <v>0.2672525416104364</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>-0.4765919867744781</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2989800846953045</v>
+      </c>
+      <c r="C81">
+        <v>-38.40745868461968</v>
+      </c>
+      <c r="D81">
+        <v>20.52754131538032</v>
+      </c>
+      <c r="E81">
+        <v>21.745</v>
+      </c>
+      <c r="F81">
+        <v>67.545</v>
+      </c>
+      <c r="G81">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H81">
+        <v>39.7</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>2.06</v>
+      </c>
+      <c r="K81">
+        <v>9.65</v>
+      </c>
+      <c r="L81">
+        <v>-7.59</v>
+      </c>
+      <c r="M81">
+        <v>16.129746</v>
+      </c>
+      <c r="N81">
+        <v>-23.719746</v>
+      </c>
+      <c r="O81">
+        <v>-5.9299365</v>
+      </c>
+      <c r="P81">
+        <v>-17.7898095</v>
+      </c>
+      <c r="Q81">
+        <v>-8.1398095</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.4196909630436385</v>
+      </c>
+      <c r="T81">
+        <v>4.391629994461405</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>-0.1176397942038269</v>
+      </c>
+      <c r="W81">
+        <v>0.2668923828558739</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>-0.4705591768153075</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.3009800846953044</v>
+      </c>
+      <c r="C82">
+        <v>-39.41904984095589</v>
+      </c>
+      <c r="D82">
+        <v>20.37095015904412</v>
+      </c>
+      <c r="E82">
+        <v>22.60000000000001</v>
+      </c>
+      <c r="F82">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="G82">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H82">
+        <v>39.7</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>2.06</v>
+      </c>
+      <c r="K82">
+        <v>9.65</v>
+      </c>
+      <c r="L82">
+        <v>-7.59</v>
+      </c>
+      <c r="M82">
+        <v>16.33392</v>
+      </c>
+      <c r="N82">
+        <v>-23.92392</v>
+      </c>
+      <c r="O82">
+        <v>-5.980980000000001</v>
+      </c>
+      <c r="P82">
+        <v>-17.94294</v>
+      </c>
+      <c r="Q82">
+        <v>-8.29294</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.4387355111958204</v>
+      </c>
+      <c r="T82">
+        <v>4.611211494184475</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>-0.116169296776279</v>
+      </c>
+      <c r="W82">
+        <v>0.2665412280701754</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>-0.4646771871051161</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.3029800846953045</v>
+      </c>
+      <c r="C83">
+        <v>-40.42827002134942</v>
+      </c>
+      <c r="D83">
+        <v>20.21672997865059</v>
+      </c>
+      <c r="E83">
+        <v>23.45500000000001</v>
+      </c>
+      <c r="F83">
+        <v>69.25500000000001</v>
+      </c>
+      <c r="G83">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H83">
+        <v>39.7</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>2.06</v>
+      </c>
+      <c r="K83">
+        <v>9.65</v>
+      </c>
+      <c r="L83">
+        <v>-7.59</v>
+      </c>
+      <c r="M83">
+        <v>16.538094</v>
+      </c>
+      <c r="N83">
+        <v>-24.128094</v>
+      </c>
+      <c r="O83">
+        <v>-6.032023500000001</v>
+      </c>
+      <c r="P83">
+        <v>-18.0960705</v>
+      </c>
+      <c r="Q83">
+        <v>-8.446070500000003</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.4597847486271794</v>
+      </c>
+      <c r="T83">
+        <v>4.853906835983659</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>-0.1147351079271892</v>
+      </c>
+      <c r="W83">
+        <v>0.2661987437730128</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>-0.4589404317087566</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.3049800846953045</v>
+      </c>
+      <c r="C84">
+        <v>-41.43517267027818</v>
+      </c>
+      <c r="D84">
+        <v>20.06482732972182</v>
+      </c>
+      <c r="E84">
+        <v>24.31</v>
+      </c>
+      <c r="F84">
+        <v>70.11</v>
+      </c>
+      <c r="G84">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H84">
+        <v>39.7</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>2.06</v>
+      </c>
+      <c r="K84">
+        <v>9.65</v>
+      </c>
+      <c r="L84">
+        <v>-7.59</v>
+      </c>
+      <c r="M84">
+        <v>16.742268</v>
+      </c>
+      <c r="N84">
+        <v>-24.332268</v>
+      </c>
+      <c r="O84">
+        <v>-6.083067</v>
+      </c>
+      <c r="P84">
+        <v>-18.249201</v>
+      </c>
+      <c r="Q84">
+        <v>-8.599200999999999</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.4831727902175783</v>
+      </c>
+      <c r="T84">
+        <v>5.12356832687164</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>-0.1133358992939308</v>
+      </c>
+      <c r="W84">
+        <v>0.2658646127513907</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>-0.4533435971757231</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.3069800846953045</v>
+      </c>
+      <c r="C85">
+        <v>-42.43980963793385</v>
+      </c>
+      <c r="D85">
+        <v>19.91519036206615</v>
+      </c>
+      <c r="E85">
+        <v>25.16500000000001</v>
+      </c>
+      <c r="F85">
+        <v>70.965</v>
+      </c>
+      <c r="G85">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H85">
+        <v>39.7</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>2.06</v>
+      </c>
+      <c r="K85">
+        <v>9.65</v>
+      </c>
+      <c r="L85">
+        <v>-7.59</v>
+      </c>
+      <c r="M85">
+        <v>16.946442</v>
+      </c>
+      <c r="N85">
+        <v>-24.536442</v>
+      </c>
+      <c r="O85">
+        <v>-6.1341105</v>
+      </c>
+      <c r="P85">
+        <v>-18.4023315</v>
+      </c>
+      <c r="Q85">
+        <v>-8.752331500000002</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.5093123661127301</v>
+      </c>
+      <c r="T85">
+        <v>5.42495469904056</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>-0.1119704065313533</v>
+      </c>
+      <c r="W85">
+        <v>0.2655385330796872</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>-0.4478816261254133</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.3089800846953045</v>
+      </c>
+      <c r="C86">
+        <v>-43.44223123923007</v>
+      </c>
+      <c r="D86">
+        <v>19.76776876076992</v>
+      </c>
+      <c r="E86">
+        <v>26.02</v>
+      </c>
+      <c r="F86">
+        <v>71.81999999999999</v>
+      </c>
+      <c r="G86">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H86">
+        <v>39.7</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>2.06</v>
+      </c>
+      <c r="K86">
+        <v>9.65</v>
+      </c>
+      <c r="L86">
+        <v>-7.59</v>
+      </c>
+      <c r="M86">
+        <v>17.150616</v>
+      </c>
+      <c r="N86">
+        <v>-24.740616</v>
+      </c>
+      <c r="O86">
+        <v>-6.185154</v>
+      </c>
+      <c r="P86">
+        <v>-18.555462</v>
+      </c>
+      <c r="Q86">
+        <v>-8.905461999999998</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.5387193889947753</v>
+      </c>
+      <c r="T86">
+        <v>5.764014367730591</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>-0.1106374255012181</v>
+      </c>
+      <c r="W86">
+        <v>0.2652202172096909</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>-0.4425497020048725</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.3109800846953044</v>
+      </c>
+      <c r="C87">
+        <v>-44.44248631020926</v>
+      </c>
+      <c r="D87">
+        <v>19.62251368979074</v>
+      </c>
+      <c r="E87">
+        <v>26.875</v>
+      </c>
+      <c r="F87">
+        <v>72.675</v>
+      </c>
+      <c r="G87">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H87">
+        <v>39.7</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>2.06</v>
+      </c>
+      <c r="K87">
+        <v>9.65</v>
+      </c>
+      <c r="L87">
+        <v>-7.59</v>
+      </c>
+      <c r="M87">
+        <v>17.35479</v>
+      </c>
+      <c r="N87">
+        <v>-24.94479</v>
+      </c>
+      <c r="O87">
+        <v>-6.2361975</v>
+      </c>
+      <c r="P87">
+        <v>-18.7085925</v>
+      </c>
+      <c r="Q87">
+        <v>-9.058592500000001</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.5720473482610937</v>
+      </c>
+      <c r="T87">
+        <v>6.148281992245964</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>-0.1093358087306156</v>
+      </c>
+      <c r="W87">
+        <v>0.264909391124871</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>-0.4373432349224622</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.3129800846953045</v>
+      </c>
+      <c r="C88">
+        <v>-45.44062226198051</v>
+      </c>
+      <c r="D88">
+        <v>19.47937773801949</v>
+      </c>
+      <c r="E88">
+        <v>27.73</v>
+      </c>
+      <c r="F88">
+        <v>73.53</v>
+      </c>
+      <c r="G88">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H88">
+        <v>39.7</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>2.06</v>
+      </c>
+      <c r="K88">
+        <v>9.65</v>
+      </c>
+      <c r="L88">
+        <v>-7.59</v>
+      </c>
+      <c r="M88">
+        <v>17.558964</v>
+      </c>
+      <c r="N88">
+        <v>-25.148964</v>
+      </c>
+      <c r="O88">
+        <v>-6.287241</v>
+      </c>
+      <c r="P88">
+        <v>-18.861723</v>
+      </c>
+      <c r="Q88">
+        <v>-9.211722999999997</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.6101364445654576</v>
+      </c>
+      <c r="T88">
+        <v>6.587444991692106</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>-0.1080644621174689</v>
+      </c>
+      <c r="W88">
+        <v>0.2646057935536516</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>-0.4322578484698756</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.3149800846953044</v>
+      </c>
+      <c r="C89">
+        <v>-46.4366851323139</v>
+      </c>
+      <c r="D89">
+        <v>19.3383148676861</v>
+      </c>
+      <c r="E89">
+        <v>28.58500000000001</v>
+      </c>
+      <c r="F89">
+        <v>74.38500000000001</v>
+      </c>
+      <c r="G89">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H89">
+        <v>39.7</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>2.06</v>
+      </c>
+      <c r="K89">
+        <v>9.65</v>
+      </c>
+      <c r="L89">
+        <v>-7.59</v>
+      </c>
+      <c r="M89">
+        <v>17.763138</v>
+      </c>
+      <c r="N89">
+        <v>-25.353138</v>
+      </c>
+      <c r="O89">
+        <v>-6.3382845</v>
+      </c>
+      <c r="P89">
+        <v>-19.0148535</v>
+      </c>
+      <c r="Q89">
+        <v>-9.364853500000001</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.6540854018397235</v>
+      </c>
+      <c r="T89">
+        <v>7.094171529514574</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>-0.1068223418632451</v>
+      </c>
+      <c r="W89">
+        <v>0.2643091752369429</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>-0.4272893674529803</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.3169800846953044</v>
+      </c>
+      <c r="C90">
+        <v>-47.43071963500928</v>
+      </c>
+      <c r="D90">
+        <v>19.19928036499071</v>
+      </c>
+      <c r="E90">
+        <v>29.44</v>
+      </c>
+      <c r="F90">
+        <v>75.23999999999999</v>
+      </c>
+      <c r="G90">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H90">
+        <v>39.7</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>2.06</v>
+      </c>
+      <c r="K90">
+        <v>9.65</v>
+      </c>
+      <c r="L90">
+        <v>-7.59</v>
+      </c>
+      <c r="M90">
+        <v>17.967312</v>
+      </c>
+      <c r="N90">
+        <v>-25.557312</v>
+      </c>
+      <c r="O90">
+        <v>-6.389328</v>
+      </c>
+      <c r="P90">
+        <v>-19.167984</v>
+      </c>
+      <c r="Q90">
+        <v>-9.517984</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.7053591853263672</v>
+      </c>
+      <c r="T90">
+        <v>7.685352490307456</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>-0.1056084516147991</v>
+      </c>
+      <c r="W90">
+        <v>0.264019298245614</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>-0.4224338064591966</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.3189800846953044</v>
+      </c>
+      <c r="C91">
+        <v>-48.42276920715049</v>
+      </c>
+      <c r="D91">
+        <v>19.0622307928495</v>
+      </c>
+      <c r="E91">
+        <v>30.295</v>
+      </c>
+      <c r="F91">
+        <v>76.095</v>
+      </c>
+      <c r="G91">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H91">
+        <v>39.7</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>2.06</v>
+      </c>
+      <c r="K91">
+        <v>9.65</v>
+      </c>
+      <c r="L91">
+        <v>-7.59</v>
+      </c>
+      <c r="M91">
+        <v>18.171486</v>
+      </c>
+      <c r="N91">
+        <v>-25.761486</v>
+      </c>
+      <c r="O91">
+        <v>-6.4403715</v>
+      </c>
+      <c r="P91">
+        <v>-19.3211145</v>
+      </c>
+      <c r="Q91">
+        <v>-9.6711145</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.7659554749014914</v>
+      </c>
+      <c r="T91">
+        <v>8.384020898517225</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>-0.1044218397989025</v>
+      </c>
+      <c r="W91">
+        <v>0.2637359353439779</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>-0.4176873591956101</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.3209800846953045</v>
+      </c>
+      <c r="C92">
+        <v>-49.41287605435011</v>
+      </c>
+      <c r="D92">
+        <v>18.92712394564989</v>
+      </c>
+      <c r="E92">
+        <v>31.15000000000001</v>
+      </c>
+      <c r="F92">
+        <v>76.95</v>
+      </c>
+      <c r="G92">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H92">
+        <v>39.7</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>2.06</v>
+      </c>
+      <c r="K92">
+        <v>9.65</v>
+      </c>
+      <c r="L92">
+        <v>-7.59</v>
+      </c>
+      <c r="M92">
+        <v>18.37566</v>
+      </c>
+      <c r="N92">
+        <v>-25.96566</v>
+      </c>
+      <c r="O92">
+        <v>-6.491415</v>
+      </c>
+      <c r="P92">
+        <v>-19.474245</v>
+      </c>
+      <c r="Q92">
+        <v>-9.824244999999999</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.8386710223916407</v>
+      </c>
+      <c r="T92">
+        <v>9.222422988368949</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>-0.1032615971344703</v>
+      </c>
+      <c r="W92">
+        <v>0.2634588693957116</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>-0.413046388537881</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.3229800846953044</v>
+      </c>
+      <c r="C93">
+        <v>-50.40108119408356</v>
+      </c>
+      <c r="D93">
+        <v>18.79391880591645</v>
+      </c>
+      <c r="E93">
+        <v>32.00500000000001</v>
+      </c>
+      <c r="F93">
+        <v>77.80500000000001</v>
+      </c>
+      <c r="G93">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H93">
+        <v>39.7</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>2.06</v>
+      </c>
+      <c r="K93">
+        <v>9.65</v>
+      </c>
+      <c r="L93">
+        <v>-7.59</v>
+      </c>
+      <c r="M93">
+        <v>18.579834</v>
+      </c>
+      <c r="N93">
+        <v>-26.169834</v>
+      </c>
+      <c r="O93">
+        <v>-6.5424585</v>
+      </c>
+      <c r="P93">
+        <v>-19.6273755</v>
+      </c>
+      <c r="Q93">
+        <v>-9.977375499999999</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.9275455804351564</v>
+      </c>
+      <c r="T93">
+        <v>10.24713665374328</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>-0.1021268543088167</v>
+      </c>
+      <c r="W93">
+        <v>0.2631878928089454</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>-0.408507417235267</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.3249800846953044</v>
+      </c>
+      <c r="C94">
+        <v>-51.38742449720631</v>
+      </c>
+      <c r="D94">
+        <v>18.66257550279369</v>
+      </c>
+      <c r="E94">
+        <v>32.86</v>
+      </c>
+      <c r="F94">
+        <v>78.66</v>
+      </c>
+      <c r="G94">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H94">
+        <v>39.7</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>2.06</v>
+      </c>
+      <c r="K94">
+        <v>9.65</v>
+      </c>
+      <c r="L94">
+        <v>-7.59</v>
+      </c>
+      <c r="M94">
+        <v>18.784008</v>
+      </c>
+      <c r="N94">
+        <v>-26.374008</v>
+      </c>
+      <c r="O94">
+        <v>-6.593502</v>
+      </c>
+      <c r="P94">
+        <v>-19.780506</v>
+      </c>
+      <c r="Q94">
+        <v>-10.130506</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>1.038638777989551</v>
+      </c>
+      <c r="T94">
+        <v>11.52802873546119</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>-0.10101677980546</v>
+      </c>
+      <c r="W94">
+        <v>0.2629228070175438</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>-0.4040671192218401</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.3269800846953044</v>
+      </c>
+      <c r="C95">
+        <v>-52.3719447277422</v>
+      </c>
+      <c r="D95">
+        <v>18.5330552722578</v>
+      </c>
+      <c r="E95">
+        <v>33.715</v>
+      </c>
+      <c r="F95">
+        <v>79.515</v>
+      </c>
+      <c r="G95">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H95">
+        <v>39.7</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>2.06</v>
+      </c>
+      <c r="K95">
+        <v>9.65</v>
+      </c>
+      <c r="L95">
+        <v>-7.59</v>
+      </c>
+      <c r="M95">
+        <v>18.988182</v>
+      </c>
+      <c r="N95">
+        <v>-26.578182</v>
+      </c>
+      <c r="O95">
+        <v>-6.6445455</v>
+      </c>
+      <c r="P95">
+        <v>-19.9336365</v>
+      </c>
+      <c r="Q95">
+        <v>-10.2836365</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.181472889130916</v>
+      </c>
+      <c r="T95">
+        <v>13.17488998338422</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>-0.09993057787206799</v>
+      </c>
+      <c r="W95">
+        <v>0.2626634219958499</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>-0.399722311488272</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.3289800846953045</v>
+      </c>
+      <c r="C96">
+        <v>-53.35467958102629</v>
+      </c>
+      <c r="D96">
+        <v>18.40532041897372</v>
+      </c>
+      <c r="E96">
+        <v>34.57000000000001</v>
+      </c>
+      <c r="F96">
+        <v>80.37</v>
+      </c>
+      <c r="G96">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H96">
+        <v>39.7</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>2.06</v>
+      </c>
+      <c r="K96">
+        <v>9.65</v>
+      </c>
+      <c r="L96">
+        <v>-7.59</v>
+      </c>
+      <c r="M96">
+        <v>19.192356</v>
+      </c>
+      <c r="N96">
+        <v>-26.782356</v>
+      </c>
+      <c r="O96">
+        <v>-6.695589000000001</v>
+      </c>
+      <c r="P96">
+        <v>-20.086767</v>
+      </c>
+      <c r="Q96">
+        <v>-10.436767</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.371918370652736</v>
+      </c>
+      <c r="T96">
+        <v>15.37070498061493</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>-0.09886748661810982</v>
+      </c>
+      <c r="W96">
+        <v>0.2624095558044047</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>-0.3954699464724392</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.3309800846953045</v>
+      </c>
+      <c r="C97">
+        <v>-54.33566572028124</v>
+      </c>
+      <c r="D97">
+        <v>18.27933427971876</v>
+      </c>
+      <c r="E97">
+        <v>35.42500000000001</v>
+      </c>
+      <c r="F97">
+        <v>81.22500000000001</v>
+      </c>
+      <c r="G97">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H97">
+        <v>39.7</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>2.06</v>
+      </c>
+      <c r="K97">
+        <v>9.65</v>
+      </c>
+      <c r="L97">
+        <v>-7.59</v>
+      </c>
+      <c r="M97">
+        <v>19.39653</v>
+      </c>
+      <c r="N97">
+        <v>-26.98653</v>
+      </c>
+      <c r="O97">
+        <v>-6.7466325</v>
+      </c>
+      <c r="P97">
+        <v>-20.2398975</v>
+      </c>
+      <c r="Q97">
+        <v>-10.5898975</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.638542044783284</v>
+      </c>
+      <c r="T97">
+        <v>18.44484597673792</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>-0.09782677623265604</v>
+      </c>
+      <c r="W97">
+        <v>0.2621610341643583</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>-0.391307104930624</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.3329800846953044</v>
+      </c>
+      <c r="C98">
+        <v>-55.31493881170175</v>
+      </c>
+      <c r="D98">
+        <v>18.15506118829825</v>
+      </c>
+      <c r="E98">
+        <v>36.28</v>
+      </c>
+      <c r="F98">
+        <v>82.08</v>
+      </c>
+      <c r="G98">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H98">
+        <v>39.7</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>2.06</v>
+      </c>
+      <c r="K98">
+        <v>9.65</v>
+      </c>
+      <c r="L98">
+        <v>-7.59</v>
+      </c>
+      <c r="M98">
+        <v>19.600704</v>
+      </c>
+      <c r="N98">
+        <v>-27.190704</v>
+      </c>
+      <c r="O98">
+        <v>-6.797676</v>
+      </c>
+      <c r="P98">
+        <v>-20.393028</v>
+      </c>
+      <c r="Q98">
+        <v>-10.743028</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>2.0384775559791</v>
+      </c>
+      <c r="T98">
+        <v>23.05605747092235</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>-0.09680774731356588</v>
+      </c>
+      <c r="W98">
+        <v>0.2619176900584795</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>-0.3872309892542636</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.3349800846953044</v>
+      </c>
+      <c r="C99">
+        <v>-56.29253355811744</v>
+      </c>
+      <c r="D99">
+        <v>18.03246644188256</v>
+      </c>
+      <c r="E99">
+        <v>37.13500000000001</v>
+      </c>
+      <c r="F99">
+        <v>82.935</v>
+      </c>
+      <c r="G99">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H99">
+        <v>39.7</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>2.06</v>
+      </c>
+      <c r="K99">
+        <v>9.65</v>
+      </c>
+      <c r="L99">
+        <v>-7.59</v>
+      </c>
+      <c r="M99">
+        <v>19.804878</v>
+      </c>
+      <c r="N99">
+        <v>-27.394878</v>
+      </c>
+      <c r="O99">
+        <v>-6.848719500000001</v>
+      </c>
+      <c r="P99">
+        <v>-20.5461585</v>
+      </c>
+      <c r="Q99">
+        <v>-10.8961585</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.705036741305467</v>
+      </c>
+      <c r="T99">
+        <v>30.7414099612298</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>-0.09580972930002395</v>
+      </c>
+      <c r="W99">
+        <v>0.2616793633568457</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>-0.3832389172000958</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.3369800846953044</v>
+      </c>
+      <c r="C100">
+        <v>-57.26848373130092</v>
+      </c>
+      <c r="D100">
+        <v>17.91151626869907</v>
+      </c>
+      <c r="E100">
+        <v>37.98999999999999</v>
+      </c>
+      <c r="F100">
+        <v>83.78999999999999</v>
+      </c>
+      <c r="G100">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H100">
+        <v>39.7</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>2.06</v>
+      </c>
+      <c r="K100">
+        <v>9.65</v>
+      </c>
+      <c r="L100">
+        <v>-7.59</v>
+      </c>
+      <c r="M100">
+        <v>20.009052</v>
+      </c>
+      <c r="N100">
+        <v>-27.599052</v>
+      </c>
+      <c r="O100">
+        <v>-6.899763</v>
+      </c>
+      <c r="P100">
+        <v>-20.699289</v>
+      </c>
+      <c r="Q100">
+        <v>-11.049289</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>4.0381551119582</v>
+      </c>
+      <c r="T100">
+        <v>46.1121149418447</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>-0.09483207900104412</v>
+      </c>
+      <c r="W100">
+        <v>0.2614459004654494</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>-0.3793283160041765</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.3389800846953044</v>
+      </c>
+      <c r="C101">
+        <v>-58.24282220298454</v>
+      </c>
+      <c r="D101">
+        <v>17.79217779701545</v>
+      </c>
+      <c r="E101">
+        <v>38.845</v>
+      </c>
+      <c r="F101">
+        <v>84.645</v>
+      </c>
+      <c r="G101">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H101">
+        <v>39.7</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>2.06</v>
+      </c>
+      <c r="K101">
+        <v>9.65</v>
+      </c>
+      <c r="L101">
+        <v>-7.59</v>
+      </c>
+      <c r="M101">
+        <v>20.213226</v>
+      </c>
+      <c r="N101">
+        <v>-27.803226</v>
+      </c>
+      <c r="O101">
+        <v>-6.9508065</v>
+      </c>
+      <c r="P101">
+        <v>-20.8524195</v>
+      </c>
+      <c r="Q101">
+        <v>-11.2024195</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>8.037510223916399</v>
+      </c>
+      <c r="T101">
+        <v>92.2242298836894</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>-0.0938741792131548</v>
+      </c>
+      <c r="W101">
+        <v>0.2612171539961013</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>-0.3754967168526191</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/spain/spain_apparel.xlsx
+++ b/research/traditional_assets/database/data/spain/spain_apparel.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,13 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
+      </c>
+      <c r="B2">
+        <v>0.1173144434439832</v>
+      </c>
+      <c r="C2">
+        <v>75.94556613815041</v>
+      </c>
+      <c r="D2">
+        <v>74.89856613815041</v>
       </c>
       <c r="E2">
-        <v>-59</v>
+        <v>-57.957</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.043</v>
       </c>
       <c r="G2">
         <v>2.09</v>
@@ -1442,43 +1451,45 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.2459394</v>
       </c>
       <c r="N2">
-        <v>-6.746666666666666</v>
+        <v>-6.992606066666666</v>
       </c>
       <c r="O2">
-        <v>-1.686666666666667</v>
+        <v>-1.748151516666667</v>
       </c>
       <c r="P2">
-        <v>-5.06</v>
+        <v>-5.244454549999999</v>
       </c>
       <c r="Q2">
-        <v>11.14</v>
+        <v>10.95554545</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S2">
+        <v>0.09978297243325665</v>
+      </c>
+      <c r="T2">
+        <v>0.8350994148999304</v>
       </c>
       <c r="U2">
-        <v>0.0503</v>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>-Inf</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.2358</v>
+      </c>
+      <c r="V2">
+        <v>-6.858057987726515</v>
+      </c>
+      <c r="W2">
+        <v>1.852930073505912</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>-27.43223195090606</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1486,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1173144434439832</v>
+        <v>0.1192144434439832</v>
       </c>
       <c r="C3">
-        <v>75.94556613815041</v>
+        <v>73.37000337348303</v>
       </c>
       <c r="D3">
-        <v>74.89856613815041</v>
+        <v>73.36600337348303</v>
       </c>
       <c r="E3">
-        <v>-57.957</v>
+        <v>-56.914</v>
       </c>
       <c r="F3">
-        <v>1.043</v>
+        <v>2.086</v>
       </c>
       <c r="G3">
         <v>2.09</v>
@@ -1522,37 +1533,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M3">
-        <v>0.2459394</v>
+        <v>0.4918788</v>
       </c>
       <c r="N3">
-        <v>-6.992606066666666</v>
+        <v>-7.238545466666666</v>
       </c>
       <c r="O3">
-        <v>-1.748151516666667</v>
+        <v>-1.809636366666667</v>
       </c>
       <c r="P3">
-        <v>-5.244454549999999</v>
+        <v>-5.4289091</v>
       </c>
       <c r="Q3">
-        <v>10.95554545</v>
+        <v>10.7710909</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09978297243325665</v>
+        <v>0.1003338190907389</v>
       </c>
       <c r="T3">
-        <v>0.8350994148999304</v>
+        <v>0.8436208375009502</v>
       </c>
       <c r="U3">
         <v>0.2358</v>
       </c>
       <c r="V3">
-        <v>-6.858057987726515</v>
+        <v>-3.429028993863258</v>
       </c>
       <c r="W3">
-        <v>1.852930073505912</v>
+        <v>1.044365036752956</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1560,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>-27.43223195090606</v>
+        <v>-13.71611597545303</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1568,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1192144434439832</v>
+        <v>0.1211144434439832</v>
       </c>
       <c r="C4">
-        <v>73.37000337348303</v>
+        <v>70.85590113311673</v>
       </c>
       <c r="D4">
-        <v>73.36600337348303</v>
+        <v>71.89490113311673</v>
       </c>
       <c r="E4">
-        <v>-56.914</v>
+        <v>-55.871</v>
       </c>
       <c r="F4">
-        <v>2.086</v>
+        <v>3.129</v>
       </c>
       <c r="G4">
         <v>2.09</v>
@@ -1604,37 +1615,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M4">
-        <v>0.4918788</v>
+        <v>0.7378182</v>
       </c>
       <c r="N4">
-        <v>-7.238545466666666</v>
+        <v>-7.484484866666666</v>
       </c>
       <c r="O4">
-        <v>-1.809636366666667</v>
+        <v>-1.871121216666666</v>
       </c>
       <c r="P4">
-        <v>-5.4289091</v>
+        <v>-5.613363649999999</v>
       </c>
       <c r="Q4">
-        <v>10.7710909</v>
+        <v>10.58663635</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1003338190907389</v>
+        <v>0.1008960234112619</v>
       </c>
       <c r="T4">
-        <v>0.8436208375009502</v>
+        <v>0.8523179595370424</v>
       </c>
       <c r="U4">
         <v>0.2358</v>
       </c>
       <c r="V4">
-        <v>-3.429028993863258</v>
+        <v>-2.286019329242172</v>
       </c>
       <c r="W4">
-        <v>1.044365036752956</v>
+        <v>0.7748433578353041</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1642,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>-13.71611597545303</v>
+        <v>-9.144077316968687</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1650,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1211144434439832</v>
+        <v>0.1230144434439832</v>
       </c>
       <c r="C5">
-        <v>70.85590113311673</v>
+        <v>68.39963495639452</v>
       </c>
       <c r="D5">
-        <v>71.89490113311673</v>
+        <v>70.48163495639452</v>
       </c>
       <c r="E5">
-        <v>-55.871</v>
+        <v>-54.828</v>
       </c>
       <c r="F5">
-        <v>3.129</v>
+        <v>4.172</v>
       </c>
       <c r="G5">
         <v>2.09</v>
@@ -1686,37 +1697,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M5">
-        <v>0.7378182</v>
+        <v>0.9837576</v>
       </c>
       <c r="N5">
-        <v>-7.484484866666666</v>
+        <v>-7.730424266666666</v>
       </c>
       <c r="O5">
-        <v>-1.871121216666666</v>
+        <v>-1.932606066666666</v>
       </c>
       <c r="P5">
-        <v>-5.613363649999999</v>
+        <v>-5.797818199999999</v>
       </c>
       <c r="Q5">
-        <v>10.58663635</v>
+        <v>10.4021818</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1008960234112619</v>
+        <v>0.1014699403217959</v>
       </c>
       <c r="T5">
-        <v>0.8523179595370424</v>
+        <v>0.8611962716155533</v>
       </c>
       <c r="U5">
         <v>0.2358</v>
       </c>
       <c r="V5">
-        <v>-2.286019329242172</v>
+        <v>-1.714514496931629</v>
       </c>
       <c r="W5">
-        <v>0.7748433578353041</v>
+        <v>0.640082518376478</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1724,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>-9.144077316968687</v>
+        <v>-6.858057987726515</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1732,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1230144434439832</v>
+        <v>0.1249144434439832</v>
       </c>
       <c r="C6">
-        <v>68.39963495639452</v>
+        <v>65.99785987826505</v>
       </c>
       <c r="D6">
-        <v>70.48163495639452</v>
+        <v>69.12285987826505</v>
       </c>
       <c r="E6">
-        <v>-54.828</v>
+        <v>-53.785</v>
       </c>
       <c r="F6">
-        <v>4.172</v>
+        <v>5.215</v>
       </c>
       <c r="G6">
         <v>2.09</v>
@@ -1768,37 +1779,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M6">
-        <v>0.9837576</v>
+        <v>1.229697</v>
       </c>
       <c r="N6">
-        <v>-7.730424266666666</v>
+        <v>-7.976363666666666</v>
       </c>
       <c r="O6">
-        <v>-1.932606066666666</v>
+        <v>-1.994090916666666</v>
       </c>
       <c r="P6">
-        <v>-5.797818199999999</v>
+        <v>-5.98227275</v>
       </c>
       <c r="Q6">
-        <v>10.4021818</v>
+        <v>10.21772725</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1014699403217959</v>
+        <v>0.1020559396936043</v>
       </c>
       <c r="T6">
-        <v>0.8611962716155533</v>
+        <v>0.870261495527296</v>
       </c>
       <c r="U6">
         <v>0.2358</v>
       </c>
       <c r="V6">
-        <v>-1.714514496931629</v>
+        <v>-1.371611597545303</v>
       </c>
       <c r="W6">
-        <v>0.640082518376478</v>
+        <v>0.5592260147011824</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1806,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>-6.858057987726515</v>
+        <v>-5.486446390181212</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1814,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1249144434439832</v>
+        <v>0.1268144434439832</v>
       </c>
       <c r="C7">
-        <v>65.99785987826505</v>
+        <v>63.64748399766405</v>
       </c>
       <c r="D7">
-        <v>69.12285987826505</v>
+        <v>67.81548399766405</v>
       </c>
       <c r="E7">
-        <v>-53.785</v>
+        <v>-52.742</v>
       </c>
       <c r="F7">
-        <v>5.215</v>
+        <v>6.258</v>
       </c>
       <c r="G7">
         <v>2.09</v>
@@ -1850,37 +1861,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M7">
-        <v>1.229697</v>
+        <v>1.4756364</v>
       </c>
       <c r="N7">
-        <v>-7.976363666666666</v>
+        <v>-8.222303066666665</v>
       </c>
       <c r="O7">
-        <v>-1.994090916666666</v>
+        <v>-2.055575766666666</v>
       </c>
       <c r="P7">
-        <v>-5.98227275</v>
+        <v>-6.166727299999999</v>
       </c>
       <c r="Q7">
-        <v>10.21772725</v>
+        <v>10.0332727</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1020559396936043</v>
+        <v>0.1026544071371533</v>
       </c>
       <c r="T7">
-        <v>0.870261495527296</v>
+        <v>0.8795195965435437</v>
       </c>
       <c r="U7">
         <v>0.2358</v>
       </c>
       <c r="V7">
-        <v>-1.371611597545303</v>
+        <v>-1.143009664621086</v>
       </c>
       <c r="W7">
-        <v>0.5592260147011824</v>
+        <v>0.5053216789176521</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1888,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>-5.486446390181212</v>
+        <v>-4.572038658484343</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1896,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1268144434439832</v>
+        <v>0.1287144434439832</v>
       </c>
       <c r="C8">
-        <v>63.64748399766405</v>
+        <v>61.34564498975023</v>
       </c>
       <c r="D8">
-        <v>67.81548399766405</v>
+        <v>66.55664498975023</v>
       </c>
       <c r="E8">
-        <v>-52.742</v>
+        <v>-51.699</v>
       </c>
       <c r="F8">
-        <v>6.258</v>
+        <v>7.300999999999999</v>
       </c>
       <c r="G8">
         <v>2.09</v>
@@ -1932,37 +1943,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M8">
-        <v>1.4756364</v>
+        <v>1.7215758</v>
       </c>
       <c r="N8">
-        <v>-8.222303066666665</v>
+        <v>-8.468242466666666</v>
       </c>
       <c r="O8">
-        <v>-2.055575766666666</v>
+        <v>-2.117060616666667</v>
       </c>
       <c r="P8">
-        <v>-6.166727299999999</v>
+        <v>-6.35118185</v>
       </c>
       <c r="Q8">
-        <v>10.0332727</v>
+        <v>9.84881815</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1026544071371533</v>
+        <v>0.1032657448483055</v>
       </c>
       <c r="T8">
-        <v>0.8795195965435437</v>
+        <v>0.8889767965063776</v>
       </c>
       <c r="U8">
         <v>0.2358</v>
       </c>
       <c r="V8">
-        <v>-1.143009664621086</v>
+        <v>-0.9797225696752165</v>
       </c>
       <c r="W8">
-        <v>0.5053216789176521</v>
+        <v>0.4668185819294161</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1970,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>-4.572038658484343</v>
+        <v>-3.918890278700866</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1978,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1287144434439832</v>
+        <v>0.1306144434439832</v>
       </c>
       <c r="C9">
-        <v>61.34564498975023</v>
+        <v>59.08968918644533</v>
       </c>
       <c r="D9">
-        <v>66.55664498975023</v>
+        <v>65.34368918644533</v>
       </c>
       <c r="E9">
-        <v>-51.699</v>
+        <v>-50.656</v>
       </c>
       <c r="F9">
-        <v>7.301</v>
+        <v>8.343999999999999</v>
       </c>
       <c r="G9">
         <v>2.09</v>
@@ -2014,37 +2025,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M9">
-        <v>1.7215758</v>
+        <v>1.9675152</v>
       </c>
       <c r="N9">
-        <v>-8.468242466666666</v>
+        <v>-8.714181866666665</v>
       </c>
       <c r="O9">
-        <v>-2.117060616666667</v>
+        <v>-2.178545466666666</v>
       </c>
       <c r="P9">
-        <v>-6.35118185</v>
+        <v>-6.5356364</v>
       </c>
       <c r="Q9">
-        <v>9.84881815</v>
+        <v>9.6643636</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1032657448483055</v>
+        <v>0.1038903725097001</v>
       </c>
       <c r="T9">
-        <v>0.8889767965063776</v>
+        <v>0.8986395877727512</v>
       </c>
       <c r="U9">
         <v>0.2358</v>
       </c>
       <c r="V9">
-        <v>-0.9797225696752164</v>
+        <v>-0.8572572484658144</v>
       </c>
       <c r="W9">
-        <v>0.4668185819294161</v>
+        <v>0.437941259188239</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2052,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>-3.918890278700865</v>
+        <v>-3.429028993863257</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2060,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1306144434439832</v>
+        <v>0.1325144434439832</v>
       </c>
       <c r="C10">
-        <v>59.08968918644533</v>
+        <v>56.87715290350224</v>
       </c>
       <c r="D10">
-        <v>65.34368918644533</v>
+        <v>64.17415290350223</v>
       </c>
       <c r="E10">
-        <v>-50.656</v>
+        <v>-49.613</v>
       </c>
       <c r="F10">
-        <v>8.343999999999999</v>
+        <v>9.386999999999999</v>
       </c>
       <c r="G10">
         <v>2.09</v>
@@ -2096,37 +2107,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M10">
-        <v>1.9675152</v>
+        <v>2.2134546</v>
       </c>
       <c r="N10">
-        <v>-8.714181866666665</v>
+        <v>-8.960121266666667</v>
       </c>
       <c r="O10">
-        <v>-2.178545466666666</v>
+        <v>-2.240030316666667</v>
       </c>
       <c r="P10">
-        <v>-6.5356364</v>
+        <v>-6.720090949999999</v>
       </c>
       <c r="Q10">
-        <v>9.6643636</v>
+        <v>9.47990905</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1038903725097001</v>
+        <v>0.1045287282515649</v>
       </c>
       <c r="T10">
-        <v>0.8986395877727512</v>
+        <v>0.9085147480779463</v>
       </c>
       <c r="U10">
         <v>0.2358</v>
       </c>
       <c r="V10">
-        <v>-0.8572572484658144</v>
+        <v>-0.762006443080724</v>
       </c>
       <c r="W10">
-        <v>0.437941259188239</v>
+        <v>0.4154811192784347</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2134,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>-3.429028993863257</v>
+        <v>-3.048025772322896</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2142,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1325144434439832</v>
+        <v>0.1344144434439832</v>
       </c>
       <c r="C11">
-        <v>56.87715290350224</v>
+        <v>54.70574573758713</v>
       </c>
       <c r="D11">
-        <v>64.17415290350223</v>
+        <v>63.04574573758713</v>
       </c>
       <c r="E11">
-        <v>-49.613</v>
+        <v>-48.57</v>
       </c>
       <c r="F11">
-        <v>9.386999999999999</v>
+        <v>10.43</v>
       </c>
       <c r="G11">
         <v>2.09</v>
@@ -2178,37 +2189,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M11">
-        <v>2.2134546</v>
+        <v>2.459394</v>
       </c>
       <c r="N11">
-        <v>-8.960121266666667</v>
+        <v>-9.206060666666666</v>
       </c>
       <c r="O11">
-        <v>-2.240030316666667</v>
+        <v>-2.301515166666666</v>
       </c>
       <c r="P11">
-        <v>-6.720090949999999</v>
+        <v>-6.904545499999999</v>
       </c>
       <c r="Q11">
-        <v>9.47990905</v>
+        <v>9.2954545</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1045287282515649</v>
+        <v>0.1051812696765823</v>
       </c>
       <c r="T11">
-        <v>0.9085147480779463</v>
+        <v>0.9186093563899235</v>
       </c>
       <c r="U11">
         <v>0.2358</v>
       </c>
       <c r="V11">
-        <v>-0.762006443080724</v>
+        <v>-0.6858057987726515</v>
       </c>
       <c r="W11">
-        <v>0.4154811192784347</v>
+        <v>0.3975130073505912</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2216,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>-3.048025772322896</v>
+        <v>-2.743223195090606</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2224,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1344144434439832</v>
+        <v>0.1363144434439832</v>
       </c>
       <c r="C12">
-        <v>54.70574573758712</v>
+        <v>52.57333559508838</v>
       </c>
       <c r="D12">
-        <v>63.04574573758711</v>
+        <v>61.95633559508838</v>
       </c>
       <c r="E12">
-        <v>-48.57</v>
+        <v>-47.527</v>
       </c>
       <c r="F12">
-        <v>10.43</v>
+        <v>11.473</v>
       </c>
       <c r="G12">
         <v>2.09</v>
@@ -2260,37 +2271,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M12">
-        <v>2.459394</v>
+        <v>2.7053334</v>
       </c>
       <c r="N12">
-        <v>-9.206060666666666</v>
+        <v>-9.452000066666667</v>
       </c>
       <c r="O12">
-        <v>-2.301515166666666</v>
+        <v>-2.363000016666667</v>
       </c>
       <c r="P12">
-        <v>-6.904545499999999</v>
+        <v>-7.08900005</v>
       </c>
       <c r="Q12">
-        <v>9.2954545</v>
+        <v>9.11099995</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1051812696765823</v>
+        <v>0.1058484749538473</v>
       </c>
       <c r="T12">
-        <v>0.9186093563899235</v>
+        <v>0.928930809832507</v>
       </c>
       <c r="U12">
         <v>0.2358</v>
       </c>
       <c r="V12">
-        <v>-0.6858057987726515</v>
+        <v>-0.6234598170660469</v>
       </c>
       <c r="W12">
-        <v>0.3975130073505912</v>
+        <v>0.3828118248641739</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2298,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>-2.743223195090606</v>
+        <v>-2.493839268264188</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2306,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1363144434439832</v>
+        <v>0.1382144434439832</v>
       </c>
       <c r="C13">
-        <v>52.57333559508838</v>
+        <v>50.47793524674371</v>
       </c>
       <c r="D13">
-        <v>61.95633559508838</v>
+        <v>60.9039352467437</v>
       </c>
       <c r="E13">
-        <v>-47.527</v>
+        <v>-46.484</v>
       </c>
       <c r="F13">
-        <v>11.473</v>
+        <v>12.516</v>
       </c>
       <c r="G13">
         <v>2.09</v>
@@ -2342,37 +2353,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M13">
-        <v>2.7053334</v>
+        <v>2.9512728</v>
       </c>
       <c r="N13">
-        <v>-9.452000066666667</v>
+        <v>-9.697939466666666</v>
       </c>
       <c r="O13">
-        <v>-2.363000016666667</v>
+        <v>-2.424484866666667</v>
       </c>
       <c r="P13">
-        <v>-7.08900005</v>
+        <v>-7.273454599999999</v>
       </c>
       <c r="Q13">
-        <v>9.11099995</v>
+        <v>8.9265454</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1058484749538473</v>
+        <v>0.1065308439874137</v>
       </c>
       <c r="T13">
-        <v>0.928930809832507</v>
+        <v>0.9394868417624217</v>
       </c>
       <c r="U13">
         <v>0.2358</v>
       </c>
       <c r="V13">
-        <v>-0.6234598170660469</v>
+        <v>-0.5715048323105429</v>
       </c>
       <c r="W13">
-        <v>0.3828118248641739</v>
+        <v>0.3705608394588261</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2380,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>-2.493839268264188</v>
+        <v>-2.286019329242172</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2388,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1382144434439832</v>
+        <v>0.1401144434439832</v>
       </c>
       <c r="C14">
-        <v>50.47793524674371</v>
+        <v>48.41769022969116</v>
       </c>
       <c r="D14">
-        <v>60.9039352467437</v>
+        <v>59.88669022969116</v>
       </c>
       <c r="E14">
-        <v>-46.484</v>
+        <v>-45.441</v>
       </c>
       <c r="F14">
-        <v>12.516</v>
+        <v>13.559</v>
       </c>
       <c r="G14">
         <v>2.09</v>
@@ -2424,37 +2435,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M14">
-        <v>2.9512728</v>
+        <v>3.1972122</v>
       </c>
       <c r="N14">
-        <v>-9.697939466666666</v>
+        <v>-9.943878866666665</v>
       </c>
       <c r="O14">
-        <v>-2.424484866666667</v>
+        <v>-2.485969716666666</v>
       </c>
       <c r="P14">
-        <v>-7.273454599999999</v>
+        <v>-7.457909149999999</v>
       </c>
       <c r="Q14">
-        <v>8.9265454</v>
+        <v>8.74209085</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1065308439874137</v>
+        <v>0.10722889966543</v>
       </c>
       <c r="T14">
-        <v>0.9394868417624217</v>
+        <v>0.9502855410930244</v>
       </c>
       <c r="U14">
         <v>0.2358</v>
       </c>
       <c r="V14">
-        <v>-0.5715048323105429</v>
+        <v>-0.5275429221328088</v>
       </c>
       <c r="W14">
-        <v>0.3705608394588261</v>
+        <v>0.3601946210389163</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2462,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>-2.286019329242172</v>
+        <v>-2.110171688531235</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2470,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1401144434439832</v>
+        <v>0.1420144434439832</v>
       </c>
       <c r="C15">
-        <v>48.41769022969116</v>
+        <v>46.39086794199584</v>
       </c>
       <c r="D15">
-        <v>59.88669022969116</v>
+        <v>58.90286794199584</v>
       </c>
       <c r="E15">
-        <v>-45.441</v>
+        <v>-44.398</v>
       </c>
       <c r="F15">
-        <v>13.559</v>
+        <v>14.602</v>
       </c>
       <c r="G15">
         <v>2.09</v>
@@ -2506,37 +2517,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M15">
-        <v>3.1972122</v>
+        <v>3.4431516</v>
       </c>
       <c r="N15">
-        <v>-9.943878866666665</v>
+        <v>-10.18981826666667</v>
       </c>
       <c r="O15">
-        <v>-2.485969716666666</v>
+        <v>-2.547454566666667</v>
       </c>
       <c r="P15">
-        <v>-7.457909149999999</v>
+        <v>-7.6423637</v>
       </c>
       <c r="Q15">
-        <v>8.74209085</v>
+        <v>8.557636299999999</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.10722889966543</v>
+        <v>0.1079431891964234</v>
       </c>
       <c r="T15">
-        <v>0.9502855410930244</v>
+        <v>0.9613353729661991</v>
       </c>
       <c r="U15">
         <v>0.2358</v>
       </c>
       <c r="V15">
-        <v>-0.5275429221328088</v>
+        <v>-0.4898612848376082</v>
       </c>
       <c r="W15">
-        <v>0.3601946210389163</v>
+        <v>0.351309290964708</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2544,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>-2.110171688531235</v>
+        <v>-1.959445139350433</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2552,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1420144434439832</v>
+        <v>0.1439144434439832</v>
       </c>
       <c r="C16">
-        <v>46.39086794199584</v>
+        <v>44.39584779473726</v>
       </c>
       <c r="D16">
-        <v>58.90286794199584</v>
+        <v>57.95084779473726</v>
       </c>
       <c r="E16">
-        <v>-44.398</v>
+        <v>-43.355</v>
       </c>
       <c r="F16">
-        <v>14.602</v>
+        <v>15.645</v>
       </c>
       <c r="G16">
         <v>2.09</v>
@@ -2588,37 +2599,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M16">
-        <v>3.4431516</v>
+        <v>3.689091</v>
       </c>
       <c r="N16">
-        <v>-10.18981826666667</v>
+        <v>-10.43575766666667</v>
       </c>
       <c r="O16">
-        <v>-2.547454566666667</v>
+        <v>-2.608939416666667</v>
       </c>
       <c r="P16">
-        <v>-7.6423637</v>
+        <v>-7.826818250000001</v>
       </c>
       <c r="Q16">
-        <v>8.557636299999999</v>
+        <v>8.373181749999999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1079431891964234</v>
+        <v>0.1086742855399107</v>
       </c>
       <c r="T16">
-        <v>0.9613353729661991</v>
+        <v>0.9726452008834484</v>
       </c>
       <c r="U16">
         <v>0.2358</v>
       </c>
       <c r="V16">
-        <v>-0.4898612848376082</v>
+        <v>-0.4572038658484343</v>
       </c>
       <c r="W16">
-        <v>0.351309290964708</v>
+        <v>0.3436086715670608</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2626,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>-1.959445139350433</v>
+        <v>-1.828815463393738</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2634,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1439144434439832</v>
+        <v>0.1458144434439832</v>
       </c>
       <c r="C17">
-        <v>44.39584779473726</v>
+        <v>42.43111230391088</v>
       </c>
       <c r="D17">
-        <v>57.95084779473726</v>
+        <v>57.02911230391089</v>
       </c>
       <c r="E17">
-        <v>-43.355</v>
+        <v>-42.312</v>
       </c>
       <c r="F17">
-        <v>15.645</v>
+        <v>16.688</v>
       </c>
       <c r="G17">
         <v>2.09</v>
@@ -2670,37 +2681,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M17">
-        <v>3.689091</v>
+        <v>3.9350304</v>
       </c>
       <c r="N17">
-        <v>-10.43575766666667</v>
+        <v>-10.68169706666667</v>
       </c>
       <c r="O17">
-        <v>-2.608939416666666</v>
+        <v>-2.670424266666667</v>
       </c>
       <c r="P17">
-        <v>-7.826818249999999</v>
+        <v>-8.0112728</v>
       </c>
       <c r="Q17">
-        <v>8.373181750000001</v>
+        <v>8.188727199999999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1086742855399107</v>
+        <v>0.1094227889391954</v>
       </c>
       <c r="T17">
-        <v>0.9726452008834484</v>
+        <v>0.9842243104177751</v>
       </c>
       <c r="U17">
         <v>0.2358</v>
       </c>
       <c r="V17">
-        <v>-0.4572038658484344</v>
+        <v>-0.4286286242329072</v>
       </c>
       <c r="W17">
-        <v>0.3436086715670608</v>
+        <v>0.3368706295941195</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2708,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>-1.828815463393737</v>
+        <v>-1.714514496931629</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2716,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1458144434439832</v>
+        <v>0.1477144434439832</v>
       </c>
       <c r="C18">
-        <v>42.43111230391088</v>
+        <v>40.49523901914494</v>
       </c>
       <c r="D18">
-        <v>57.02911230391089</v>
+        <v>56.13623901914494</v>
       </c>
       <c r="E18">
-        <v>-42.312</v>
+        <v>-41.269</v>
       </c>
       <c r="F18">
-        <v>16.688</v>
+        <v>17.731</v>
       </c>
       <c r="G18">
         <v>2.09</v>
@@ -2752,37 +2763,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M18">
-        <v>3.9350304</v>
+        <v>4.180969800000001</v>
       </c>
       <c r="N18">
-        <v>-10.68169706666667</v>
+        <v>-10.92763646666667</v>
       </c>
       <c r="O18">
-        <v>-2.670424266666667</v>
+        <v>-2.731909116666666</v>
       </c>
       <c r="P18">
-        <v>-8.0112728</v>
+        <v>-8.195727349999999</v>
       </c>
       <c r="Q18">
-        <v>8.188727199999999</v>
+        <v>8.004272650000001</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1094227889391954</v>
+        <v>0.1101893285649688</v>
       </c>
       <c r="T18">
-        <v>0.9842243104177751</v>
+        <v>0.9960824346396761</v>
       </c>
       <c r="U18">
         <v>0.2358</v>
       </c>
       <c r="V18">
-        <v>-0.4286286242329072</v>
+        <v>-0.4034151757486185</v>
       </c>
       <c r="W18">
-        <v>0.3368706295941195</v>
+        <v>0.3309252984415242</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2790,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>-1.714514496931629</v>
+        <v>-1.613660702994474</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2798,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1477144434439832</v>
+        <v>0.1496144434439832</v>
       </c>
       <c r="C19">
-        <v>40.49523901914494</v>
+        <v>38.58689319893486</v>
       </c>
       <c r="D19">
-        <v>56.13623901914494</v>
+        <v>55.27089319893486</v>
       </c>
       <c r="E19">
-        <v>-41.269</v>
+        <v>-40.226</v>
       </c>
       <c r="F19">
-        <v>17.731</v>
+        <v>18.774</v>
       </c>
       <c r="G19">
         <v>2.09</v>
@@ -2834,37 +2845,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M19">
-        <v>4.180969800000001</v>
+        <v>4.426909200000001</v>
       </c>
       <c r="N19">
-        <v>-10.92763646666667</v>
+        <v>-11.17357586666667</v>
       </c>
       <c r="O19">
-        <v>-2.731909116666666</v>
+        <v>-2.793393966666667</v>
       </c>
       <c r="P19">
-        <v>-8.195727349999999</v>
+        <v>-8.3801819</v>
       </c>
       <c r="Q19">
-        <v>8.004272650000001</v>
+        <v>7.819818099999999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1101893285649688</v>
+        <v>0.1109745642791757</v>
       </c>
       <c r="T19">
-        <v>0.9960824346396761</v>
+        <v>1.008229781403575</v>
       </c>
       <c r="U19">
         <v>0.2358</v>
       </c>
       <c r="V19">
-        <v>-0.4034151757486185</v>
+        <v>-0.3810032215403619</v>
       </c>
       <c r="W19">
-        <v>0.3309252984415242</v>
+        <v>0.3256405596392173</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2872,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>-1.613660702994474</v>
+        <v>-1.524012886161448</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2880,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1496144434439832</v>
+        <v>0.1515144434439832</v>
       </c>
       <c r="C20">
-        <v>38.58689319893483</v>
+        <v>36.70482115306508</v>
       </c>
       <c r="D20">
-        <v>55.27089319893484</v>
+        <v>54.43182115306508</v>
       </c>
       <c r="E20">
-        <v>-40.226</v>
+        <v>-39.183</v>
       </c>
       <c r="F20">
-        <v>18.774</v>
+        <v>19.817</v>
       </c>
       <c r="G20">
         <v>2.09</v>
@@ -2916,37 +2927,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M20">
-        <v>4.4269092</v>
+        <v>4.6728486</v>
       </c>
       <c r="N20">
-        <v>-11.17357586666667</v>
+        <v>-11.41951526666667</v>
       </c>
       <c r="O20">
-        <v>-2.793393966666667</v>
+        <v>-2.854878816666667</v>
       </c>
       <c r="P20">
-        <v>-8.3801819</v>
+        <v>-8.56463645</v>
       </c>
       <c r="Q20">
-        <v>7.819818099999999</v>
+        <v>7.635363549999999</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1109745642791757</v>
+        <v>0.1117791885295359</v>
       </c>
       <c r="T20">
-        <v>1.008229781403575</v>
+        <v>1.020677062655471</v>
       </c>
       <c r="U20">
         <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>-0.381003221540362</v>
+        <v>-0.3609504204066587</v>
       </c>
       <c r="W20">
-        <v>0.3256405596392174</v>
+        <v>0.3209121091318901</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2954,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>-1.524012886161448</v>
+        <v>-1.443801681626635</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2962,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1515144434439832</v>
+        <v>0.1534144434439833</v>
       </c>
       <c r="C21">
-        <v>36.70482115306508</v>
+        <v>34.84784418237807</v>
       </c>
       <c r="D21">
-        <v>54.43182115306508</v>
+        <v>53.61784418237807</v>
       </c>
       <c r="E21">
-        <v>-39.183</v>
+        <v>-38.14</v>
       </c>
       <c r="F21">
-        <v>19.817</v>
+        <v>20.86</v>
       </c>
       <c r="G21">
         <v>2.09</v>
@@ -2998,37 +3009,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M21">
-        <v>4.6728486</v>
+        <v>4.918788</v>
       </c>
       <c r="N21">
-        <v>-11.41951526666667</v>
+        <v>-11.66545466666667</v>
       </c>
       <c r="O21">
-        <v>-2.854878816666667</v>
+        <v>-2.916363666666666</v>
       </c>
       <c r="P21">
-        <v>-8.56463645</v>
+        <v>-8.749091</v>
       </c>
       <c r="Q21">
-        <v>7.635363549999999</v>
+        <v>7.450908999999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1117791885295359</v>
+        <v>0.1126039283861551</v>
       </c>
       <c r="T21">
-        <v>1.020677062655471</v>
+        <v>1.033435525938664</v>
       </c>
       <c r="U21">
         <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>-0.3609504204066587</v>
+        <v>-0.3429028993863257</v>
       </c>
       <c r="W21">
-        <v>0.3209121091318901</v>
+        <v>0.3166565036752956</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3036,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>-1.443801681626635</v>
+        <v>-1.371611597545303</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3044,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1534144434439833</v>
+        <v>0.1553144434439832</v>
       </c>
       <c r="C22">
-        <v>34.84784418237807</v>
+        <v>33.0148530542822</v>
       </c>
       <c r="D22">
-        <v>53.61784418237807</v>
+        <v>52.8278530542822</v>
       </c>
       <c r="E22">
-        <v>-38.14</v>
+        <v>-37.09699999999999</v>
       </c>
       <c r="F22">
-        <v>20.86</v>
+        <v>21.903</v>
       </c>
       <c r="G22">
         <v>2.09</v>
@@ -3080,37 +3091,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M22">
-        <v>4.918788</v>
+        <v>5.1647274</v>
       </c>
       <c r="N22">
-        <v>-11.66545466666667</v>
+        <v>-11.91139406666667</v>
       </c>
       <c r="O22">
-        <v>-2.916363666666666</v>
+        <v>-2.977848516666667</v>
       </c>
       <c r="P22">
-        <v>-8.749091</v>
+        <v>-8.93354555</v>
       </c>
       <c r="Q22">
-        <v>7.450908999999999</v>
+        <v>7.266454449999999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1126039283861551</v>
+        <v>0.1134495477328153</v>
       </c>
       <c r="T22">
-        <v>1.033435525938664</v>
+        <v>1.046516988292318</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>-0.3429028993863257</v>
+        <v>-0.3265741898917388</v>
       </c>
       <c r="W22">
-        <v>0.3166565036752956</v>
+        <v>0.312806193976472</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3118,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>-1.371611597545303</v>
+        <v>-1.306296759566955</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3126,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1553144434439832</v>
+        <v>0.1572144434439832</v>
       </c>
       <c r="C23">
-        <v>33.01485305428222</v>
+        <v>31.20480295954702</v>
       </c>
       <c r="D23">
-        <v>52.82785305428222</v>
+        <v>52.06080295954702</v>
       </c>
       <c r="E23">
-        <v>-37.097</v>
+        <v>-36.054</v>
       </c>
       <c r="F23">
-        <v>21.903</v>
+        <v>22.946</v>
       </c>
       <c r="G23">
         <v>2.09</v>
@@ -3162,37 +3173,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M23">
-        <v>5.1647274</v>
+        <v>5.4106668</v>
       </c>
       <c r="N23">
-        <v>-11.91139406666667</v>
+        <v>-12.15733346666667</v>
       </c>
       <c r="O23">
-        <v>-2.977848516666667</v>
+        <v>-3.039333366666666</v>
       </c>
       <c r="P23">
-        <v>-8.93354555</v>
+        <v>-9.1180001</v>
       </c>
       <c r="Q23">
-        <v>7.266454449999999</v>
+        <v>7.0819999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1134495477328153</v>
+        <v>0.1143168496268258</v>
       </c>
       <c r="T23">
-        <v>1.046516988292318</v>
+        <v>1.059933872757604</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>-0.3265741898917388</v>
+        <v>-0.3117299085330235</v>
       </c>
       <c r="W23">
-        <v>0.312806193976472</v>
+        <v>0.3093059124320869</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3200,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>-1.306296759566955</v>
+        <v>-1.246919634132094</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3208,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1572144434439832</v>
+        <v>0.1591144434439832</v>
       </c>
       <c r="C24">
-        <v>31.20480295954702</v>
+        <v>29.41670890216851</v>
       </c>
       <c r="D24">
-        <v>52.06080295954702</v>
+        <v>51.31570890216851</v>
       </c>
       <c r="E24">
-        <v>-36.054</v>
+        <v>-35.011</v>
       </c>
       <c r="F24">
-        <v>22.946</v>
+        <v>23.989</v>
       </c>
       <c r="G24">
         <v>2.09</v>
@@ -3244,37 +3255,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M24">
-        <v>5.4106668</v>
+        <v>5.656606200000001</v>
       </c>
       <c r="N24">
-        <v>-12.15733346666667</v>
+        <v>-12.40327286666667</v>
       </c>
       <c r="O24">
-        <v>-3.039333366666666</v>
+        <v>-3.100818216666667</v>
       </c>
       <c r="P24">
-        <v>-9.1180001</v>
+        <v>-9.30245465</v>
       </c>
       <c r="Q24">
-        <v>7.0819999</v>
+        <v>6.89754535</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1143168496268258</v>
+        <v>0.1152066788427586</v>
       </c>
       <c r="T24">
-        <v>1.059933872757604</v>
+        <v>1.073699247728482</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>-0.3117299085330235</v>
+        <v>-0.2981764342489789</v>
       </c>
       <c r="W24">
-        <v>0.3093059124320869</v>
+        <v>0.3061100031959092</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3282,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>-1.246919634132094</v>
+        <v>-1.192705736995916</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3290,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1591144434439832</v>
+        <v>0.1610144434439832</v>
       </c>
       <c r="C25">
-        <v>29.41670890216851</v>
+        <v>27.64964147952974</v>
       </c>
       <c r="D25">
-        <v>51.31570890216851</v>
+        <v>50.59164147952974</v>
       </c>
       <c r="E25">
-        <v>-35.011</v>
+        <v>-33.968</v>
       </c>
       <c r="F25">
-        <v>23.989</v>
+        <v>25.032</v>
       </c>
       <c r="G25">
         <v>2.09</v>
@@ -3326,37 +3337,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M25">
-        <v>5.656606200000001</v>
+        <v>5.9025456</v>
       </c>
       <c r="N25">
-        <v>-12.40327286666667</v>
+        <v>-12.64921226666667</v>
       </c>
       <c r="O25">
-        <v>-3.100818216666667</v>
+        <v>-3.162303066666666</v>
       </c>
       <c r="P25">
-        <v>-9.30245465</v>
+        <v>-9.486909199999999</v>
       </c>
       <c r="Q25">
-        <v>6.89754535</v>
+        <v>6.7130908</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1152066788427586</v>
+        <v>0.1161199246170054</v>
       </c>
       <c r="T25">
-        <v>1.073699247728482</v>
+        <v>1.08782686940912</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>-0.2981764342489789</v>
+        <v>-0.2857524161552715</v>
       </c>
       <c r="W25">
-        <v>0.3061100031959092</v>
+        <v>0.3031804197294131</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3364,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>-1.192705736995916</v>
+        <v>-1.143009664621086</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3372,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1610144434439832</v>
+        <v>0.1629144434439832</v>
       </c>
       <c r="C26">
-        <v>27.64964147952976</v>
+        <v>25.90272301484405</v>
       </c>
       <c r="D26">
-        <v>50.59164147952976</v>
+        <v>49.88772301484405</v>
       </c>
       <c r="E26">
-        <v>-33.968</v>
+        <v>-32.925</v>
       </c>
       <c r="F26">
-        <v>25.032</v>
+        <v>26.075</v>
       </c>
       <c r="G26">
         <v>2.09</v>
@@ -3408,37 +3419,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M26">
-        <v>5.9025456</v>
+        <v>6.148485</v>
       </c>
       <c r="N26">
-        <v>-12.64921226666667</v>
+        <v>-12.89515166666667</v>
       </c>
       <c r="O26">
-        <v>-3.162303066666666</v>
+        <v>-3.223787916666667</v>
       </c>
       <c r="P26">
-        <v>-9.486909199999999</v>
+        <v>-9.671363750000001</v>
       </c>
       <c r="Q26">
-        <v>6.7130908</v>
+        <v>6.528636249999998</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1161199246170054</v>
+        <v>0.1170575236118988</v>
       </c>
       <c r="T26">
-        <v>1.08782686940912</v>
+        <v>1.102331227667908</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>-0.2857524161552715</v>
+        <v>-0.2743223195090606</v>
       </c>
       <c r="W26">
-        <v>0.3031804197294131</v>
+        <v>0.3004852029402365</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3446,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>-1.143009664621086</v>
+        <v>-1.097289278036242</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3454,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1629144434439832</v>
+        <v>0.1648144434439832</v>
       </c>
       <c r="C27">
-        <v>25.90272301484405</v>
+        <v>24.17512400803984</v>
       </c>
       <c r="D27">
-        <v>49.88772301484405</v>
+        <v>49.20312400803984</v>
       </c>
       <c r="E27">
-        <v>-32.925</v>
+        <v>-31.882</v>
       </c>
       <c r="F27">
-        <v>26.075</v>
+        <v>27.118</v>
       </c>
       <c r="G27">
         <v>2.09</v>
@@ -3490,37 +3501,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M27">
-        <v>6.148485</v>
+        <v>6.3944244</v>
       </c>
       <c r="N27">
-        <v>-12.89515166666667</v>
+        <v>-13.14109106666667</v>
       </c>
       <c r="O27">
-        <v>-3.223787916666667</v>
+        <v>-3.285272766666667</v>
       </c>
       <c r="P27">
-        <v>-9.671363750000001</v>
+        <v>-9.855818299999999</v>
       </c>
       <c r="Q27">
-        <v>6.528636249999998</v>
+        <v>6.3441817</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1170575236118988</v>
+        <v>0.1180204631201677</v>
       </c>
       <c r="T27">
-        <v>1.102331227667908</v>
+        <v>1.117227595609366</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>-0.2743223195090606</v>
+        <v>-0.2637714610664044</v>
       </c>
       <c r="W27">
-        <v>0.3004852029402365</v>
+        <v>0.2979973105194582</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3528,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>-1.097289278036242</v>
+        <v>-1.055085844265618</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3536,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1648144434439832</v>
+        <v>0.1667144434439832</v>
       </c>
       <c r="C28">
-        <v>24.17512400803984</v>
+        <v>22.46605987491284</v>
       </c>
       <c r="D28">
-        <v>49.20312400803984</v>
+        <v>48.53705987491285</v>
       </c>
       <c r="E28">
-        <v>-31.882</v>
+        <v>-30.839</v>
       </c>
       <c r="F28">
-        <v>27.118</v>
+        <v>28.161</v>
       </c>
       <c r="G28">
         <v>2.09</v>
@@ -3572,37 +3583,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M28">
-        <v>6.3944244</v>
+        <v>6.6403638</v>
       </c>
       <c r="N28">
-        <v>-13.14109106666667</v>
+        <v>-13.38703046666667</v>
       </c>
       <c r="O28">
-        <v>-3.285272766666667</v>
+        <v>-3.346757616666666</v>
       </c>
       <c r="P28">
-        <v>-9.855818299999999</v>
+        <v>-10.04027285</v>
       </c>
       <c r="Q28">
-        <v>6.3441817</v>
+        <v>6.15972715</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1180204631201677</v>
+        <v>0.1190097845327727</v>
       </c>
       <c r="T28">
-        <v>1.117227595609366</v>
+        <v>1.132532083220454</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>-0.2637714610664044</v>
+        <v>-0.2540021476935747</v>
       </c>
       <c r="W28">
-        <v>0.2979973105194582</v>
+        <v>0.2956937064261449</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3610,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>-1.055085844265618</v>
+        <v>-1.016008590774298</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3618,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1667144434439832</v>
+        <v>0.1686144434439832</v>
       </c>
       <c r="C29">
-        <v>22.46605987491284</v>
+        <v>20.77478794759369</v>
       </c>
       <c r="D29">
-        <v>48.53705987491285</v>
+        <v>47.88878794759369</v>
       </c>
       <c r="E29">
-        <v>-30.839</v>
+        <v>-29.796</v>
       </c>
       <c r="F29">
-        <v>28.161</v>
+        <v>29.204</v>
       </c>
       <c r="G29">
         <v>2.09</v>
@@ -3654,37 +3665,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M29">
-        <v>6.6403638</v>
+        <v>6.8863032</v>
       </c>
       <c r="N29">
-        <v>-13.38703046666667</v>
+        <v>-13.63296986666667</v>
       </c>
       <c r="O29">
-        <v>-3.346757616666666</v>
+        <v>-3.408242466666667</v>
       </c>
       <c r="P29">
-        <v>-10.04027285</v>
+        <v>-10.2247274</v>
       </c>
       <c r="Q29">
-        <v>6.15972715</v>
+        <v>5.9752726</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1190097845327727</v>
+        <v>0.1200265870957279</v>
       </c>
       <c r="T29">
-        <v>1.132532083220454</v>
+        <v>1.148261695487405</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>-0.2540021476935747</v>
+        <v>-0.2449306424188041</v>
       </c>
       <c r="W29">
-        <v>0.2956937064261449</v>
+        <v>0.293554645482354</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3692,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>-1.016008590774298</v>
+        <v>-0.9797225696752163</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3700,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1686144434439832</v>
+        <v>0.1705144434439833</v>
       </c>
       <c r="C30">
-        <v>20.77478794759369</v>
+        <v>19.10060471222192</v>
       </c>
       <c r="D30">
-        <v>47.88878794759369</v>
+        <v>47.25760471222193</v>
       </c>
       <c r="E30">
-        <v>-29.796</v>
+        <v>-28.753</v>
       </c>
       <c r="F30">
-        <v>29.204</v>
+        <v>30.247</v>
       </c>
       <c r="G30">
         <v>2.09</v>
@@ -3736,37 +3747,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M30">
-        <v>6.8863032</v>
+        <v>7.132242600000001</v>
       </c>
       <c r="N30">
-        <v>-13.63296986666667</v>
+        <v>-13.87890926666667</v>
       </c>
       <c r="O30">
-        <v>-3.408242466666667</v>
+        <v>-3.469727316666667</v>
       </c>
       <c r="P30">
-        <v>-10.2247274</v>
+        <v>-10.40918195</v>
       </c>
       <c r="Q30">
-        <v>5.9752726</v>
+        <v>5.790818049999999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1200265870957279</v>
+        <v>0.1210720319844001</v>
       </c>
       <c r="T30">
-        <v>1.148261695487405</v>
+        <v>1.164434395423847</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>-0.2449306424188041</v>
+        <v>-0.236484758197466</v>
       </c>
       <c r="W30">
-        <v>0.293554645482354</v>
+        <v>0.2915631059829625</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3774,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>-0.9797225696752163</v>
+        <v>-0.945939032789864</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3782,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1705144434439832</v>
+        <v>0.1724144434439832</v>
       </c>
       <c r="C31">
-        <v>19.10060471222195</v>
+        <v>17.44284326222645</v>
       </c>
       <c r="D31">
-        <v>47.25760471222195</v>
+        <v>46.64284326222646</v>
       </c>
       <c r="E31">
-        <v>-28.753</v>
+        <v>-27.71</v>
       </c>
       <c r="F31">
-        <v>30.247</v>
+        <v>31.29</v>
       </c>
       <c r="G31">
         <v>2.09</v>
@@ -3818,37 +3829,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M31">
-        <v>7.1322426</v>
+        <v>7.378182</v>
       </c>
       <c r="N31">
-        <v>-13.87890926666667</v>
+        <v>-14.12484866666667</v>
       </c>
       <c r="O31">
-        <v>-3.469727316666666</v>
+        <v>-3.531212166666666</v>
       </c>
       <c r="P31">
-        <v>-10.40918195</v>
+        <v>-10.5936365</v>
       </c>
       <c r="Q31">
-        <v>5.79081805</v>
+        <v>5.6063635</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1210720319844001</v>
+        <v>0.1221473467270344</v>
       </c>
       <c r="T31">
-        <v>1.164434395423847</v>
+        <v>1.18106917250133</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>-0.2364847581974661</v>
+        <v>-0.2286019329242172</v>
       </c>
       <c r="W31">
-        <v>0.2915631059829625</v>
+        <v>0.2897043357835304</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3856,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>-0.9459390327898642</v>
+        <v>-0.9144077316968686</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3864,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1724144434439832</v>
+        <v>0.1743144434439832</v>
       </c>
       <c r="C32">
-        <v>17.44284326222645</v>
+        <v>15.8008709478304</v>
       </c>
       <c r="D32">
-        <v>46.64284326222646</v>
+        <v>46.0438709478304</v>
       </c>
       <c r="E32">
-        <v>-27.71</v>
+        <v>-26.667</v>
       </c>
       <c r="F32">
-        <v>31.29</v>
+        <v>32.333</v>
       </c>
       <c r="G32">
         <v>2.09</v>
@@ -3900,37 +3911,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M32">
-        <v>7.378182</v>
+        <v>7.6241214</v>
       </c>
       <c r="N32">
-        <v>-14.12484866666667</v>
+        <v>-14.37078806666667</v>
       </c>
       <c r="O32">
-        <v>-3.531212166666666</v>
+        <v>-3.592697016666667</v>
       </c>
       <c r="P32">
-        <v>-10.5936365</v>
+        <v>-10.77809105</v>
       </c>
       <c r="Q32">
-        <v>5.6063635</v>
+        <v>5.421908949999999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1221473467270344</v>
+        <v>0.1232538300129335</v>
       </c>
       <c r="T32">
-        <v>1.18106917250133</v>
+        <v>1.198186117030335</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>-0.2286019329242172</v>
+        <v>-0.221227677023436</v>
       </c>
       <c r="W32">
-        <v>0.2897043357835304</v>
+        <v>0.2879654862421263</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3938,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>-0.9144077316968686</v>
+        <v>-0.8849107080937439</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3946,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1743144434439832</v>
+        <v>0.1762144434439832</v>
       </c>
       <c r="C33">
-        <v>15.8008709478304</v>
+        <v>14.17408720436601</v>
       </c>
       <c r="D33">
-        <v>46.0438709478304</v>
+        <v>45.460087204366</v>
       </c>
       <c r="E33">
-        <v>-26.667</v>
+        <v>-25.624</v>
       </c>
       <c r="F33">
-        <v>32.333</v>
+        <v>33.376</v>
       </c>
       <c r="G33">
         <v>2.09</v>
@@ -3982,37 +3993,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M33">
-        <v>7.6241214</v>
+        <v>7.8700608</v>
       </c>
       <c r="N33">
-        <v>-14.37078806666667</v>
+        <v>-14.61672746666667</v>
       </c>
       <c r="O33">
-        <v>-3.592697016666667</v>
+        <v>-3.654181866666667</v>
       </c>
       <c r="P33">
-        <v>-10.77809105</v>
+        <v>-10.9625456</v>
       </c>
       <c r="Q33">
-        <v>5.421908949999999</v>
+        <v>5.237454399999999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1232538300129335</v>
+        <v>0.1243928569248884</v>
       </c>
       <c r="T33">
-        <v>1.198186117030335</v>
+        <v>1.215806501104311</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>-0.221227677023436</v>
+        <v>-0.2143143121164536</v>
       </c>
       <c r="W33">
-        <v>0.2879654862421263</v>
+        <v>0.2863353147970598</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4020,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>-0.8849107080937439</v>
+        <v>-0.8572572484658145</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4028,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1762144434439832</v>
+        <v>0.1781144434439832</v>
       </c>
       <c r="C34">
-        <v>14.17408720436601</v>
+        <v>12.56192154372776</v>
       </c>
       <c r="D34">
-        <v>45.460087204366</v>
+        <v>44.89092154372776</v>
       </c>
       <c r="E34">
-        <v>-25.624</v>
+        <v>-24.581</v>
       </c>
       <c r="F34">
-        <v>33.376</v>
+        <v>34.419</v>
       </c>
       <c r="G34">
         <v>2.09</v>
@@ -4064,37 +4075,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M34">
-        <v>7.8700608</v>
+        <v>8.116000200000002</v>
       </c>
       <c r="N34">
-        <v>-14.61672746666667</v>
+        <v>-14.86266686666667</v>
       </c>
       <c r="O34">
-        <v>-3.654181866666667</v>
+        <v>-3.715666716666667</v>
       </c>
       <c r="P34">
-        <v>-10.9625456</v>
+        <v>-11.14700015</v>
       </c>
       <c r="Q34">
-        <v>5.237454399999999</v>
+        <v>5.052999849999999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1243928569248884</v>
+        <v>0.1255658846401852</v>
       </c>
       <c r="T34">
-        <v>1.215806501104311</v>
+        <v>1.233952866792435</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>-0.2143143121164536</v>
+        <v>-0.2078199390220156</v>
       </c>
       <c r="W34">
-        <v>0.2863353147970598</v>
+        <v>0.2848039416213913</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4102,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>-0.8572572484658145</v>
+        <v>-0.8312797560880623</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4110,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1781144434439832</v>
+        <v>0.1800144434439832</v>
       </c>
       <c r="C35">
-        <v>12.56192154372776</v>
+        <v>10.96383169484341</v>
       </c>
       <c r="D35">
-        <v>44.89092154372776</v>
+        <v>44.33583169484341</v>
       </c>
       <c r="E35">
-        <v>-24.581</v>
+        <v>-23.538</v>
       </c>
       <c r="F35">
-        <v>34.419</v>
+        <v>35.462</v>
       </c>
       <c r="G35">
         <v>2.09</v>
@@ -4146,37 +4157,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M35">
-        <v>8.116000200000002</v>
+        <v>8.361939600000001</v>
       </c>
       <c r="N35">
-        <v>-14.86266686666667</v>
+        <v>-15.10860626666667</v>
       </c>
       <c r="O35">
-        <v>-3.715666716666667</v>
+        <v>-3.777151566666667</v>
       </c>
       <c r="P35">
-        <v>-11.14700015</v>
+        <v>-11.3314547</v>
       </c>
       <c r="Q35">
-        <v>5.052999849999999</v>
+        <v>4.868545299999999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1255658846401852</v>
+        <v>0.126774458649885</v>
       </c>
       <c r="T35">
-        <v>1.233952866792435</v>
+        <v>1.252649122349896</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>-0.2078199390220156</v>
+        <v>-0.2017075878743092</v>
       </c>
       <c r="W35">
-        <v>0.2848039416213913</v>
+        <v>0.2833626492207622</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4184,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>-0.8312797560880623</v>
+        <v>-0.806830351497237</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4192,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1800144434439832</v>
+        <v>0.1819144434439832</v>
       </c>
       <c r="C36">
-        <v>10.96383169484341</v>
+        <v>9.379301880421586</v>
       </c>
       <c r="D36">
-        <v>44.33583169484341</v>
+        <v>43.79430188042159</v>
       </c>
       <c r="E36">
-        <v>-23.538</v>
+        <v>-22.495</v>
       </c>
       <c r="F36">
-        <v>35.462</v>
+        <v>36.505</v>
       </c>
       <c r="G36">
         <v>2.09</v>
@@ -4228,37 +4239,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M36">
-        <v>8.361939600000001</v>
+        <v>8.607879000000001</v>
       </c>
       <c r="N36">
-        <v>-15.10860626666667</v>
+        <v>-15.35454566666667</v>
       </c>
       <c r="O36">
-        <v>-3.777151566666667</v>
+        <v>-3.838636416666667</v>
       </c>
       <c r="P36">
-        <v>-11.3314547</v>
+        <v>-11.51590925</v>
       </c>
       <c r="Q36">
-        <v>4.868545299999999</v>
+        <v>4.684090749999999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.126774458649885</v>
+        <v>0.1280202195521909</v>
       </c>
       <c r="T36">
-        <v>1.252649122349896</v>
+        <v>1.271920647309125</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>-0.2017075878743092</v>
+        <v>-0.1959445139350433</v>
       </c>
       <c r="W36">
-        <v>0.2833626492207622</v>
+        <v>0.2820037163858832</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4266,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>-0.806830351497237</v>
+        <v>-0.7837780557401732</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4274,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1819144434439832</v>
+        <v>0.1838144434439832</v>
       </c>
       <c r="C37">
-        <v>9.379301880421586</v>
+        <v>7.807841218465313</v>
       </c>
       <c r="D37">
-        <v>43.79430188042159</v>
+        <v>43.26584121846531</v>
       </c>
       <c r="E37">
-        <v>-22.495</v>
+        <v>-21.452</v>
       </c>
       <c r="F37">
-        <v>36.505</v>
+        <v>37.548</v>
       </c>
       <c r="G37">
         <v>2.09</v>
@@ -4310,37 +4321,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M37">
-        <v>8.607879000000001</v>
+        <v>8.853818400000002</v>
       </c>
       <c r="N37">
-        <v>-15.35454566666667</v>
+        <v>-15.60048506666667</v>
       </c>
       <c r="O37">
-        <v>-3.838636416666667</v>
+        <v>-3.900121266666667</v>
       </c>
       <c r="P37">
-        <v>-11.51590925</v>
+        <v>-11.7003638</v>
       </c>
       <c r="Q37">
-        <v>4.684090749999999</v>
+        <v>4.499636199999998</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1280202195521909</v>
+        <v>0.1293049104826939</v>
       </c>
       <c r="T37">
-        <v>1.271920647309125</v>
+        <v>1.29179440742333</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>-0.1959445139350433</v>
+        <v>-0.1905016107701809</v>
       </c>
       <c r="W37">
-        <v>0.2820037163858832</v>
+        <v>0.2807202798196087</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4348,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>-0.7837780557401732</v>
+        <v>-0.7620064430807238</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4356,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1838144434439832</v>
+        <v>0.1857144434439832</v>
       </c>
       <c r="C38">
-        <v>7.80784121846532</v>
+        <v>6.248982238137863</v>
       </c>
       <c r="D38">
-        <v>43.26584121846531</v>
+        <v>42.74998223813787</v>
       </c>
       <c r="E38">
-        <v>-21.45200000000001</v>
+        <v>-20.409</v>
       </c>
       <c r="F38">
-        <v>37.54799999999999</v>
+        <v>38.591</v>
       </c>
       <c r="G38">
         <v>2.09</v>
@@ -4392,37 +4403,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M38">
-        <v>8.8538184</v>
+        <v>9.099757800000001</v>
       </c>
       <c r="N38">
-        <v>-15.60048506666667</v>
+        <v>-15.84642446666667</v>
       </c>
       <c r="O38">
-        <v>-3.900121266666666</v>
+        <v>-3.961606116666667</v>
       </c>
       <c r="P38">
-        <v>-11.7003638</v>
+        <v>-11.88481835</v>
       </c>
       <c r="Q38">
-        <v>4.499636199999999</v>
+        <v>4.31518165</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1293049104826939</v>
+        <v>0.1306303852522605</v>
       </c>
       <c r="T38">
-        <v>1.29179440742333</v>
+        <v>1.312299080557034</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>-0.190501610770181</v>
+        <v>-0.1853529185872031</v>
       </c>
       <c r="W38">
-        <v>0.2807202798196087</v>
+        <v>0.2795062182028625</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4430,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>-0.7620064430807238</v>
+        <v>-0.7414116743488124</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4438,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1857144434439832</v>
+        <v>0.1876144434439832</v>
       </c>
       <c r="C39">
-        <v>6.248982238137863</v>
+        <v>4.702279500550048</v>
       </c>
       <c r="D39">
-        <v>42.74998223813787</v>
+        <v>42.24627950055005</v>
       </c>
       <c r="E39">
-        <v>-20.409</v>
+        <v>-19.366</v>
       </c>
       <c r="F39">
-        <v>38.591</v>
+        <v>39.634</v>
       </c>
       <c r="G39">
         <v>2.09</v>
@@ -4474,37 +4485,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M39">
-        <v>9.099757800000001</v>
+        <v>9.3456972</v>
       </c>
       <c r="N39">
-        <v>-15.84642446666667</v>
+        <v>-16.09236386666667</v>
       </c>
       <c r="O39">
-        <v>-3.961606116666667</v>
+        <v>-4.023090966666667</v>
       </c>
       <c r="P39">
-        <v>-11.88481835</v>
+        <v>-12.0692729</v>
       </c>
       <c r="Q39">
-        <v>4.31518165</v>
+        <v>4.1307271</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1306303852522605</v>
+        <v>0.1319986172724582</v>
       </c>
       <c r="T39">
-        <v>1.312299080557034</v>
+        <v>1.333465194759566</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>-0.1853529185872031</v>
+        <v>-0.1804752102033294</v>
       </c>
       <c r="W39">
-        <v>0.2795062182028625</v>
+        <v>0.2783560545659451</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4512,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>-0.7414116743488124</v>
+        <v>-0.7219008408133174</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4520,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1876144434439832</v>
+        <v>0.1895144434439832</v>
       </c>
       <c r="C40">
-        <v>4.702279500550048</v>
+        <v>3.167308315915271</v>
       </c>
       <c r="D40">
-        <v>42.24627950055005</v>
+        <v>41.75430831591527</v>
       </c>
       <c r="E40">
-        <v>-19.366</v>
+        <v>-18.323</v>
       </c>
       <c r="F40">
-        <v>39.634</v>
+        <v>40.677</v>
       </c>
       <c r="G40">
         <v>2.09</v>
@@ -4556,37 +4567,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M40">
-        <v>9.3456972</v>
+        <v>9.591636600000001</v>
       </c>
       <c r="N40">
-        <v>-16.09236386666667</v>
+        <v>-16.33830326666667</v>
       </c>
       <c r="O40">
-        <v>-4.023090966666667</v>
+        <v>-4.084575816666667</v>
       </c>
       <c r="P40">
-        <v>-12.0692729</v>
+        <v>-12.25372745</v>
       </c>
       <c r="Q40">
-        <v>4.1307271</v>
+        <v>3.94627255</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1319986172724582</v>
+        <v>0.133411709358892</v>
       </c>
       <c r="T40">
-        <v>1.333465194759566</v>
+        <v>1.355325279919559</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>-0.1804752102033294</v>
+        <v>-0.1758476407109363</v>
       </c>
       <c r="W40">
-        <v>0.2783560545659451</v>
+        <v>0.2772648736796388</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4594,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>-0.7219008408133174</v>
+        <v>-0.7033905628437451</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4602,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1895144434439832</v>
+        <v>0.1914144434439832</v>
       </c>
       <c r="C41">
-        <v>3.167308315915271</v>
+        <v>1.643663549307917</v>
       </c>
       <c r="D41">
-        <v>41.75430831591527</v>
+        <v>41.27366354930792</v>
       </c>
       <c r="E41">
-        <v>-18.323</v>
+        <v>-17.28</v>
       </c>
       <c r="F41">
-        <v>40.677</v>
+        <v>41.72</v>
       </c>
       <c r="G41">
         <v>2.09</v>
@@ -4638,37 +4649,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M41">
-        <v>9.591636600000001</v>
+        <v>9.837576</v>
       </c>
       <c r="N41">
-        <v>-16.33830326666667</v>
+        <v>-16.58424266666667</v>
       </c>
       <c r="O41">
-        <v>-4.084575816666667</v>
+        <v>-4.146060666666667</v>
       </c>
       <c r="P41">
-        <v>-12.25372745</v>
+        <v>-12.438182</v>
       </c>
       <c r="Q41">
-        <v>3.94627255</v>
+        <v>3.761817999999998</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.133411709358892</v>
+        <v>0.1348719045148735</v>
       </c>
       <c r="T41">
-        <v>1.355325279919559</v>
+        <v>1.377914034584885</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>-0.1758476407109363</v>
+        <v>-0.1714514496931629</v>
       </c>
       <c r="W41">
-        <v>0.2772648736796388</v>
+        <v>0.2762282518376478</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4676,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>-0.7033905628437451</v>
+        <v>-0.6858057987726518</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4684,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1914144434439832</v>
+        <v>0.1933144434439832</v>
       </c>
       <c r="C42">
-        <v>1.643663549307917</v>
+        <v>0.130958507966298</v>
       </c>
       <c r="D42">
-        <v>41.27366354930792</v>
+        <v>40.80395850796631</v>
       </c>
       <c r="E42">
-        <v>-17.28</v>
+        <v>-16.23699999999999</v>
       </c>
       <c r="F42">
-        <v>41.72</v>
+        <v>42.76300000000001</v>
       </c>
       <c r="G42">
         <v>2.09</v>
@@ -4720,37 +4731,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M42">
-        <v>9.837576</v>
+        <v>10.0835154</v>
       </c>
       <c r="N42">
-        <v>-16.58424266666667</v>
+        <v>-16.83018206666667</v>
       </c>
       <c r="O42">
-        <v>-4.146060666666667</v>
+        <v>-4.207545516666666</v>
       </c>
       <c r="P42">
-        <v>-12.438182</v>
+        <v>-12.62263655</v>
       </c>
       <c r="Q42">
-        <v>3.761817999999998</v>
+        <v>3.57736345</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1348719045148735</v>
+        <v>0.1363815978117358</v>
       </c>
       <c r="T42">
-        <v>1.377914034584885</v>
+        <v>1.401268509747341</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>-0.1714514496931629</v>
+        <v>-0.1672697070177199</v>
       </c>
       <c r="W42">
-        <v>0.2762282518376478</v>
+        <v>0.2752421969147784</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4758,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>-0.6858057987726518</v>
+        <v>-0.6690788280708793</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4766,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1933144434439832</v>
+        <v>0.1952144434439832</v>
       </c>
       <c r="C43">
-        <v>0.130958507966298</v>
+        <v>-1.371176096282632</v>
       </c>
       <c r="D43">
-        <v>40.80395850796631</v>
+        <v>40.34482390371737</v>
       </c>
       <c r="E43">
-        <v>-16.23699999999999</v>
+        <v>-15.194</v>
       </c>
       <c r="F43">
-        <v>42.76300000000001</v>
+        <v>43.806</v>
       </c>
       <c r="G43">
         <v>2.09</v>
@@ -4802,37 +4813,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M43">
-        <v>10.0835154</v>
+        <v>10.3294548</v>
       </c>
       <c r="N43">
-        <v>-16.83018206666667</v>
+        <v>-17.07612146666667</v>
       </c>
       <c r="O43">
-        <v>-4.207545516666666</v>
+        <v>-4.269030366666667</v>
       </c>
       <c r="P43">
-        <v>-12.62263655</v>
+        <v>-12.8070911</v>
       </c>
       <c r="Q43">
-        <v>3.57736345</v>
+        <v>3.392908899999998</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1363815978117358</v>
+        <v>0.137943349498145</v>
       </c>
       <c r="T43">
-        <v>1.401268509747341</v>
+        <v>1.425428311639537</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>-0.1672697070177199</v>
+        <v>-0.1632870949458694</v>
       </c>
       <c r="W43">
-        <v>0.2752421969147784</v>
+        <v>0.274303096988236</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4840,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>-0.6690788280708793</v>
+        <v>-0.6531483797834776</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4848,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1952144434439832</v>
+        <v>0.1971144434439832</v>
       </c>
       <c r="C44">
-        <v>-1.371176096282625</v>
+        <v>-2.863093115327978</v>
       </c>
       <c r="D44">
-        <v>40.34482390371737</v>
+        <v>39.89590688467202</v>
       </c>
       <c r="E44">
-        <v>-15.194</v>
+        <v>-14.151</v>
       </c>
       <c r="F44">
-        <v>43.806</v>
+        <v>44.849</v>
       </c>
       <c r="G44">
         <v>2.09</v>
@@ -4884,37 +4895,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M44">
-        <v>10.3294548</v>
+        <v>10.5753942</v>
       </c>
       <c r="N44">
-        <v>-17.07612146666667</v>
+        <v>-17.32206086666667</v>
       </c>
       <c r="O44">
-        <v>-4.269030366666667</v>
+        <v>-4.330515216666667</v>
       </c>
       <c r="P44">
-        <v>-12.8070911</v>
+        <v>-12.99154565</v>
       </c>
       <c r="Q44">
-        <v>3.392908899999998</v>
+        <v>3.208454349999998</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.137943349498145</v>
+        <v>0.1395598994893405</v>
       </c>
       <c r="T44">
-        <v>1.425428311639536</v>
+        <v>1.450435825878827</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>-0.1632870949458694</v>
+        <v>-0.1594897206448027</v>
       </c>
       <c r="W44">
-        <v>0.274303096988236</v>
+        <v>0.2734076761280445</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4922,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>-0.6531483797834776</v>
+        <v>-0.6379588825792109</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4930,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1971144434439832</v>
+        <v>0.1990144434439832</v>
       </c>
       <c r="C45">
-        <v>-2.863093115327978</v>
+        <v>-4.345129869144884</v>
       </c>
       <c r="D45">
-        <v>39.89590688467202</v>
+        <v>39.45687013085511</v>
       </c>
       <c r="E45">
-        <v>-14.151</v>
+        <v>-13.108</v>
       </c>
       <c r="F45">
-        <v>44.849</v>
+        <v>45.892</v>
       </c>
       <c r="G45">
         <v>2.09</v>
@@ -4966,37 +4977,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M45">
-        <v>10.5753942</v>
+        <v>10.8213336</v>
       </c>
       <c r="N45">
-        <v>-17.32206086666667</v>
+        <v>-17.56800026666667</v>
       </c>
       <c r="O45">
-        <v>-4.330515216666667</v>
+        <v>-4.392000066666666</v>
       </c>
       <c r="P45">
-        <v>-12.99154565</v>
+        <v>-13.1760002</v>
       </c>
       <c r="Q45">
-        <v>3.208454349999998</v>
+        <v>3.0239998</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1395598994893405</v>
+        <v>0.141234183408793</v>
       </c>
       <c r="T45">
-        <v>1.450435825878827</v>
+        <v>1.476336465626663</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>-0.1594897206448027</v>
+        <v>-0.1558649542665117</v>
       </c>
       <c r="W45">
-        <v>0.2734076761280445</v>
+        <v>0.2725529562160435</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5004,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>-0.6379588825792109</v>
+        <v>-0.6234598170660468</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5012,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1990144434439832</v>
+        <v>0.2009144434439832</v>
       </c>
       <c r="C46">
-        <v>-4.345129869144884</v>
+        <v>-5.81760899110148</v>
       </c>
       <c r="D46">
-        <v>39.45687013085511</v>
+        <v>39.02739100889853</v>
       </c>
       <c r="E46">
-        <v>-13.108</v>
+        <v>-12.065</v>
       </c>
       <c r="F46">
-        <v>45.892</v>
+        <v>46.935</v>
       </c>
       <c r="G46">
         <v>2.09</v>
@@ -5048,37 +5059,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M46">
-        <v>10.8213336</v>
+        <v>11.067273</v>
       </c>
       <c r="N46">
-        <v>-17.56800026666667</v>
+        <v>-17.81393966666667</v>
       </c>
       <c r="O46">
-        <v>-4.392000066666666</v>
+        <v>-4.453484916666667</v>
       </c>
       <c r="P46">
-        <v>-13.1760002</v>
+        <v>-13.36045475</v>
       </c>
       <c r="Q46">
-        <v>3.0239998</v>
+        <v>2.83954525</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.141234183408793</v>
+        <v>0.142969350379862</v>
       </c>
       <c r="T46">
-        <v>1.476336465626663</v>
+        <v>1.503178946819875</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>-0.1558649542665117</v>
+        <v>-0.1524012886161448</v>
       </c>
       <c r="W46">
-        <v>0.2725529562160435</v>
+        <v>0.271736223855687</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5086,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>-0.6234598170660468</v>
+        <v>-0.6096051544645791</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5094,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.2009144434439832</v>
+        <v>0.2028144434439832</v>
       </c>
       <c r="C47">
-        <v>-5.81760899110148</v>
+        <v>-7.280839218654229</v>
       </c>
       <c r="D47">
-        <v>39.02739100889853</v>
+        <v>38.60716078134578</v>
       </c>
       <c r="E47">
-        <v>-12.065</v>
+        <v>-11.022</v>
       </c>
       <c r="F47">
-        <v>46.935</v>
+        <v>47.978</v>
       </c>
       <c r="G47">
         <v>2.09</v>
@@ -5130,37 +5141,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M47">
-        <v>11.067273</v>
+        <v>11.3132124</v>
       </c>
       <c r="N47">
-        <v>-17.81393966666667</v>
+        <v>-18.05987906666667</v>
       </c>
       <c r="O47">
-        <v>-4.453484916666667</v>
+        <v>-4.514969766666667</v>
       </c>
       <c r="P47">
-        <v>-13.36045475</v>
+        <v>-13.5449093</v>
       </c>
       <c r="Q47">
-        <v>2.83954525</v>
+        <v>2.655090699999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.142969350379862</v>
+        <v>0.1447687827943039</v>
       </c>
       <c r="T47">
-        <v>1.503178946819875</v>
+        <v>1.531015593983206</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>-0.1524012886161448</v>
+        <v>-0.1490882171244894</v>
       </c>
       <c r="W47">
-        <v>0.271736223855687</v>
+        <v>0.2709550015979546</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5168,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>-0.6096051544645791</v>
+        <v>-0.5963528684979578</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5176,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.2028144434439832</v>
+        <v>0.2047144434439832</v>
       </c>
       <c r="C48">
-        <v>-7.280839218654229</v>
+        <v>-8.735116133504519</v>
       </c>
       <c r="D48">
-        <v>38.60716078134578</v>
+        <v>38.19588386649548</v>
       </c>
       <c r="E48">
-        <v>-11.022</v>
+        <v>-9.978999999999999</v>
       </c>
       <c r="F48">
-        <v>47.978</v>
+        <v>49.021</v>
       </c>
       <c r="G48">
         <v>2.09</v>
@@ -5212,37 +5223,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M48">
-        <v>11.3132124</v>
+        <v>11.5591518</v>
       </c>
       <c r="N48">
-        <v>-18.05987906666667</v>
+        <v>-18.30581846666666</v>
       </c>
       <c r="O48">
-        <v>-4.514969766666667</v>
+        <v>-4.576454616666666</v>
       </c>
       <c r="P48">
-        <v>-13.5449093</v>
+        <v>-13.72936385</v>
       </c>
       <c r="Q48">
-        <v>2.655090699999999</v>
+        <v>2.470636150000001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1447687827943039</v>
+        <v>0.1466361183187247</v>
       </c>
       <c r="T48">
-        <v>1.531015593983206</v>
+        <v>1.559902680662134</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>-0.1490882171244894</v>
+        <v>-0.1459161273984365</v>
       </c>
       <c r="W48">
-        <v>0.2709550015979546</v>
+        <v>0.2702070228405513</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5250,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>-0.5963528684979578</v>
+        <v>-0.5836645095937458</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5258,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.2047144434439832</v>
+        <v>0.2066144434439832</v>
       </c>
       <c r="C49">
-        <v>-8.735116133504519</v>
+        <v>-10.18072285494494</v>
       </c>
       <c r="D49">
-        <v>38.19588386649548</v>
+        <v>37.79327714505506</v>
       </c>
       <c r="E49">
-        <v>-9.978999999999999</v>
+        <v>-8.936</v>
       </c>
       <c r="F49">
-        <v>49.021</v>
+        <v>50.064</v>
       </c>
       <c r="G49">
         <v>2.09</v>
@@ -5294,37 +5305,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M49">
-        <v>11.5591518</v>
+        <v>11.8050912</v>
       </c>
       <c r="N49">
-        <v>-18.30581846666666</v>
+        <v>-18.55175786666667</v>
       </c>
       <c r="O49">
-        <v>-4.576454616666666</v>
+        <v>-4.637939466666666</v>
       </c>
       <c r="P49">
-        <v>-13.72936385</v>
+        <v>-13.9138184</v>
       </c>
       <c r="Q49">
-        <v>2.470636150000001</v>
+        <v>2.286181599999999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1466361183187247</v>
+        <v>0.1485752744402386</v>
       </c>
       <c r="T49">
-        <v>1.559902680662134</v>
+        <v>1.589900809136406</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>-0.1459161273984365</v>
+        <v>-0.1428762080776357</v>
       </c>
       <c r="W49">
-        <v>0.2702070228405513</v>
+        <v>0.2694902098647065</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5332,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>-0.5836645095937458</v>
+        <v>-0.5715048323105429</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5340,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.2066144434439832</v>
+        <v>0.2085144434439832</v>
       </c>
       <c r="C50">
-        <v>-10.18072285494494</v>
+        <v>-11.61793068981336</v>
       </c>
       <c r="D50">
-        <v>37.79327714505506</v>
+        <v>37.39906931018663</v>
       </c>
       <c r="E50">
-        <v>-8.936</v>
+        <v>-7.893000000000001</v>
       </c>
       <c r="F50">
-        <v>50.064</v>
+        <v>51.107</v>
       </c>
       <c r="G50">
         <v>2.09</v>
@@ -5376,37 +5387,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M50">
-        <v>11.8050912</v>
+        <v>12.0510306</v>
       </c>
       <c r="N50">
-        <v>-18.55175786666667</v>
+        <v>-18.79769726666667</v>
       </c>
       <c r="O50">
-        <v>-4.637939466666666</v>
+        <v>-4.699424316666667</v>
       </c>
       <c r="P50">
-        <v>-13.9138184</v>
+        <v>-14.09827295</v>
       </c>
       <c r="Q50">
-        <v>2.286181599999999</v>
+        <v>2.101727049999999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1485752744402386</v>
+        <v>0.1505904758998511</v>
       </c>
       <c r="T50">
-        <v>1.589900809136406</v>
+        <v>1.621075334805747</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>-0.1428762080776357</v>
+        <v>-0.1399603670964595</v>
       </c>
       <c r="W50">
-        <v>0.2694902098647065</v>
+        <v>0.2688026545613452</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5414,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>-0.5715048323105429</v>
+        <v>-0.5598414683858379</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5422,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.2085144434439832</v>
+        <v>0.2104144434439832</v>
       </c>
       <c r="C51">
-        <v>-11.61793068981336</v>
+        <v>-13.04699974219043</v>
       </c>
       <c r="D51">
-        <v>37.39906931018663</v>
+        <v>37.01300025780957</v>
       </c>
       <c r="E51">
-        <v>-7.893000000000001</v>
+        <v>-6.850000000000001</v>
       </c>
       <c r="F51">
-        <v>51.107</v>
+        <v>52.15</v>
       </c>
       <c r="G51">
         <v>2.09</v>
@@ -5458,37 +5469,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M51">
-        <v>12.0510306</v>
+        <v>12.29697</v>
       </c>
       <c r="N51">
-        <v>-18.79769726666667</v>
+        <v>-19.04363666666666</v>
       </c>
       <c r="O51">
-        <v>-4.699424316666667</v>
+        <v>-4.760909166666666</v>
       </c>
       <c r="P51">
-        <v>-14.09827295</v>
+        <v>-14.2827275</v>
       </c>
       <c r="Q51">
-        <v>2.101727049999999</v>
+        <v>1.917272500000001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1505904758998511</v>
+        <v>0.1526862854178482</v>
       </c>
       <c r="T51">
-        <v>1.621075334805747</v>
+        <v>1.653496841501862</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>-0.1399603670964595</v>
+        <v>-0.1371611597545303</v>
       </c>
       <c r="W51">
-        <v>0.2688026545613452</v>
+        <v>0.2681426014701183</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5496,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>-0.5598414683858379</v>
+        <v>-0.548644639018121</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5504,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.2104144434439832</v>
+        <v>0.2123144434439833</v>
       </c>
       <c r="C52">
-        <v>-13.04699974219043</v>
+        <v>-14.46817948571952</v>
       </c>
       <c r="D52">
-        <v>37.01300025780957</v>
+        <v>36.63482051428048</v>
       </c>
       <c r="E52">
-        <v>-6.850000000000001</v>
+        <v>-5.807000000000002</v>
       </c>
       <c r="F52">
-        <v>52.15</v>
+        <v>53.193</v>
       </c>
       <c r="G52">
         <v>2.09</v>
@@ -5540,37 +5551,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M52">
-        <v>12.29697</v>
+        <v>12.5429094</v>
       </c>
       <c r="N52">
-        <v>-19.04363666666666</v>
+        <v>-19.28957606666667</v>
       </c>
       <c r="O52">
-        <v>-4.760909166666666</v>
+        <v>-4.822394016666666</v>
       </c>
       <c r="P52">
-        <v>-14.2827275</v>
+        <v>-14.46718205</v>
       </c>
       <c r="Q52">
-        <v>1.917272500000001</v>
+        <v>1.732817950000001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1526862854178482</v>
+        <v>0.1548676381814778</v>
       </c>
       <c r="T52">
-        <v>1.653496841501862</v>
+        <v>1.687241675001901</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>-0.1371611597545303</v>
+        <v>-0.1344717252495395</v>
       </c>
       <c r="W52">
-        <v>0.2681426014701183</v>
+        <v>0.2675084328138415</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5578,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>-0.548644639018121</v>
+        <v>-0.5378869009981582</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5586,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.2123144434439833</v>
+        <v>0.2142144434439832</v>
       </c>
       <c r="C53">
-        <v>-14.46817948571952</v>
+        <v>-15.88170930119546</v>
       </c>
       <c r="D53">
-        <v>36.63482051428048</v>
+        <v>36.26429069880453</v>
       </c>
       <c r="E53">
-        <v>-5.807000000000002</v>
+        <v>-4.764000000000003</v>
       </c>
       <c r="F53">
-        <v>53.193</v>
+        <v>54.236</v>
       </c>
       <c r="G53">
         <v>2.09</v>
@@ -5622,37 +5633,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M53">
-        <v>12.5429094</v>
+        <v>12.7888488</v>
       </c>
       <c r="N53">
-        <v>-19.28957606666667</v>
+        <v>-19.53551546666667</v>
       </c>
       <c r="O53">
-        <v>-4.822394016666666</v>
+        <v>-4.883878866666667</v>
       </c>
       <c r="P53">
-        <v>-14.46718205</v>
+        <v>-14.6516366</v>
       </c>
       <c r="Q53">
-        <v>1.732817950000001</v>
+        <v>1.5483634</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1548676381814778</v>
+        <v>0.1571398806435919</v>
       </c>
       <c r="T53">
-        <v>1.687241675001901</v>
+        <v>1.722392543231107</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>-0.1344717252495395</v>
+        <v>-0.1318857305332022</v>
       </c>
       <c r="W53">
-        <v>0.2675084328138415</v>
+        <v>0.2668986552597291</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5660,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>-0.5378869009981582</v>
+        <v>-0.527542922132809</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5668,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.2142144434439832</v>
+        <v>0.2161144434439832</v>
       </c>
       <c r="C54">
-        <v>-15.88170930119546</v>
+        <v>-17.28781898185668</v>
       </c>
       <c r="D54">
-        <v>36.26429069880453</v>
+        <v>35.90118101814332</v>
       </c>
       <c r="E54">
-        <v>-4.764000000000003</v>
+        <v>-3.720999999999997</v>
       </c>
       <c r="F54">
-        <v>54.236</v>
+        <v>55.279</v>
       </c>
       <c r="G54">
         <v>2.09</v>
@@ -5704,37 +5715,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M54">
-        <v>12.7888488</v>
+        <v>13.0347882</v>
       </c>
       <c r="N54">
-        <v>-19.53551546666667</v>
+        <v>-19.78145486666667</v>
       </c>
       <c r="O54">
-        <v>-4.883878866666667</v>
+        <v>-4.945363716666667</v>
       </c>
       <c r="P54">
-        <v>-14.6516366</v>
+        <v>-14.83609115</v>
       </c>
       <c r="Q54">
-        <v>1.5483634</v>
+        <v>1.363908849999998</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1571398806435919</v>
+        <v>0.1595088142743066</v>
       </c>
       <c r="T54">
-        <v>1.722392543231107</v>
+        <v>1.759039193087087</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>-0.1318857305332022</v>
+        <v>-0.1293973205231418</v>
       </c>
       <c r="W54">
-        <v>0.2668986552597291</v>
+        <v>0.2663118881793569</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5742,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>-0.527542922132809</v>
+        <v>-0.5175892820925672</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5750,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.2161144434439832</v>
+        <v>0.2180144434439832</v>
       </c>
       <c r="C55">
-        <v>-17.28781898185668</v>
+        <v>-18.68672920862143</v>
       </c>
       <c r="D55">
-        <v>35.90118101814332</v>
+        <v>35.54527079137857</v>
       </c>
       <c r="E55">
-        <v>-3.720999999999997</v>
+        <v>-2.677999999999997</v>
       </c>
       <c r="F55">
-        <v>55.279</v>
+        <v>56.322</v>
       </c>
       <c r="G55">
         <v>2.09</v>
@@ -5786,37 +5797,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M55">
-        <v>13.0347882</v>
+        <v>13.2807276</v>
       </c>
       <c r="N55">
-        <v>-19.78145486666667</v>
+        <v>-20.02739426666667</v>
       </c>
       <c r="O55">
-        <v>-4.945363716666667</v>
+        <v>-5.006848566666667</v>
       </c>
       <c r="P55">
-        <v>-14.83609115</v>
+        <v>-15.0205457</v>
       </c>
       <c r="Q55">
-        <v>1.363908849999998</v>
+        <v>1.179454299999998</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1595088142743066</v>
+        <v>0.1619807450194002</v>
       </c>
       <c r="T55">
-        <v>1.759039193087087</v>
+        <v>1.797279175545503</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>-0.1293973205231418</v>
+        <v>-0.1270010738467873</v>
       </c>
       <c r="W55">
-        <v>0.2663118881793569</v>
+        <v>0.2657468532130725</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5824,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>-0.5175892820925672</v>
+        <v>-0.5080042953871493</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5832,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2180144434439832</v>
+        <v>0.2199144434439833</v>
       </c>
       <c r="C56">
-        <v>-18.68672920862143</v>
+        <v>-20.07865199733386</v>
       </c>
       <c r="D56">
-        <v>35.54527079137857</v>
+        <v>35.19634800266615</v>
       </c>
       <c r="E56">
-        <v>-2.677999999999997</v>
+        <v>-1.634999999999998</v>
       </c>
       <c r="F56">
-        <v>56.322</v>
+        <v>57.365</v>
       </c>
       <c r="G56">
         <v>2.09</v>
@@ -5868,37 +5879,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M56">
-        <v>13.2807276</v>
+        <v>13.526667</v>
       </c>
       <c r="N56">
-        <v>-20.02739426666667</v>
+        <v>-20.27333366666667</v>
       </c>
       <c r="O56">
-        <v>-5.006848566666667</v>
+        <v>-5.068333416666666</v>
       </c>
       <c r="P56">
-        <v>-15.0205457</v>
+        <v>-15.20500025</v>
       </c>
       <c r="Q56">
-        <v>1.179454299999998</v>
+        <v>0.9949997499999998</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1619807450194002</v>
+        <v>0.1645625393531647</v>
       </c>
       <c r="T56">
-        <v>1.797279175545503</v>
+        <v>1.837218712779847</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>-0.1270010738467873</v>
+        <v>-0.1246919634132094</v>
       </c>
       <c r="W56">
-        <v>0.2657468532130725</v>
+        <v>0.2652023649728348</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5906,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>-0.5080042953871493</v>
+        <v>-0.4987678536528373</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5914,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2199144434439833</v>
+        <v>0.2218144434439832</v>
       </c>
       <c r="C57">
-        <v>-20.07865199733386</v>
+        <v>-21.46379111992427</v>
       </c>
       <c r="D57">
-        <v>35.19634800266615</v>
+        <v>34.85420888007574</v>
       </c>
       <c r="E57">
-        <v>-1.634999999999998</v>
+        <v>-0.5919999999999987</v>
       </c>
       <c r="F57">
-        <v>57.365</v>
+        <v>58.408</v>
       </c>
       <c r="G57">
         <v>2.09</v>
@@ -5950,37 +5961,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M57">
-        <v>13.526667</v>
+        <v>13.7726064</v>
       </c>
       <c r="N57">
-        <v>-20.27333366666667</v>
+        <v>-20.51927306666667</v>
       </c>
       <c r="O57">
-        <v>-5.068333416666666</v>
+        <v>-5.129818266666667</v>
       </c>
       <c r="P57">
-        <v>-15.20500025</v>
+        <v>-15.3894548</v>
       </c>
       <c r="Q57">
-        <v>0.9949997499999998</v>
+        <v>0.8105452</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1645625393531647</v>
+        <v>0.1672616879748275</v>
       </c>
       <c r="T57">
-        <v>1.837218712779847</v>
+        <v>1.878973683524844</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>-0.1246919634132094</v>
+        <v>-0.1224653212094021</v>
       </c>
       <c r="W57">
-        <v>0.2652023649728348</v>
+        <v>0.264677322741177</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5988,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>-0.4987678536528373</v>
+        <v>-0.4898612848376083</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5996,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2218144434439832</v>
+        <v>0.2237144434439832</v>
       </c>
       <c r="C58">
-        <v>-21.46379111992427</v>
+        <v>-22.84234250124172</v>
       </c>
       <c r="D58">
-        <v>34.85420888007574</v>
+        <v>34.51865749875829</v>
       </c>
       <c r="E58">
-        <v>-0.5919999999999987</v>
+        <v>0.4510000000000076</v>
       </c>
       <c r="F58">
-        <v>58.408</v>
+        <v>59.45100000000001</v>
       </c>
       <c r="G58">
         <v>2.09</v>
@@ -6032,37 +6043,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M58">
-        <v>13.7726064</v>
+        <v>14.0185458</v>
       </c>
       <c r="N58">
-        <v>-20.51927306666667</v>
+        <v>-20.76521246666667</v>
       </c>
       <c r="O58">
-        <v>-5.129818266666667</v>
+        <v>-5.191303116666667</v>
       </c>
       <c r="P58">
-        <v>-15.3894548</v>
+        <v>-15.57390935</v>
       </c>
       <c r="Q58">
-        <v>0.8105452</v>
+        <v>0.6260906499999983</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1672616879748275</v>
+        <v>0.1700863783928467</v>
       </c>
       <c r="T58">
-        <v>1.878973683524844</v>
+        <v>1.922670745932398</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>-0.1224653212094021</v>
+        <v>-0.1203168068022196</v>
       </c>
       <c r="W58">
-        <v>0.264677322741177</v>
+        <v>0.2641707030439634</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6070,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>-0.4898612848376083</v>
+        <v>-0.4812672272088783</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6078,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2237144434439832</v>
+        <v>0.2256144434439832</v>
       </c>
       <c r="C59">
-        <v>-22.84234250124172</v>
+        <v>-24.2144945931825</v>
       </c>
       <c r="D59">
-        <v>34.51865749875829</v>
+        <v>34.1895054068175</v>
       </c>
       <c r="E59">
-        <v>0.4510000000000076</v>
+        <v>1.494000000000007</v>
       </c>
       <c r="F59">
-        <v>59.45100000000001</v>
+        <v>60.49400000000001</v>
       </c>
       <c r="G59">
         <v>2.09</v>
@@ -6114,37 +6125,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M59">
-        <v>14.0185458</v>
+        <v>14.2644852</v>
       </c>
       <c r="N59">
-        <v>-20.76521246666667</v>
+        <v>-21.01115186666667</v>
       </c>
       <c r="O59">
-        <v>-5.191303116666667</v>
+        <v>-5.252787966666667</v>
       </c>
       <c r="P59">
-        <v>-15.57390935</v>
+        <v>-15.7583639</v>
       </c>
       <c r="Q59">
-        <v>0.6260906499999983</v>
+        <v>0.4416360999999966</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1700863783928467</v>
+        <v>0.1730455778783907</v>
       </c>
       <c r="T59">
-        <v>1.922670745932398</v>
+        <v>1.968448620835551</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>-0.1203168068022196</v>
+        <v>-0.118242379098733</v>
       </c>
       <c r="W59">
-        <v>0.2641707030439634</v>
+        <v>0.2636815529914813</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6152,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>-0.4812672272088783</v>
+        <v>-0.4729695163949319</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6160,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2256144434439832</v>
+        <v>0.2275144434439832</v>
       </c>
       <c r="C60">
-        <v>-24.21449459318247</v>
+        <v>-25.58042872761595</v>
       </c>
       <c r="D60">
-        <v>34.18950540681752</v>
+        <v>33.86657127238404</v>
       </c>
       <c r="E60">
-        <v>1.493999999999993</v>
+        <v>2.536999999999992</v>
       </c>
       <c r="F60">
-        <v>60.49399999999999</v>
+        <v>61.53699999999999</v>
       </c>
       <c r="G60">
         <v>2.09</v>
@@ -6196,37 +6207,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M60">
-        <v>14.2644852</v>
+        <v>14.5104246</v>
       </c>
       <c r="N60">
-        <v>-21.01115186666667</v>
+        <v>-21.25709126666666</v>
       </c>
       <c r="O60">
-        <v>-5.252787966666666</v>
+        <v>-5.314272816666666</v>
       </c>
       <c r="P60">
-        <v>-15.7583639</v>
+        <v>-15.94281845</v>
       </c>
       <c r="Q60">
-        <v>0.4416361000000002</v>
+        <v>0.2571815500000021</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1730455778783907</v>
+        <v>0.1761491285583514</v>
       </c>
       <c r="T60">
-        <v>1.96844862083555</v>
+        <v>2.016459562807149</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>-0.118242379098733</v>
+        <v>-0.1162382709784155</v>
       </c>
       <c r="W60">
-        <v>0.2636815529914813</v>
+        <v>0.2632089842967104</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6234,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>-0.4729695163949321</v>
+        <v>-0.464953083913662</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6242,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2275144434439832</v>
+        <v>0.2294144434439833</v>
       </c>
       <c r="C61">
-        <v>-25.58042872761595</v>
+        <v>-26.94031944949626</v>
       </c>
       <c r="D61">
-        <v>33.86657127238404</v>
+        <v>33.54968055050374</v>
       </c>
       <c r="E61">
-        <v>2.536999999999992</v>
+        <v>3.579999999999998</v>
       </c>
       <c r="F61">
-        <v>61.53699999999999</v>
+        <v>62.58</v>
       </c>
       <c r="G61">
         <v>2.09</v>
@@ -6278,37 +6289,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M61">
-        <v>14.5104246</v>
+        <v>14.756364</v>
       </c>
       <c r="N61">
-        <v>-21.25709126666666</v>
+        <v>-21.50303066666667</v>
       </c>
       <c r="O61">
-        <v>-5.314272816666666</v>
+        <v>-5.375757666666667</v>
       </c>
       <c r="P61">
-        <v>-15.94281845</v>
+        <v>-16.127273</v>
       </c>
       <c r="Q61">
-        <v>0.2571815500000021</v>
+        <v>0.07272699999999688</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1761491285583514</v>
+        <v>0.1794078567723102</v>
       </c>
       <c r="T61">
-        <v>2.016459562807149</v>
+        <v>2.066871051877328</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>-0.1162382709784155</v>
+        <v>-0.1143009664621086</v>
       </c>
       <c r="W61">
-        <v>0.2632089842967104</v>
+        <v>0.2627521678917653</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6316,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>-0.464953083913662</v>
+        <v>-0.4572038658484345</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6324,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2294144434439833</v>
+        <v>0.2313144434439832</v>
       </c>
       <c r="C62">
-        <v>-26.94031944949626</v>
+        <v>-28.29433483144573</v>
       </c>
       <c r="D62">
-        <v>33.54968055050374</v>
+        <v>33.23866516855426</v>
       </c>
       <c r="E62">
-        <v>3.579999999999998</v>
+        <v>4.622999999999998</v>
       </c>
       <c r="F62">
-        <v>62.58</v>
+        <v>63.623</v>
       </c>
       <c r="G62">
         <v>2.09</v>
@@ -6360,37 +6371,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M62">
-        <v>14.756364</v>
+        <v>15.0023034</v>
       </c>
       <c r="N62">
-        <v>-21.50303066666667</v>
+        <v>-21.74897006666666</v>
       </c>
       <c r="O62">
-        <v>-5.375757666666667</v>
+        <v>-5.437242516666666</v>
       </c>
       <c r="P62">
-        <v>-16.127273</v>
+        <v>-16.31172755</v>
       </c>
       <c r="Q62">
-        <v>0.07272699999999688</v>
+        <v>-0.1117275500000012</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1794078567723102</v>
+        <v>0.1828336992536515</v>
       </c>
       <c r="T62">
-        <v>2.066871051877328</v>
+        <v>2.119867745515208</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>-0.1143009664621086</v>
+        <v>-0.1124271801266642</v>
       </c>
       <c r="W62">
-        <v>0.2627521678917653</v>
+        <v>0.2623103290738674</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6398,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>-0.4572038658484345</v>
+        <v>-0.4497087205066566</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6406,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2313144434439832</v>
+        <v>0.2332144434439832</v>
       </c>
       <c r="C63">
-        <v>-28.29433483144573</v>
+        <v>-29.64263677100159</v>
       </c>
       <c r="D63">
-        <v>33.23866516855426</v>
+        <v>32.9333632289984</v>
       </c>
       <c r="E63">
-        <v>4.622999999999998</v>
+        <v>5.665999999999997</v>
       </c>
       <c r="F63">
-        <v>63.623</v>
+        <v>64.666</v>
       </c>
       <c r="G63">
         <v>2.09</v>
@@ -6442,37 +6453,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M63">
-        <v>15.0023034</v>
+        <v>15.2482428</v>
       </c>
       <c r="N63">
-        <v>-21.74897006666666</v>
+        <v>-21.99490946666667</v>
       </c>
       <c r="O63">
-        <v>-5.437242516666666</v>
+        <v>-5.498727366666667</v>
       </c>
       <c r="P63">
-        <v>-16.31172755</v>
+        <v>-16.4961821</v>
       </c>
       <c r="Q63">
-        <v>-0.1117275500000012</v>
+        <v>-0.2961820999999993</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1828336992536515</v>
+        <v>0.1864398492340107</v>
       </c>
       <c r="T63">
-        <v>2.119867745515208</v>
+        <v>2.17565373881824</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>-0.1124271801266642</v>
+        <v>-0.110613838511718</v>
       </c>
       <c r="W63">
-        <v>0.2623103290738674</v>
+        <v>0.2618827431210631</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6480,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>-0.4497087205066566</v>
+        <v>-0.4424553540468719</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6488,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2332144434439832</v>
+        <v>0.2351144434439832</v>
       </c>
       <c r="C64">
-        <v>-29.64263677100159</v>
+        <v>-30.98538127162986</v>
       </c>
       <c r="D64">
-        <v>32.9333632289984</v>
+        <v>32.63361872837014</v>
       </c>
       <c r="E64">
-        <v>5.665999999999997</v>
+        <v>6.709000000000003</v>
       </c>
       <c r="F64">
-        <v>64.666</v>
+        <v>65.709</v>
       </c>
       <c r="G64">
         <v>2.09</v>
@@ -6524,37 +6535,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M64">
-        <v>15.2482428</v>
+        <v>15.4941822</v>
       </c>
       <c r="N64">
-        <v>-21.99490946666667</v>
+        <v>-22.24084886666667</v>
       </c>
       <c r="O64">
-        <v>-5.498727366666667</v>
+        <v>-5.560212216666667</v>
       </c>
       <c r="P64">
-        <v>-16.4961821</v>
+        <v>-16.68063665</v>
       </c>
       <c r="Q64">
-        <v>-0.2961820999999993</v>
+        <v>-0.480636650000001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1864398492340107</v>
+        <v>0.1902409262403354</v>
       </c>
       <c r="T64">
-        <v>2.17565373881824</v>
+        <v>2.234455191218732</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>-0.110613838511718</v>
+        <v>-0.1088580632972463</v>
       </c>
       <c r="W64">
-        <v>0.2618827431210631</v>
+        <v>0.2614687313254907</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6562,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>-0.4424553540468719</v>
+        <v>-0.4354322531889852</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6570,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2351144434439832</v>
+        <v>0.2370144434439832</v>
       </c>
       <c r="C65">
-        <v>-30.98538127162986</v>
+        <v>-32.32271870853189</v>
       </c>
       <c r="D65">
-        <v>32.63361872837014</v>
+        <v>32.3392812914681</v>
       </c>
       <c r="E65">
-        <v>6.709000000000003</v>
+        <v>7.751999999999995</v>
       </c>
       <c r="F65">
-        <v>65.709</v>
+        <v>66.752</v>
       </c>
       <c r="G65">
         <v>2.09</v>
@@ -6606,37 +6617,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M65">
-        <v>15.4941822</v>
+        <v>15.7401216</v>
       </c>
       <c r="N65">
-        <v>-22.24084886666667</v>
+        <v>-22.48678826666666</v>
       </c>
       <c r="O65">
-        <v>-5.560212216666667</v>
+        <v>-5.621697066666666</v>
       </c>
       <c r="P65">
-        <v>-16.68063665</v>
+        <v>-16.8650912</v>
       </c>
       <c r="Q65">
-        <v>-0.480636650000001</v>
+        <v>-0.6650911999999991</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1902409262403354</v>
+        <v>0.1942531741914558</v>
       </c>
       <c r="T65">
-        <v>2.234455191218732</v>
+        <v>2.296523390974809</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>-0.1088580632972463</v>
+        <v>-0.1071571560582268</v>
       </c>
       <c r="W65">
-        <v>0.2614687313254907</v>
+        <v>0.2610676573985299</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6644,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>-0.4354322531889852</v>
+        <v>-0.4286286242329072</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6652,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2370144434439832</v>
+        <v>0.2389144434439832</v>
       </c>
       <c r="C66">
-        <v>-32.32271870853189</v>
+        <v>-33.65479408019509</v>
       </c>
       <c r="D66">
-        <v>32.3392812914681</v>
+        <v>32.05020591980492</v>
       </c>
       <c r="E66">
-        <v>7.751999999999995</v>
+        <v>8.795000000000002</v>
       </c>
       <c r="F66">
-        <v>66.752</v>
+        <v>67.795</v>
       </c>
       <c r="G66">
         <v>2.09</v>
@@ -6688,37 +6699,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M66">
-        <v>15.7401216</v>
+        <v>15.986061</v>
       </c>
       <c r="N66">
-        <v>-22.48678826666666</v>
+        <v>-22.73272766666667</v>
       </c>
       <c r="O66">
-        <v>-5.621697066666666</v>
+        <v>-5.683181916666667</v>
       </c>
       <c r="P66">
-        <v>-16.8650912</v>
+        <v>-17.04954575</v>
       </c>
       <c r="Q66">
-        <v>-0.6650911999999991</v>
+        <v>-0.8495457500000008</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1942531741914558</v>
+        <v>0.1984946934540688</v>
       </c>
       <c r="T66">
-        <v>2.296523390974809</v>
+        <v>2.362138345002661</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>-0.1071571560582268</v>
+        <v>-0.1055085844265618</v>
       </c>
       <c r="W66">
-        <v>0.2610676573985299</v>
+        <v>0.2606789242077833</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6726,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>-0.4286286242329072</v>
+        <v>-0.4220343377062472</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6734,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2389144434439832</v>
+        <v>0.2408144434439832</v>
       </c>
       <c r="C67">
-        <v>-33.65479408019509</v>
+        <v>-34.98174724657132</v>
       </c>
       <c r="D67">
-        <v>32.05020591980492</v>
+        <v>31.76625275342869</v>
       </c>
       <c r="E67">
-        <v>8.795000000000002</v>
+        <v>9.838000000000008</v>
       </c>
       <c r="F67">
-        <v>67.795</v>
+        <v>68.83800000000001</v>
       </c>
       <c r="G67">
         <v>2.09</v>
@@ -6770,37 +6781,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M67">
-        <v>15.986061</v>
+        <v>16.2320004</v>
       </c>
       <c r="N67">
-        <v>-22.73272766666667</v>
+        <v>-22.97866706666667</v>
       </c>
       <c r="O67">
-        <v>-5.683181916666667</v>
+        <v>-5.744666766666668</v>
       </c>
       <c r="P67">
-        <v>-17.04954575</v>
+        <v>-17.2340003</v>
       </c>
       <c r="Q67">
-        <v>-0.8495457500000008</v>
+        <v>-1.034000300000002</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1984946934540688</v>
+        <v>0.2029857138497768</v>
       </c>
       <c r="T67">
-        <v>2.362138345002661</v>
+        <v>2.431613002208621</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>-0.1055085844265618</v>
+        <v>-0.1039099695110078</v>
       </c>
       <c r="W67">
-        <v>0.2606789242077833</v>
+        <v>0.2603019708106956</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6808,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>-0.4220343377062472</v>
+        <v>-0.4156398780440311</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6816,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2408144434439832</v>
+        <v>0.2427144434439832</v>
       </c>
       <c r="C68">
-        <v>-34.98174724657132</v>
+        <v>-36.30371315470587</v>
       </c>
       <c r="D68">
-        <v>31.76625275342869</v>
+        <v>31.48728684529413</v>
       </c>
       <c r="E68">
-        <v>9.838000000000008</v>
+        <v>10.881</v>
       </c>
       <c r="F68">
-        <v>68.83800000000001</v>
+        <v>69.881</v>
       </c>
       <c r="G68">
         <v>2.09</v>
@@ -6852,37 +6863,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M68">
-        <v>16.2320004</v>
+        <v>16.4779398</v>
       </c>
       <c r="N68">
-        <v>-22.97866706666667</v>
+        <v>-23.22460646666667</v>
       </c>
       <c r="O68">
-        <v>-5.744666766666668</v>
+        <v>-5.806151616666667</v>
       </c>
       <c r="P68">
-        <v>-17.2340003</v>
+        <v>-17.41845485</v>
       </c>
       <c r="Q68">
-        <v>-1.034000300000002</v>
+        <v>-1.218454850000001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2029857138497768</v>
+        <v>0.20774891729977</v>
       </c>
       <c r="T68">
-        <v>2.431613002208621</v>
+        <v>2.505298244699792</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>-0.1039099695110078</v>
+        <v>-0.1023590744436793</v>
       </c>
       <c r="W68">
-        <v>0.2603019708106956</v>
+        <v>0.2599362697538196</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6890,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>-0.4156398780440311</v>
+        <v>-0.4094362977747172</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6898,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2427144434439832</v>
+        <v>0.2446144434439832</v>
       </c>
       <c r="C69">
-        <v>-36.30371315470587</v>
+        <v>-37.62082205258108</v>
       </c>
       <c r="D69">
-        <v>31.48728684529413</v>
+        <v>31.21317794741893</v>
       </c>
       <c r="E69">
-        <v>10.881</v>
+        <v>11.92400000000001</v>
       </c>
       <c r="F69">
-        <v>69.881</v>
+        <v>70.92400000000001</v>
       </c>
       <c r="G69">
         <v>2.09</v>
@@ -6934,37 +6945,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M69">
-        <v>16.4779398</v>
+        <v>16.7238792</v>
       </c>
       <c r="N69">
-        <v>-23.22460646666667</v>
+        <v>-23.47054586666667</v>
       </c>
       <c r="O69">
-        <v>-5.806151616666667</v>
+        <v>-5.867636466666667</v>
       </c>
       <c r="P69">
-        <v>-17.41845485</v>
+        <v>-17.6029094</v>
       </c>
       <c r="Q69">
-        <v>-1.218454850000001</v>
+        <v>-1.402909400000002</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.20774891729977</v>
+        <v>0.2128098209653878</v>
       </c>
       <c r="T69">
-        <v>2.505298244699792</v>
+        <v>2.58358881484666</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>-0.1023590744436793</v>
+        <v>-0.1008537939371546</v>
       </c>
       <c r="W69">
-        <v>0.2599362697538196</v>
+        <v>0.259581324610381</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6972,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>-0.4094362977747172</v>
+        <v>-0.4034151757486184</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6980,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2446144434439832</v>
+        <v>0.2465144434439833</v>
       </c>
       <c r="C70">
-        <v>-37.62082205258108</v>
+        <v>-38.93319969188678</v>
       </c>
       <c r="D70">
-        <v>31.21317794741893</v>
+        <v>30.94380030811322</v>
       </c>
       <c r="E70">
-        <v>11.92400000000001</v>
+        <v>12.967</v>
       </c>
       <c r="F70">
-        <v>70.92400000000001</v>
+        <v>71.967</v>
       </c>
       <c r="G70">
         <v>2.09</v>
@@ -7016,37 +7027,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M70">
-        <v>16.7238792</v>
+        <v>16.9698186</v>
       </c>
       <c r="N70">
-        <v>-23.47054586666667</v>
+        <v>-23.71648526666667</v>
       </c>
       <c r="O70">
-        <v>-5.867636466666667</v>
+        <v>-5.929121316666667</v>
       </c>
       <c r="P70">
-        <v>-17.6029094</v>
+        <v>-17.78736395</v>
       </c>
       <c r="Q70">
-        <v>-1.402909400000002</v>
+        <v>-1.58736395</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2128098209653878</v>
+        <v>0.2181972345449165</v>
       </c>
       <c r="T70">
-        <v>2.58358881484666</v>
+        <v>2.666930389519134</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>-0.1008537939371546</v>
+        <v>-0.09939214474965964</v>
       </c>
       <c r="W70">
-        <v>0.259581324610381</v>
+        <v>0.2592366677319698</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7054,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>-0.4034151757486184</v>
+        <v>-0.3975685789986385</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7062,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2465144434439833</v>
+        <v>0.2484144434439832</v>
       </c>
       <c r="C71">
-        <v>-38.93319969188678</v>
+        <v>-40.24096752038105</v>
       </c>
       <c r="D71">
-        <v>30.94380030811322</v>
+        <v>30.67903247961896</v>
       </c>
       <c r="E71">
-        <v>12.967</v>
+        <v>14.01000000000001</v>
       </c>
       <c r="F71">
-        <v>71.967</v>
+        <v>73.01000000000001</v>
       </c>
       <c r="G71">
         <v>2.09</v>
@@ -7098,37 +7109,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M71">
-        <v>16.9698186</v>
+        <v>17.215758</v>
       </c>
       <c r="N71">
-        <v>-23.71648526666667</v>
+        <v>-23.96242466666667</v>
       </c>
       <c r="O71">
-        <v>-5.929121316666667</v>
+        <v>-5.990606166666667</v>
       </c>
       <c r="P71">
-        <v>-17.78736395</v>
+        <v>-17.9718185</v>
       </c>
       <c r="Q71">
-        <v>-1.58736395</v>
+        <v>-1.771818500000002</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2181972345449165</v>
+        <v>0.223943809029747</v>
       </c>
       <c r="T71">
-        <v>2.666930389519134</v>
+        <v>2.755828069169771</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>-0.09939214474965964</v>
+        <v>-0.09797225696752164</v>
       </c>
       <c r="W71">
-        <v>0.2592366677319698</v>
+        <v>0.2589018581929416</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7136,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>-0.3975685789986385</v>
+        <v>-0.3918890278700866</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7144,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2484144434439832</v>
+        <v>0.2503144434439832</v>
       </c>
       <c r="C72">
-        <v>-40.24096752038105</v>
+        <v>-41.54424286445894</v>
       </c>
       <c r="D72">
-        <v>30.67903247961896</v>
+        <v>30.41875713554108</v>
       </c>
       <c r="E72">
-        <v>14.01000000000001</v>
+        <v>15.05300000000001</v>
       </c>
       <c r="F72">
-        <v>73.01000000000001</v>
+        <v>74.05300000000001</v>
       </c>
       <c r="G72">
         <v>2.09</v>
@@ -7180,37 +7191,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M72">
-        <v>17.215758</v>
+        <v>17.4616974</v>
       </c>
       <c r="N72">
-        <v>-23.96242466666667</v>
+        <v>-24.20836406666667</v>
       </c>
       <c r="O72">
-        <v>-5.990606166666667</v>
+        <v>-6.052091016666667</v>
       </c>
       <c r="P72">
-        <v>-17.9718185</v>
+        <v>-18.15627305</v>
       </c>
       <c r="Q72">
-        <v>-1.771818500000002</v>
+        <v>-1.956273050000004</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.223943809029747</v>
+        <v>0.23008669899629</v>
       </c>
       <c r="T72">
-        <v>2.755828069169771</v>
+        <v>2.850856623279074</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>-0.09797225696752164</v>
+        <v>-0.0965923660243171</v>
       </c>
       <c r="W72">
-        <v>0.2589018581929416</v>
+        <v>0.258576479908534</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7218,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>-0.3918890278700866</v>
+        <v>-0.3863694640972684</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7226,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2503144434439832</v>
+        <v>0.2522144434439832</v>
       </c>
       <c r="C73">
-        <v>-41.54424286445892</v>
+        <v>-42.84313910250631</v>
       </c>
       <c r="D73">
-        <v>30.41875713554108</v>
+        <v>30.16286089749368</v>
       </c>
       <c r="E73">
-        <v>15.053</v>
+        <v>16.09599999999999</v>
       </c>
       <c r="F73">
-        <v>74.053</v>
+        <v>75.09599999999999</v>
       </c>
       <c r="G73">
         <v>2.09</v>
@@ -7262,37 +7273,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M73">
-        <v>17.4616974</v>
+        <v>17.7076368</v>
       </c>
       <c r="N73">
-        <v>-24.20836406666666</v>
+        <v>-24.45430346666667</v>
       </c>
       <c r="O73">
-        <v>-6.052091016666666</v>
+        <v>-6.113575866666666</v>
       </c>
       <c r="P73">
-        <v>-18.15627305</v>
+        <v>-18.3407276</v>
       </c>
       <c r="Q73">
-        <v>-1.95627305</v>
+        <v>-2.140727600000002</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.23008669899629</v>
+        <v>0.236668366817586</v>
       </c>
       <c r="T73">
-        <v>2.850856623279073</v>
+        <v>2.952672931253325</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>-0.09659236602431713</v>
+        <v>-0.0952508053850905</v>
       </c>
       <c r="W73">
-        <v>0.258576479908534</v>
+        <v>0.2582601399098043</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7300,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>-0.3863694640972686</v>
+        <v>-0.381003221540362</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7308,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2522144434439832</v>
+        <v>0.2541144434439832</v>
       </c>
       <c r="C74">
-        <v>-42.84313910250631</v>
+        <v>-44.13776582957673</v>
       </c>
       <c r="D74">
-        <v>30.16286089749368</v>
+        <v>29.91123417042327</v>
       </c>
       <c r="E74">
-        <v>16.09599999999999</v>
+        <v>17.139</v>
       </c>
       <c r="F74">
-        <v>75.09599999999999</v>
+        <v>76.139</v>
       </c>
       <c r="G74">
         <v>2.09</v>
@@ -7344,37 +7355,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M74">
-        <v>17.7076368</v>
+        <v>17.9535762</v>
       </c>
       <c r="N74">
-        <v>-24.45430346666667</v>
+        <v>-24.70024286666667</v>
       </c>
       <c r="O74">
-        <v>-6.113575866666666</v>
+        <v>-6.175060716666667</v>
       </c>
       <c r="P74">
-        <v>-18.3407276</v>
+        <v>-18.52518215</v>
       </c>
       <c r="Q74">
-        <v>-2.140727600000002</v>
+        <v>-2.32518215</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.236668366817586</v>
+        <v>0.2437375655886077</v>
       </c>
       <c r="T74">
-        <v>2.952672931253325</v>
+        <v>3.062031187966411</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>-0.0952508053850905</v>
+        <v>-0.09394599983187008</v>
       </c>
       <c r="W74">
-        <v>0.2582601399098043</v>
+        <v>0.257952466760355</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7382,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>-0.381003221540362</v>
+        <v>-0.3757839993274803</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7390,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2541144434439832</v>
+        <v>0.2560144434439832</v>
       </c>
       <c r="C75">
-        <v>-44.13776582957673</v>
+        <v>-45.4282290138936</v>
       </c>
       <c r="D75">
-        <v>29.91123417042327</v>
+        <v>29.66377098610641</v>
       </c>
       <c r="E75">
-        <v>17.139</v>
+        <v>18.182</v>
       </c>
       <c r="F75">
-        <v>76.139</v>
+        <v>77.182</v>
       </c>
       <c r="G75">
         <v>2.09</v>
@@ -7426,37 +7437,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M75">
-        <v>17.9535762</v>
+        <v>18.1995156</v>
       </c>
       <c r="N75">
-        <v>-24.70024286666667</v>
+        <v>-24.94618226666667</v>
       </c>
       <c r="O75">
-        <v>-6.175060716666667</v>
+        <v>-6.236545566666667</v>
       </c>
       <c r="P75">
-        <v>-18.52518215</v>
+        <v>-18.7096367</v>
       </c>
       <c r="Q75">
-        <v>-2.32518215</v>
+        <v>-2.509636700000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2437375655886077</v>
+        <v>0.2513505488804772</v>
       </c>
       <c r="T75">
-        <v>3.062031187966411</v>
+        <v>3.179801618272811</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>-0.09394599983187008</v>
+        <v>-0.09267645929360155</v>
       </c>
       <c r="W75">
-        <v>0.257952466760355</v>
+        <v>0.2576531091014312</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7464,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>-0.3757839993274803</v>
+        <v>-0.3707058371744063</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7472,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2560144434439832</v>
+        <v>0.2579144434439832</v>
       </c>
       <c r="C76">
-        <v>-45.4282290138936</v>
+        <v>-46.71463114564762</v>
       </c>
       <c r="D76">
-        <v>29.66377098610641</v>
+        <v>29.42036885435238</v>
       </c>
       <c r="E76">
-        <v>18.182</v>
+        <v>19.22499999999999</v>
       </c>
       <c r="F76">
-        <v>77.182</v>
+        <v>78.22499999999999</v>
       </c>
       <c r="G76">
         <v>2.09</v>
@@ -7508,37 +7519,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M76">
-        <v>18.1995156</v>
+        <v>18.445455</v>
       </c>
       <c r="N76">
-        <v>-24.94618226666667</v>
+        <v>-25.19212166666667</v>
       </c>
       <c r="O76">
-        <v>-6.236545566666667</v>
+        <v>-6.298030416666666</v>
       </c>
       <c r="P76">
-        <v>-18.7096367</v>
+        <v>-18.89409125</v>
       </c>
       <c r="Q76">
-        <v>-2.509636700000001</v>
+        <v>-2.69409125</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2513505488804772</v>
+        <v>0.2595725708356964</v>
       </c>
       <c r="T76">
-        <v>3.179801618272811</v>
+        <v>3.306993683003725</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>-0.09267645929360155</v>
+        <v>-0.09144077316968688</v>
       </c>
       <c r="W76">
-        <v>0.2576531091014312</v>
+        <v>0.2573617343134122</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7546,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>-0.3707058371744063</v>
+        <v>-0.3657630926787474</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7554,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2579144434439832</v>
+        <v>0.2598144434439832</v>
       </c>
       <c r="C77">
-        <v>-46.71463114564762</v>
+        <v>-47.99707137852816</v>
       </c>
       <c r="D77">
-        <v>29.42036885435238</v>
+        <v>29.18092862147184</v>
       </c>
       <c r="E77">
-        <v>19.22499999999999</v>
+        <v>20.268</v>
       </c>
       <c r="F77">
-        <v>78.22499999999999</v>
+        <v>79.268</v>
       </c>
       <c r="G77">
         <v>2.09</v>
@@ -7590,37 +7601,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M77">
-        <v>18.445455</v>
+        <v>18.6913944</v>
       </c>
       <c r="N77">
-        <v>-25.19212166666667</v>
+        <v>-25.43806106666667</v>
       </c>
       <c r="O77">
-        <v>-6.298030416666666</v>
+        <v>-6.359515266666667</v>
       </c>
       <c r="P77">
-        <v>-18.89409125</v>
+        <v>-19.0785458</v>
       </c>
       <c r="Q77">
-        <v>-2.69409125</v>
+        <v>-2.878545800000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2595725708356964</v>
+        <v>0.2684797612871837</v>
       </c>
       <c r="T77">
-        <v>3.306993683003725</v>
+        <v>3.444785086462213</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>-0.09144077316968688</v>
+        <v>-0.09023760510166468</v>
       </c>
       <c r="W77">
-        <v>0.2573617343134122</v>
+        <v>0.2570780272829725</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7628,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>-0.3657630926787474</v>
+        <v>-0.3609504204066587</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7636,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2598144434439832</v>
+        <v>0.2617144434439833</v>
       </c>
       <c r="C78">
-        <v>-47.99707137852816</v>
+        <v>-49.27564566439918</v>
       </c>
       <c r="D78">
-        <v>29.18092862147184</v>
+        <v>28.94535433560082</v>
       </c>
       <c r="E78">
-        <v>20.268</v>
+        <v>21.31099999999999</v>
       </c>
       <c r="F78">
-        <v>79.268</v>
+        <v>80.31099999999999</v>
       </c>
       <c r="G78">
         <v>2.09</v>
@@ -7672,37 +7683,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M78">
-        <v>18.6913944</v>
+        <v>18.9373338</v>
       </c>
       <c r="N78">
-        <v>-25.43806106666667</v>
+        <v>-25.68400046666666</v>
       </c>
       <c r="O78">
-        <v>-6.359515266666667</v>
+        <v>-6.421000116666666</v>
       </c>
       <c r="P78">
-        <v>-19.0785458</v>
+        <v>-19.26300035</v>
       </c>
       <c r="Q78">
-        <v>-2.878545800000001</v>
+        <v>-3.063000349999999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2684797612871837</v>
+        <v>0.2781614900388004</v>
       </c>
       <c r="T78">
-        <v>3.444785086462213</v>
+        <v>3.594558351091006</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>-0.09023760510166468</v>
+        <v>-0.08906568815229242</v>
       </c>
       <c r="W78">
-        <v>0.2570780272829725</v>
+        <v>0.2568016892663106</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7710,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>-0.3609504204066587</v>
+        <v>-0.3562627526091697</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7718,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2617144434439833</v>
+        <v>0.2636144434439832</v>
       </c>
       <c r="C79">
-        <v>-49.27564566439918</v>
+        <v>-50.55044688150409</v>
       </c>
       <c r="D79">
-        <v>28.94535433560082</v>
+        <v>28.71355311849591</v>
       </c>
       <c r="E79">
-        <v>21.31099999999999</v>
+        <v>22.354</v>
       </c>
       <c r="F79">
-        <v>80.31099999999999</v>
+        <v>81.354</v>
       </c>
       <c r="G79">
         <v>2.09</v>
@@ -7754,37 +7765,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M79">
-        <v>18.9373338</v>
+        <v>19.1832732</v>
       </c>
       <c r="N79">
-        <v>-25.68400046666666</v>
+        <v>-25.92993986666667</v>
       </c>
       <c r="O79">
-        <v>-6.421000116666666</v>
+        <v>-6.482484966666667</v>
       </c>
       <c r="P79">
-        <v>-19.26300035</v>
+        <v>-19.4474549</v>
       </c>
       <c r="Q79">
-        <v>-3.063000349999999</v>
+        <v>-3.247454900000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2781614900388004</v>
+        <v>0.288723375949655</v>
       </c>
       <c r="T79">
-        <v>3.594558351091006</v>
+        <v>3.757947367049688</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>-0.08906568815229242</v>
+        <v>-0.08792382035546814</v>
       </c>
       <c r="W79">
-        <v>0.2568016892663106</v>
+        <v>0.2565324368398194</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7792,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>-0.3562627526091697</v>
+        <v>-0.3516952814218726</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7800,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2636144434439832</v>
+        <v>0.2655144434439832</v>
       </c>
       <c r="C80">
-        <v>-50.55044688150409</v>
+        <v>-51.82156495655947</v>
       </c>
       <c r="D80">
-        <v>28.71355311849591</v>
+        <v>28.48543504344054</v>
       </c>
       <c r="E80">
-        <v>22.354</v>
+        <v>23.39700000000001</v>
       </c>
       <c r="F80">
-        <v>81.354</v>
+        <v>82.39700000000001</v>
       </c>
       <c r="G80">
         <v>2.09</v>
@@ -7836,37 +7847,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M80">
-        <v>19.1832732</v>
+        <v>19.4292126</v>
       </c>
       <c r="N80">
-        <v>-25.92993986666667</v>
+        <v>-26.17587926666667</v>
       </c>
       <c r="O80">
-        <v>-6.482484966666667</v>
+        <v>-6.543969816666667</v>
       </c>
       <c r="P80">
-        <v>-19.4474549</v>
+        <v>-19.63190945</v>
       </c>
       <c r="Q80">
-        <v>-3.247454900000001</v>
+        <v>-3.431909450000003</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.288723375949655</v>
+        <v>0.3002911557567814</v>
       </c>
       <c r="T80">
-        <v>3.757947367049688</v>
+        <v>3.936897241671101</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>-0.08792382035546814</v>
+        <v>-0.08681086060413309</v>
       </c>
       <c r="W80">
-        <v>0.2565324368398194</v>
+        <v>0.2562700009304546</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7874,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>-0.3516952814218726</v>
+        <v>-0.3472434424165323</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7882,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2655144434439832</v>
+        <v>0.2674144434439832</v>
       </c>
       <c r="C81">
-        <v>-51.82156495655947</v>
+        <v>-53.08908698107449</v>
       </c>
       <c r="D81">
-        <v>28.48543504344054</v>
+        <v>28.26091301892551</v>
       </c>
       <c r="E81">
-        <v>23.39700000000001</v>
+        <v>24.44</v>
       </c>
       <c r="F81">
-        <v>82.39700000000001</v>
+        <v>83.44</v>
       </c>
       <c r="G81">
         <v>2.09</v>
@@ -7918,37 +7929,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M81">
-        <v>19.4292126</v>
+        <v>19.675152</v>
       </c>
       <c r="N81">
-        <v>-26.17587926666667</v>
+        <v>-26.42181866666667</v>
       </c>
       <c r="O81">
-        <v>-6.543969816666667</v>
+        <v>-6.605454666666667</v>
       </c>
       <c r="P81">
-        <v>-19.63190945</v>
+        <v>-19.816364</v>
       </c>
       <c r="Q81">
-        <v>-3.431909450000003</v>
+        <v>-3.616364000000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3002911557567814</v>
+        <v>0.3130157135446205</v>
       </c>
       <c r="T81">
-        <v>3.936897241671101</v>
+        <v>4.133742103754657</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>-0.08681086060413309</v>
+        <v>-0.08572572484658143</v>
       </c>
       <c r="W81">
-        <v>0.2562700009304546</v>
+        <v>0.2560141259188239</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7956,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>-0.3472434424165323</v>
+        <v>-0.3429028993863257</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7964,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2674144434439832</v>
+        <v>0.2693144434439832</v>
       </c>
       <c r="C82">
-        <v>-53.08908698107449</v>
+        <v>-54.3530973222127</v>
       </c>
       <c r="D82">
-        <v>28.26091301892551</v>
+        <v>28.03990267778731</v>
       </c>
       <c r="E82">
-        <v>24.44</v>
+        <v>25.483</v>
       </c>
       <c r="F82">
-        <v>83.44</v>
+        <v>84.483</v>
       </c>
       <c r="G82">
         <v>2.09</v>
@@ -8000,37 +8011,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M82">
-        <v>19.675152</v>
+        <v>19.9210914</v>
       </c>
       <c r="N82">
-        <v>-26.42181866666667</v>
+        <v>-26.66775806666667</v>
       </c>
       <c r="O82">
-        <v>-6.605454666666667</v>
+        <v>-6.666939516666667</v>
       </c>
       <c r="P82">
-        <v>-19.816364</v>
+        <v>-20.00081855</v>
       </c>
       <c r="Q82">
-        <v>-3.616364000000001</v>
+        <v>-3.800818550000002</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3130157135446205</v>
+        <v>0.3270796984680216</v>
       </c>
       <c r="T82">
-        <v>4.133742103754657</v>
+        <v>4.351307477636481</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>-0.08572572484658143</v>
+        <v>-0.08466738256452487</v>
       </c>
       <c r="W82">
-        <v>0.2560141259188239</v>
+        <v>0.255764568808715</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8038,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>-0.3429028993863257</v>
+        <v>-0.3386695302580995</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8046,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2693144434439832</v>
+        <v>0.2712144434439833</v>
       </c>
       <c r="C83">
-        <v>-54.3530973222127</v>
+        <v>-55.61367772849206</v>
       </c>
       <c r="D83">
-        <v>28.03990267778731</v>
+        <v>27.82232227150795</v>
       </c>
       <c r="E83">
-        <v>25.483</v>
+        <v>26.52600000000001</v>
       </c>
       <c r="F83">
-        <v>84.483</v>
+        <v>85.52600000000001</v>
       </c>
       <c r="G83">
         <v>2.09</v>
@@ -8082,37 +8093,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M83">
-        <v>19.9210914</v>
+        <v>20.1670308</v>
       </c>
       <c r="N83">
-        <v>-26.66775806666667</v>
+        <v>-26.91369746666667</v>
       </c>
       <c r="O83">
-        <v>-6.666939516666667</v>
+        <v>-6.728424366666667</v>
       </c>
       <c r="P83">
-        <v>-20.00081855</v>
+        <v>-20.1852731</v>
       </c>
       <c r="Q83">
-        <v>-3.800818550000002</v>
+        <v>-3.985273100000004</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3270796984680216</v>
+        <v>0.3427063483829118</v>
       </c>
       <c r="T83">
-        <v>4.351307477636481</v>
+        <v>4.59304678194962</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>-0.08466738256452487</v>
+        <v>-0.08363485350885994</v>
       </c>
       <c r="W83">
-        <v>0.255764568808715</v>
+        <v>0.2555210984573892</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8120,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>-0.3386695302580995</v>
+        <v>-0.3345394140354396</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8128,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2712144434439833</v>
+        <v>0.2731144434439832</v>
       </c>
       <c r="C84">
-        <v>-55.61367772849206</v>
+        <v>-56.87090743060175</v>
       </c>
       <c r="D84">
-        <v>27.82232227150795</v>
+        <v>27.60809256939825</v>
       </c>
       <c r="E84">
-        <v>26.52600000000001</v>
+        <v>27.569</v>
       </c>
       <c r="F84">
-        <v>85.52600000000001</v>
+        <v>86.569</v>
       </c>
       <c r="G84">
         <v>2.09</v>
@@ -8164,37 +8175,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M84">
-        <v>20.1670308</v>
+        <v>20.4129702</v>
       </c>
       <c r="N84">
-        <v>-26.91369746666667</v>
+        <v>-27.15963686666667</v>
       </c>
       <c r="O84">
-        <v>-6.728424366666667</v>
+        <v>-6.789909216666667</v>
       </c>
       <c r="P84">
-        <v>-20.1852731</v>
+        <v>-20.36972765</v>
       </c>
       <c r="Q84">
-        <v>-3.985273100000004</v>
+        <v>-4.169727650000002</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3427063483829118</v>
+        <v>0.3601714276995536</v>
       </c>
       <c r="T84">
-        <v>4.59304678194962</v>
+        <v>4.863226004417244</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>-0.08363485350885994</v>
+        <v>-0.0826272046714038</v>
       </c>
       <c r="W84">
-        <v>0.2555210984573892</v>
+        <v>0.255283494861517</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8202,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>-0.3345394140354396</v>
+        <v>-0.3305088186856151</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8210,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2731144434439832</v>
+        <v>0.2750144434439832</v>
       </c>
       <c r="C85">
-        <v>-56.87090743060175</v>
+        <v>-58.12486323759703</v>
       </c>
       <c r="D85">
-        <v>27.60809256939825</v>
+        <v>27.39713676240298</v>
       </c>
       <c r="E85">
-        <v>27.569</v>
+        <v>28.61200000000001</v>
       </c>
       <c r="F85">
-        <v>86.569</v>
+        <v>87.61200000000001</v>
       </c>
       <c r="G85">
         <v>2.09</v>
@@ -8246,37 +8257,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M85">
-        <v>20.4129702</v>
+        <v>20.6589096</v>
       </c>
       <c r="N85">
-        <v>-27.15963686666667</v>
+        <v>-27.40557626666667</v>
       </c>
       <c r="O85">
-        <v>-6.789909216666667</v>
+        <v>-6.851394066666667</v>
       </c>
       <c r="P85">
-        <v>-20.36972765</v>
+        <v>-20.5541822</v>
       </c>
       <c r="Q85">
-        <v>-4.169727650000002</v>
+        <v>-4.3541822</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3601714276995536</v>
+        <v>0.3798196419307757</v>
       </c>
       <c r="T85">
-        <v>4.863226004417244</v>
+        <v>5.167177629693322</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>-0.0826272046714038</v>
+        <v>-0.0816435474729347</v>
       </c>
       <c r="W85">
-        <v>0.255283494861517</v>
+        <v>0.255051548494118</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8284,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>-0.3305088186856151</v>
+        <v>-0.3265741898917387</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8292,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2750144434439832</v>
+        <v>0.2769144434439832</v>
       </c>
       <c r="C86">
-        <v>-58.12486323759701</v>
+        <v>-59.37561962871704</v>
       </c>
       <c r="D86">
-        <v>27.39713676240298</v>
+        <v>27.18938037128296</v>
       </c>
       <c r="E86">
-        <v>28.61199999999999</v>
+        <v>29.655</v>
       </c>
       <c r="F86">
-        <v>87.61199999999999</v>
+        <v>88.655</v>
       </c>
       <c r="G86">
         <v>2.09</v>
@@ -8328,37 +8339,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M86">
-        <v>20.6589096</v>
+        <v>20.904849</v>
       </c>
       <c r="N86">
-        <v>-27.40557626666667</v>
+        <v>-27.65151566666667</v>
       </c>
       <c r="O86">
-        <v>-6.851394066666667</v>
+        <v>-6.912878916666667</v>
       </c>
       <c r="P86">
-        <v>-20.5541822</v>
+        <v>-20.73863675</v>
       </c>
       <c r="Q86">
-        <v>-4.3541822</v>
+        <v>-4.538636750000002</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3798196419307756</v>
+        <v>0.4020876180594939</v>
       </c>
       <c r="T86">
-        <v>5.167177629693319</v>
+        <v>5.51165613833954</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>-0.0816435474729347</v>
+        <v>-0.08068303514972371</v>
       </c>
       <c r="W86">
-        <v>0.255051548494118</v>
+        <v>0.2548250596883048</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8366,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>-0.3265741898917387</v>
+        <v>-0.3227321405988948</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8374,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2769144434439832</v>
+        <v>0.2788144434439833</v>
       </c>
       <c r="C87">
-        <v>-59.37561962871704</v>
+        <v>-60.62324884105674</v>
       </c>
       <c r="D87">
-        <v>27.18938037128296</v>
+        <v>26.98475115894325</v>
       </c>
       <c r="E87">
-        <v>29.655</v>
+        <v>30.69799999999999</v>
       </c>
       <c r="F87">
-        <v>88.655</v>
+        <v>89.69799999999999</v>
       </c>
       <c r="G87">
         <v>2.09</v>
@@ -8410,37 +8421,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M87">
-        <v>20.904849</v>
+        <v>21.1507884</v>
       </c>
       <c r="N87">
-        <v>-27.65151566666667</v>
+        <v>-27.89745506666667</v>
       </c>
       <c r="O87">
-        <v>-6.912878916666667</v>
+        <v>-6.974363766666666</v>
       </c>
       <c r="P87">
-        <v>-20.73863675</v>
+        <v>-20.9230913</v>
       </c>
       <c r="Q87">
-        <v>-4.538636750000002</v>
+        <v>-4.7230913</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4020876180594939</v>
+        <v>0.427536733635172</v>
       </c>
       <c r="T87">
-        <v>5.51165613833954</v>
+        <v>5.905345862506651</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>-0.08068303514972371</v>
+        <v>-0.07974486032240134</v>
       </c>
       <c r="W87">
-        <v>0.2548250596883048</v>
+        <v>0.2546038380640223</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8448,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>-0.3227321405988948</v>
+        <v>-0.3189794412896054</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8456,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2788144434439833</v>
+        <v>0.2807144434439832</v>
       </c>
       <c r="C88">
-        <v>-60.62324884105674</v>
+        <v>-61.86782095330929</v>
       </c>
       <c r="D88">
-        <v>26.98475115894325</v>
+        <v>26.78317904669071</v>
       </c>
       <c r="E88">
-        <v>30.69799999999999</v>
+        <v>31.741</v>
       </c>
       <c r="F88">
-        <v>89.69799999999999</v>
+        <v>90.741</v>
       </c>
       <c r="G88">
         <v>2.09</v>
@@ -8492,37 +8503,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M88">
-        <v>21.1507884</v>
+        <v>21.3967278</v>
       </c>
       <c r="N88">
-        <v>-27.89745506666667</v>
+        <v>-28.14339446666667</v>
       </c>
       <c r="O88">
-        <v>-6.974363766666666</v>
+        <v>-7.035848616666667</v>
       </c>
       <c r="P88">
-        <v>-20.9230913</v>
+        <v>-21.10754585</v>
       </c>
       <c r="Q88">
-        <v>-4.7230913</v>
+        <v>-4.907545850000002</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.427536733635172</v>
+        <v>0.4569010977609544</v>
       </c>
       <c r="T88">
-        <v>5.905345862506651</v>
+        <v>6.359603236545623</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>-0.07974486032240134</v>
+        <v>-0.07882825273248868</v>
       </c>
       <c r="W88">
-        <v>0.2546038380640223</v>
+        <v>0.2543877019943208</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8530,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>-0.3189794412896054</v>
+        <v>-0.3153130109299547</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8538,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2807144434439832</v>
+        <v>0.2826144434439832</v>
       </c>
       <c r="C89">
-        <v>-61.86782095330929</v>
+        <v>-63.10940396578306</v>
       </c>
       <c r="D89">
-        <v>26.78317904669071</v>
+        <v>26.58459603421694</v>
       </c>
       <c r="E89">
-        <v>31.741</v>
+        <v>32.78399999999999</v>
       </c>
       <c r="F89">
-        <v>90.741</v>
+        <v>91.78399999999999</v>
       </c>
       <c r="G89">
         <v>2.09</v>
@@ -8574,37 +8585,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M89">
-        <v>21.3967278</v>
+        <v>21.6426672</v>
       </c>
       <c r="N89">
-        <v>-28.14339446666667</v>
+        <v>-28.38933386666666</v>
       </c>
       <c r="O89">
-        <v>-7.035848616666667</v>
+        <v>-7.097333466666666</v>
       </c>
       <c r="P89">
-        <v>-21.10754585</v>
+        <v>-21.2920004</v>
       </c>
       <c r="Q89">
-        <v>-4.907545850000002</v>
+        <v>-5.0920004</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4569010977609544</v>
+        <v>0.4911595225743675</v>
       </c>
       <c r="T89">
-        <v>6.359603236545623</v>
+        <v>6.889570172924427</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>-0.07882825273248868</v>
+        <v>-0.07793247713325586</v>
       </c>
       <c r="W89">
-        <v>0.2543877019943208</v>
+        <v>0.2541764781080217</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8612,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>-0.3153130109299547</v>
+        <v>-0.3117299085330234</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8620,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2826144434439832</v>
+        <v>0.2845144434439832</v>
       </c>
       <c r="C90">
-        <v>-63.10940396578306</v>
+        <v>-64.34806387688511</v>
       </c>
       <c r="D90">
-        <v>26.58459603421694</v>
+        <v>26.38893612311489</v>
       </c>
       <c r="E90">
-        <v>32.78399999999999</v>
+        <v>33.827</v>
       </c>
       <c r="F90">
-        <v>91.78399999999999</v>
+        <v>92.827</v>
       </c>
       <c r="G90">
         <v>2.09</v>
@@ -8656,37 +8667,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M90">
-        <v>21.6426672</v>
+        <v>21.8886066</v>
       </c>
       <c r="N90">
-        <v>-28.38933386666666</v>
+        <v>-28.63527326666667</v>
       </c>
       <c r="O90">
-        <v>-7.097333466666666</v>
+        <v>-7.158818316666666</v>
       </c>
       <c r="P90">
-        <v>-21.2920004</v>
+        <v>-21.47645495</v>
       </c>
       <c r="Q90">
-        <v>-5.0920004</v>
+        <v>-5.276454949999998</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4911595225743675</v>
+        <v>0.5316467518993099</v>
       </c>
       <c r="T90">
-        <v>6.889570172924427</v>
+        <v>7.515894734099374</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>-0.07793247713325586</v>
+        <v>-0.07705683132276983</v>
       </c>
       <c r="W90">
-        <v>0.2541764781080217</v>
+        <v>0.2539700008259091</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8694,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>-0.3117299085330234</v>
+        <v>-0.3082273252910794</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8702,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2845144434439832</v>
+        <v>0.2864144434439831</v>
       </c>
       <c r="C91">
-        <v>-64.34806387688511</v>
+        <v>-65.58386475625196</v>
       </c>
       <c r="D91">
-        <v>26.38893612311489</v>
+        <v>26.19613524374806</v>
       </c>
       <c r="E91">
-        <v>33.827</v>
+        <v>34.87</v>
       </c>
       <c r="F91">
-        <v>92.827</v>
+        <v>93.87</v>
       </c>
       <c r="G91">
         <v>2.09</v>
@@ -8738,37 +8749,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M91">
-        <v>21.8886066</v>
+        <v>22.134546</v>
       </c>
       <c r="N91">
-        <v>-28.63527326666667</v>
+        <v>-28.88121266666667</v>
       </c>
       <c r="O91">
-        <v>-7.158818316666666</v>
+        <v>-7.220303166666667</v>
       </c>
       <c r="P91">
-        <v>-21.47645495</v>
+        <v>-21.6609095</v>
       </c>
       <c r="Q91">
-        <v>-5.276454949999998</v>
+        <v>-5.4609095</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5316467518993099</v>
+        <v>0.5802314270892409</v>
       </c>
       <c r="T91">
-        <v>7.515894734099374</v>
+        <v>8.267484207509312</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>-0.07705683132276983</v>
+        <v>-0.07620064430807238</v>
       </c>
       <c r="W91">
-        <v>0.2539700008259091</v>
+        <v>0.2537681119278434</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8776,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>-0.3082273252910794</v>
+        <v>-0.3048025772322895</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8784,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2864144434439831</v>
+        <v>0.2883144434439833</v>
       </c>
       <c r="C92">
-        <v>-65.58386475625196</v>
+        <v>-66.81686881469763</v>
       </c>
       <c r="D92">
-        <v>26.19613524374806</v>
+        <v>26.00613118530237</v>
       </c>
       <c r="E92">
-        <v>34.87</v>
+        <v>35.913</v>
       </c>
       <c r="F92">
-        <v>93.87</v>
+        <v>94.913</v>
       </c>
       <c r="G92">
         <v>2.09</v>
@@ -8820,37 +8831,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M92">
-        <v>22.134546</v>
+        <v>22.3804854</v>
       </c>
       <c r="N92">
-        <v>-28.88121266666667</v>
+        <v>-29.12715206666667</v>
       </c>
       <c r="O92">
-        <v>-7.220303166666667</v>
+        <v>-7.281788016666667</v>
       </c>
       <c r="P92">
-        <v>-21.6609095</v>
+        <v>-21.84536405</v>
       </c>
       <c r="Q92">
-        <v>-5.4609095</v>
+        <v>-5.645364050000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5802314270892409</v>
+        <v>0.6396126967658234</v>
       </c>
       <c r="T92">
-        <v>8.267484207509312</v>
+        <v>9.18609356389924</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>-0.07620064430807238</v>
+        <v>-0.07536327459040126</v>
       </c>
       <c r="W92">
-        <v>0.2537681119278434</v>
+        <v>0.2535706601484167</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8858,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>-0.3048025772322895</v>
+        <v>-0.3014530983616051</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8866,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2883144434439833</v>
+        <v>0.2902144434439832</v>
       </c>
       <c r="C93">
-        <v>-66.81686881469763</v>
+        <v>-68.04713647113979</v>
       </c>
       <c r="D93">
-        <v>26.00613118530237</v>
+        <v>25.81886352886021</v>
       </c>
       <c r="E93">
-        <v>35.913</v>
+        <v>36.956</v>
       </c>
       <c r="F93">
-        <v>94.913</v>
+        <v>95.956</v>
       </c>
       <c r="G93">
         <v>2.09</v>
@@ -8902,37 +8913,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M93">
-        <v>22.3804854</v>
+        <v>22.6264248</v>
       </c>
       <c r="N93">
-        <v>-29.12715206666667</v>
+        <v>-29.37309146666667</v>
       </c>
       <c r="O93">
-        <v>-7.281788016666667</v>
+        <v>-7.343272866666667</v>
       </c>
       <c r="P93">
-        <v>-21.84536405</v>
+        <v>-22.0298186</v>
       </c>
       <c r="Q93">
-        <v>-5.645364050000001</v>
+        <v>-5.829818600000003</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6396126967658234</v>
+        <v>0.7138392838615514</v>
       </c>
       <c r="T93">
-        <v>9.18609356389924</v>
+        <v>10.33435525938664</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>-0.07536327459040126</v>
+        <v>-0.07454410856224472</v>
       </c>
       <c r="W93">
-        <v>0.2535706601484167</v>
+        <v>0.2533775007989773</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8940,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>-0.3014530983616051</v>
+        <v>-0.298176434248979</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8948,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2902144434439832</v>
+        <v>0.2921144434439832</v>
       </c>
       <c r="C94">
-        <v>-68.04713647113979</v>
+        <v>-69.27472641665477</v>
       </c>
       <c r="D94">
-        <v>25.81886352886021</v>
+        <v>25.63427358334523</v>
       </c>
       <c r="E94">
-        <v>36.956</v>
+        <v>37.99900000000001</v>
       </c>
       <c r="F94">
-        <v>95.956</v>
+        <v>96.99900000000001</v>
       </c>
       <c r="G94">
         <v>2.09</v>
@@ -8984,37 +8995,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M94">
-        <v>22.6264248</v>
+        <v>22.8723642</v>
       </c>
       <c r="N94">
-        <v>-29.37309146666667</v>
+        <v>-29.61903086666667</v>
       </c>
       <c r="O94">
-        <v>-7.343272866666667</v>
+        <v>-7.404757716666667</v>
       </c>
       <c r="P94">
-        <v>-22.0298186</v>
+        <v>-22.21427315</v>
       </c>
       <c r="Q94">
-        <v>-5.829818600000003</v>
+        <v>-6.014273150000005</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7138392838615514</v>
+        <v>0.8092734672703448</v>
       </c>
       <c r="T94">
-        <v>10.33435525938664</v>
+        <v>11.81069172501331</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>-0.07454410856224472</v>
+        <v>-0.07374255900781199</v>
       </c>
       <c r="W94">
-        <v>0.2533775007989773</v>
+        <v>0.2531884954140421</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9022,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>-0.298176434248979</v>
+        <v>-0.2949702360312478</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9030,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2921144434439832</v>
+        <v>0.2940144434439832</v>
       </c>
       <c r="C95">
-        <v>-69.27472641665477</v>
+        <v>-70.49969567580446</v>
       </c>
       <c r="D95">
-        <v>25.63427358334523</v>
+        <v>25.45230432419554</v>
       </c>
       <c r="E95">
-        <v>37.99900000000001</v>
+        <v>39.042</v>
       </c>
       <c r="F95">
-        <v>96.99900000000001</v>
+        <v>98.042</v>
       </c>
       <c r="G95">
         <v>2.09</v>
@@ -9066,37 +9077,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M95">
-        <v>22.8723642</v>
+        <v>23.1183036</v>
       </c>
       <c r="N95">
-        <v>-29.61903086666667</v>
+        <v>-29.86497026666667</v>
       </c>
       <c r="O95">
-        <v>-7.404757716666667</v>
+        <v>-7.466242566666667</v>
       </c>
       <c r="P95">
-        <v>-22.21427315</v>
+        <v>-22.3987277</v>
       </c>
       <c r="Q95">
-        <v>-6.014273150000005</v>
+        <v>-6.198727700000003</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8092734672703448</v>
+        <v>0.9365190451487356</v>
       </c>
       <c r="T95">
-        <v>11.81069172501331</v>
+        <v>13.77914034584887</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>-0.07374255900781199</v>
+        <v>-0.07295806369921824</v>
       </c>
       <c r="W95">
-        <v>0.2531884954140421</v>
+        <v>0.2530035114202757</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9104,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>-0.2949702360312478</v>
+        <v>-0.291832254796873</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9112,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2940144434439832</v>
+        <v>0.2959144434439833</v>
       </c>
       <c r="C96">
-        <v>-70.49969567580446</v>
+        <v>-71.72209966536963</v>
       </c>
       <c r="D96">
-        <v>25.45230432419554</v>
+        <v>25.27290033463038</v>
       </c>
       <c r="E96">
-        <v>39.042</v>
+        <v>40.08500000000001</v>
       </c>
       <c r="F96">
-        <v>98.042</v>
+        <v>99.08500000000001</v>
       </c>
       <c r="G96">
         <v>2.09</v>
@@ -9148,37 +9159,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M96">
-        <v>23.1183036</v>
+        <v>23.364243</v>
       </c>
       <c r="N96">
-        <v>-29.86497026666667</v>
+        <v>-30.11090966666667</v>
       </c>
       <c r="O96">
-        <v>-7.466242566666667</v>
+        <v>-7.527727416666667</v>
       </c>
       <c r="P96">
-        <v>-22.3987277</v>
+        <v>-22.58318225</v>
       </c>
       <c r="Q96">
-        <v>-6.198727700000003</v>
+        <v>-6.383182250000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9365190451487356</v>
+        <v>1.114662854178483</v>
       </c>
       <c r="T96">
-        <v>13.77914034584887</v>
+        <v>16.53496841501865</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>-0.07295806369921824</v>
+        <v>-0.07219008408133173</v>
       </c>
       <c r="W96">
-        <v>0.2530035114202757</v>
+        <v>0.252822421826378</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9186,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>-0.291832254796873</v>
+        <v>-0.2887603363253268</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9194,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2959144434439833</v>
+        <v>0.2978144434439832</v>
       </c>
       <c r="C97">
-        <v>-71.72209966536963</v>
+        <v>-72.94199225061649</v>
       </c>
       <c r="D97">
-        <v>25.27290033463038</v>
+        <v>25.09600774938351</v>
       </c>
       <c r="E97">
-        <v>40.08500000000001</v>
+        <v>41.128</v>
       </c>
       <c r="F97">
-        <v>99.08500000000001</v>
+        <v>100.128</v>
       </c>
       <c r="G97">
         <v>2.09</v>
@@ -9230,37 +9241,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M97">
-        <v>23.364243</v>
+        <v>23.6101824</v>
       </c>
       <c r="N97">
-        <v>-30.11090966666667</v>
+        <v>-30.35684906666667</v>
       </c>
       <c r="O97">
-        <v>-7.527727416666667</v>
+        <v>-7.589212266666666</v>
       </c>
       <c r="P97">
-        <v>-22.58318225</v>
+        <v>-22.7676368</v>
       </c>
       <c r="Q97">
-        <v>-6.383182250000001</v>
+        <v>-6.567636799999999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.114662854178483</v>
+        <v>1.381878567723105</v>
       </c>
       <c r="T97">
-        <v>16.53496841501865</v>
+        <v>20.66871051877332</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>-0.07219008408133173</v>
+        <v>-0.07143810403881787</v>
       </c>
       <c r="W97">
-        <v>0.252822421826378</v>
+        <v>0.2526451049323533</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9268,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>-0.2887603363253268</v>
+        <v>-0.2857524161552716</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9276,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2978144434439832</v>
+        <v>0.2997144434439832</v>
       </c>
       <c r="C98">
-        <v>-72.94199225061649</v>
+        <v>-74.15942579921708</v>
       </c>
       <c r="D98">
-        <v>25.09600774938351</v>
+        <v>24.92157420078291</v>
       </c>
       <c r="E98">
-        <v>41.128</v>
+        <v>42.17099999999999</v>
       </c>
       <c r="F98">
-        <v>100.128</v>
+        <v>101.171</v>
       </c>
       <c r="G98">
         <v>2.09</v>
@@ -9312,37 +9323,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M98">
-        <v>23.6101824</v>
+        <v>23.8561218</v>
       </c>
       <c r="N98">
-        <v>-30.35684906666667</v>
+        <v>-30.60278846666667</v>
       </c>
       <c r="O98">
-        <v>-7.589212266666666</v>
+        <v>-7.650697116666667</v>
       </c>
       <c r="P98">
-        <v>-22.7676368</v>
+        <v>-22.95209135</v>
       </c>
       <c r="Q98">
-        <v>-6.567636799999999</v>
+        <v>-6.752091350000001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.381878567723101</v>
+        <v>1.827238090297469</v>
       </c>
       <c r="T98">
-        <v>20.66871051877326</v>
+        <v>27.55828069169769</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>-0.07143810403881787</v>
+        <v>-0.07070162873944862</v>
       </c>
       <c r="W98">
-        <v>0.2526451049323533</v>
+        <v>0.252471444056762</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9350,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>-0.2857524161552716</v>
+        <v>-0.2828065149577945</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9358,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2997144434439832</v>
+        <v>0.3016144434439832</v>
       </c>
       <c r="C99">
-        <v>-74.15942579921708</v>
+        <v>-75.37445123293605</v>
       </c>
       <c r="D99">
-        <v>24.92157420078291</v>
+        <v>24.74954876706395</v>
       </c>
       <c r="E99">
-        <v>42.17099999999999</v>
+        <v>43.214</v>
       </c>
       <c r="F99">
-        <v>101.171</v>
+        <v>102.214</v>
       </c>
       <c r="G99">
         <v>2.09</v>
@@ -9394,37 +9405,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M99">
-        <v>23.8561218</v>
+        <v>24.1020612</v>
       </c>
       <c r="N99">
-        <v>-30.60278846666667</v>
+        <v>-30.84872786666667</v>
       </c>
       <c r="O99">
-        <v>-7.650697116666667</v>
+        <v>-7.712181966666667</v>
       </c>
       <c r="P99">
-        <v>-22.95209135</v>
+        <v>-23.1365459</v>
       </c>
       <c r="Q99">
-        <v>-6.752091350000001</v>
+        <v>-6.936545900000002</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.827238090297469</v>
+        <v>2.717957135446202</v>
       </c>
       <c r="T99">
-        <v>27.55828069169769</v>
+        <v>41.33742103754652</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>-0.07070162873944862</v>
+        <v>-0.06998018354822974</v>
       </c>
       <c r="W99">
-        <v>0.252471444056762</v>
+        <v>0.2523013272806726</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9432,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>-0.2828065149577945</v>
+        <v>-0.2799207341929191</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9440,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3016144434439832</v>
+        <v>0.3035144434439833</v>
       </c>
       <c r="C100">
-        <v>-75.37445123293605</v>
+        <v>-76.58711807719179</v>
       </c>
       <c r="D100">
-        <v>24.74954876706395</v>
+        <v>24.5798819228082</v>
       </c>
       <c r="E100">
-        <v>43.214</v>
+        <v>44.25699999999999</v>
       </c>
       <c r="F100">
-        <v>102.214</v>
+        <v>103.257</v>
       </c>
       <c r="G100">
         <v>2.09</v>
@@ -9476,37 +9487,37 @@
         <v>-6.746666666666666</v>
       </c>
       <c r="M100">
-        <v>24.1020612</v>
+        <v>24.3480006</v>
       </c>
       <c r="N100">
-        <v>-30.84872786666667</v>
+        <v>-31.09466726666667</v>
       </c>
       <c r="O100">
-        <v>-7.712181966666667</v>
+        <v>-7.773666816666666</v>
       </c>
       <c r="P100">
-        <v>-23.1365459</v>
+        <v>-23.32100045</v>
       </c>
       <c r="Q100">
-        <v>-6.936545900000002</v>
+        <v>-7.12100045</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.717957135446202</v>
+        <v>5.390114270892405</v>
       </c>
       <c r="T100">
-        <v>41.33742103754652</v>
+        <v>82.67484207509305</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>-0.06998018354822974</v>
+        <v>-0.06927331300733854</v>
       </c>
       <c r="W100">
-        <v>0.2523013272806726</v>
+        <v>0.2521346472071305</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9514,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>-0.2799207341929191</v>
+        <v>-0.2770932520293541</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3035144434439833</v>
-      </c>
-      <c r="C101">
-        <v>-76.58711807719179</v>
-      </c>
-      <c r="D101">
-        <v>24.5798819228082</v>
-      </c>
-      <c r="E101">
-        <v>44.25699999999999</v>
-      </c>
-      <c r="F101">
-        <v>103.257</v>
-      </c>
-      <c r="G101">
-        <v>2.09</v>
-      </c>
-      <c r="H101">
-        <v>45.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>9.453333333333333</v>
-      </c>
-      <c r="K101">
-        <v>16.2</v>
-      </c>
-      <c r="L101">
-        <v>-6.746666666666666</v>
-      </c>
-      <c r="M101">
-        <v>24.3480006</v>
-      </c>
-      <c r="N101">
-        <v>-31.09466726666667</v>
-      </c>
-      <c r="O101">
-        <v>-7.773666816666666</v>
-      </c>
-      <c r="P101">
-        <v>-23.32100045</v>
-      </c>
-      <c r="Q101">
-        <v>-7.12100045</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.390114270892405</v>
-      </c>
-      <c r="T101">
-        <v>82.67484207509305</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>-0.06927331300733854</v>
-      </c>
-      <c r="W101">
-        <v>0.2521346472071305</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>-0.2770932520293541</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
